--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EDCA75-6EC9-C649-AD08-1D796EED298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C850462-F81E-9241-953B-C25575513373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="2880" windowWidth="27280" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="334">
   <si>
     <t>Villes</t>
   </si>
@@ -949,13 +949,950 @@
   </si>
   <si>
     <t>Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clermont-Ferrand </t>
+  </si>
+  <si>
+    <t>Biologie des épithéliums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche translationnelle </t>
+  </si>
+  <si>
+    <t>Approches translationnelles de l’agression et de la réparation épithéliale</t>
+  </si>
+  <si>
+    <t>Institut Génétique Reproduction et Développement (iGReD) / INSERM 1103 CRNS 6295 Université Clermont Auvergne</t>
+  </si>
+  <si>
+    <t>vincent.sapin@uca.fr; loic.blanchon@uca.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La thématique centrale de l’équipe est de comprendre les mécanismes cellulaires et moléculaires de l’agression épithéliale appliquée à des pathologiques courantes afin d’en optimiser le diagnostic, le pronostic et la thérapeutique. </t>
+  </si>
+  <si>
+    <t>https://www.igred.fr/equipe/approche-translationnelle-des-lesions-epitheliales-et-de-leur-reparation-2/</t>
+  </si>
+  <si>
+    <t>Recherche et développement de biomarqueurs du traumatisme cranien léger</t>
+  </si>
+  <si>
+    <t>CHU Clermont-Ferrand  - Unité Investigation Clinique (UIC)  Bio2 (Biochemistry biomarkers)</t>
+  </si>
+  <si>
+    <t>vsapin@chu-clermontferrand.fr; dbouvier@chu-clermontferrand.fr</t>
+  </si>
+  <si>
+    <t>thématique centrale de l’UIC est d’appliquer des nouveaux biomarqueurs sanguins du Traumatisme cranien léger pour optimiser la gestion des patients dans la population générale et dans des populations spécifiques comme les enfants, les personnes âgées ou les sportifs</t>
+  </si>
+  <si>
+    <t>https://www.chu-clermontferrand.fr/liste-services/direction-de-la-recherche-clinique-et-de-linnovation-drci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHU Clermont-Ferrand - LBMR Biochimie du stress cérébral  (phénotype et génotype) </t>
+  </si>
+  <si>
+    <t>vsapin@chu-clermontferrand.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La labellisation de ce LBMR  a été obtenue pour les deux vagues (2017 et 2022). La thématique est le développement et l’intégration des biomarqueurs sanguins (protéique et génique) dans l’optimisation de la prise en charge des patientsd ayant subi un traumatisme crânien léger </t>
+  </si>
+  <si>
+    <t>CHU Clermont-Ferrand - Centre de référence des anomalies du développement et syndrômes malformatifs / Leucodystrophies et leucoencéphalopathies rares / Maladies neuromusculaires  / Syndrome d’Ehlers Danlos non vasculaires</t>
+  </si>
+  <si>
+    <t>isabelle.creveaux@uca.fr</t>
+  </si>
+  <si>
+    <t>L’Unité Fonctionnelle de Génétique Moléculaire (Pr. Creveaux) développe une expertise analytique et bioclinique des pathologies gérées de façon synergique avec le service de Génétique Médicale</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Mitophagie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche </t>
+  </si>
+  <si>
+    <t>UMRS 1237 – Physiopathologie et imagerie des troubles neurologiques (PHIND)</t>
+  </si>
+  <si>
+    <t>allouche-s@chu-caen.fr </t>
+  </si>
+  <si>
+    <t>Le rôle de la mitophagie lors d’un accident vasculaire cérébral reste encore mal compris, notamment en ce qui concerne ses effets délétères ou bénéfiques sur la survie neuronale. Nous travaillons sur la caractérisation des voies moléculaires de la mitophagie et leur modulation dans ce contexte d’hypoxie/réoxygénation.</t>
+  </si>
+  <si>
+    <t>https://www.unicaen.fr/laboratoire/umrs-1237-physiopathologie-et-imagerie-des-troubles-neurologiques-phind</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>Laboratoire PhIND, Inserm 1237, équipe NEUROPRESAGE
+« Pathological mechanisms and lifestyle-based interventions in brain disorders »</t>
+  </si>
+  <si>
+    <t>coulbault-l@unicaen.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche et évaluation de marqueurs biologiques prédictifs de la sévérité du sevrage d’alcool
+Rôle de la Thiamine et ses métabolites dans le développement des troubles cognitifs liés à l’alcool
+Recherche et évaluation de marqueurs d’exposition à l’alcool
+</t>
+  </si>
+  <si>
+    <t>Mitochondries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHU Caen LBMR cytopathies mitochondriales </t>
+  </si>
+  <si>
+    <t>allouche-s@chu-caen.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic biochimique des maladies mitochondriales : mesure de l’activité enzymatique des complexes de la chaîne respiratoire mitochondriale par spectrophotométrie sur homogénats musculaires et fibroblastes ; mesure de la respiration sur fibroblastes perméabilisés par oxygraphie. Diagnostic génétique : séquençage NGS de l’ADN mitochondrial ; analyse des 1136 gènes nucléaires à fonction mitochondriale par WES.Diagnostic des déficits en CoQ10 : dosage du CoQ10 par HPLC-MS/MS sur plasma, muscle, fibroblaste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHU Caen Biochimie nutritionnelle </t>
+  </si>
+  <si>
+    <t>coulbault-l@chu-caen.fr</t>
+  </si>
+  <si>
+    <t>nalyses pour le suivi nutritionnel des patients des vitamines et éléments traces par des approches de chromatographie classique (LC), de LC-MS/MS et d’ICP-MS</t>
+  </si>
+  <si>
+    <t>CHU Caen Biochimie métabolique</t>
+  </si>
+  <si>
+    <t>nowoczyn-m@chu-caen.fr</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t> Lipides et transfert des lipides dans l'inflammation et le sepsis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UMR 1231 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Center for Translational Medicine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> INSERM et CHU Dijon-Bourgogne (Centre Clinico-Biologique des Lipides et de l’Athérosclérose de la Nouvelle Société Francophone d’Athérosclérose).</t>
+    </r>
+  </si>
+  <si>
+    <t>david.masson@chu-dijon.fr ; damien.leleu@chu-dijon.fr</t>
+  </si>
+  <si>
+    <r>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>étude du rôle des lipoprotéines et des molécules lipidiques, ainsi que l’impact des échanges lipidiques dans la modulation de l’inflammation chronique (athérosclérose) et aiguë (notamment le sepsis). </t>
+    </r>
+  </si>
+  <si>
+    <t>https://ctm.ube.fr/</t>
+  </si>
+  <si>
+    <t>Physiopathologie des dyslipidémies dans le diabète de type 1, de type 2 et le syndrome métabolique.</t>
+  </si>
+  <si>
+    <t>laurence.duvillard@chu-dijon.fr ; damien.denimal@u-bourgogne.fr </t>
+  </si>
+  <si>
+    <t>tude de la physiopathologie des dyslipidémies humaines et plus particulièrement de celle associée au diabète et à l’insulino-résistance : études cinétiques, composition et fonctionnalité des HDL, stéatose hépatique d’origine métabolique, système endocannabinoïde périphérique…</t>
+  </si>
+  <si>
+    <t>Maladies héréditaires du métabolisme (phénotype) : métabolisme du cholestérol et des acides biliaires</t>
+  </si>
+  <si>
+    <t>CHU DIJON - LBMR « maladies héréditaires du métabolisme (phénotype) : métabolisme du cholestérol et des acides biliaires ». </t>
+  </si>
+  <si>
+    <t>louise.menegaut@chu-dijon.fr ; ahmad.dib@chu-dijon.fr ; stephanie.lemaire@chu-dijon.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage des stérols plasmatiques (cholestanol, 7-déhydrocholestérol et phytostérols) par GC-MS à visée diagnostique de la xanthomatose cérébrotendineuse, du syndrome de Smith-Lemli-Opitz et des phytostérolémies.  </t>
+  </si>
+  <si>
+    <t>Etude de biomarqueurs des dysfonctions vasculaires</t>
+  </si>
+  <si>
+    <t>Equipe Œil &amp; Nutrition - Centre des Sciences du Goût et de l’Alimentation (CSGA) - UMR 1324 INRAE, 6265 CNRS, Université de Bourgogne, Institut Agro Dijon</t>
+  </si>
+  <si>
+    <t>segolene.gambert@chu-dijon.fr</t>
+  </si>
+  <si>
+    <t>Etude au sein d’une cohorte mère/enfant, prématuré ou non, atteints ou non de ROP, des statuts lipidique, protéique et glycémique maternels et de l’enfant afin de mettre en évidence une relation entre le déséquilibre nutritionnel de la mère et celui de la descendance en relation avec le développement de la ROP</t>
+  </si>
+  <si>
+    <t>Toxicologie</t>
+  </si>
+  <si>
+    <t>prise en charge des intoxications au protoxyde d’azote</t>
+  </si>
+  <si>
+    <t>CHU DIJON - Centre de Compétences PROTOSIDE (Plateformes et Réseaux pour l’Orientation, le Traitement et l’Organisation des Soins des Intoxications au N20, Diagnostic et Education)</t>
+  </si>
+  <si>
+    <t>damien.denimal@chu-dijon.fr ; damien.leleu@chu-dijon.fr ; louise.menegaut@chu-dijon.fr</t>
+  </si>
+  <si>
+    <t>réseau local multidisciplinaire (Biochimie, Toxicologie, Médecine d’Urgence, Neurologie et Addictologie) ayant pour missions la coordination de la prise en charge de ces patients intoxiqués et la sensibilisation auprès du grand public et des professionnels. </t>
+  </si>
+  <si>
+    <t>Grenoble</t>
+  </si>
+  <si>
+    <t>Métabolomique</t>
+  </si>
+  <si>
+    <t>IMC : Innovations Translationnelles en Médecine et Complexité</t>
+  </si>
+  <si>
+    <t>alegouellec@chu-grenoble.fr</t>
+  </si>
+  <si>
+    <t>Dotée d’un équipement performant (Q-Exactive Thermo Haute Résolution) notre plateforme mixte (UGA/CHU) permet la réalisation de projets de recherche bio-clinique d’analyse du métabolome dans les liquides biologiques.</t>
+  </si>
+  <si>
+    <t>https://www.gemeli-uga.fr/</t>
+  </si>
+  <si>
+    <t>Maladies Neuromusculaires</t>
+  </si>
+  <si>
+    <t>CHU Grenoble - LBMR Maladies neuromusculaires</t>
+  </si>
+  <si>
+    <t>jfaure1@chu-grenoble.fr</t>
+  </si>
+  <si>
+    <t>L’Unité médicale est LBMR pour les myopathies congénitales et les arthrogryposes. Une forte expertise de recherche est également associée à l’activité de soin concernant les pathologies impliquant le rôle des canaux calciques dans la contraction musculaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudo Obstruction Intestinale Chronique </t>
+  </si>
+  <si>
+    <t>CHU Grenoble - LBMR Pseudo Obstruction Intestinale Chronique</t>
+  </si>
+  <si>
+    <t>jrendu@chu-grenoble.fr</t>
+  </si>
+  <si>
+    <t>L’Unité médicale est LBMR pour les Pseudo-Obstructions Intestinales Chroniques. Expertise génétique (identification de nouveaux gènes, étude de cohorte, test fonctionnel ...)</t>
+  </si>
+  <si>
+    <t>Immunologie</t>
+  </si>
+  <si>
+    <t>Déficits immunitaires innés des phagocytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHU Grenoble - LBMR Déficits immunitaires innés des phagocytes
+</t>
+  </si>
+  <si>
+    <r>
+      <t>mjstasia@chu-grenoble.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cplazy@chu-grenoble.fr</t>
+    </r>
+  </si>
+  <si>
+    <t>L’Unité Fonctionnelle est un LBMR pour le diagnostic fonctionnel et génétique de la Granulomatose Septique Chronique et du déficit en Rac2. Une forte expertise de recherche est également associée à l’activité de soin concernant les pathologies liées au déficit en NADPH oxydase NOX2 des phagocytes</t>
+  </si>
+  <si>
+    <t>Saint-Etienne</t>
+  </si>
+  <si>
+    <t>Neuropathies périphériques dysimmunes et pathologies neuromusculaires</t>
+  </si>
+  <si>
+    <t>Laboratoire Synaptopathies et autoanticorps</t>
+  </si>
+  <si>
+    <r>
+      <t>jean.philippe.camdessanche@univ-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nadia.boutahar@univ-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@univ-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>L’équipe s’intéresse aux anticorps associés aux neuropathies périphériques dysimmunes. L’un des objectifs est d’identifier de nouveaux autoanticorps par des méthodes protéomiques puis de caractériser les cibles protéiques, les autoanticorps et les patients présentant ces autoanticorps sur le plan clinique. Un autre axe de recherche est le développement de modèles in vitro de cultures cellulaires pour tester l’effet pathogène des anticorps identifiés.</t>
+  </si>
+  <si>
+    <t>https://www.univ-st-etienne.fr/fr/synatac.html</t>
+  </si>
+  <si>
+    <t>Biologie des maladies neurologiques inflammatoires</t>
+  </si>
+  <si>
+    <t>CHU Saint-Etienne</t>
+  </si>
+  <si>
+    <r>
+      <t>estelle.moschetti@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Nous réalisons les explorations permettant de mettre en évidence la présence d’une inflammation dans le liquide cérébrospinal (LCS) à l’aide de différents marqueurs tels que la recherche de bandes oligoclonales par isoélectrofocalisation et les dosages des chaines légères libres kappa dans le LCS. Ces analyses participent ainsi au diagnostic de la sclérose en plaques et des maladies neurologiques inflammatoires (Réseau Rhône-Alpes SEP).</t>
+  </si>
+  <si>
+    <t>Gammapathies monoclonales</t>
+  </si>
+  <si>
+    <r>
+      <t>Lise.thibaudin@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amelie.moreau@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diane.nehar@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>estelle.moschetti@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Notre laboratoire réalise l’ensembles des analyses (électrophorèse des protéines sériques, immunotypage sanguin et urinaire, dosage des chaines légères libres (Freelite) et des chaines lourdes d’immunoglobulines (Hevylite)) permettant le diagnostic et suivi des gammapathies monoclonales en lien avec l'Institut de Cancérologie et d'hématologie Universitaire de Saint-Étienne.</t>
+  </si>
+  <si>
+    <t>Urologie</t>
+  </si>
+  <si>
+    <t>Analyse morpho-constitutionnelle des calculs urinaires</t>
+  </si>
+  <si>
+    <r>
+      <t>Lise.thibaudin@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Notre laboratoire réalise les analyses morphologiques et constitutionnelle par spectrométrie infrarouge des calculs rénaux permettant l’orientation étiologique et l’adaptation de la prise en charge des patients en lien avec les services de néphrologie et d’urologie du GHT Loire.</t>
+  </si>
+  <si>
+    <t>Maladies héréditaires du métabolisme</t>
+  </si>
+  <si>
+    <r>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>estelle.moschetti@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Notre laboratoire réalise la chromatographie des acides aminés plasmatiques et urinaires pour le diagnostic et le suivi des maladies héréditaires du métabolisme, essentiellement les aminoacidopathies et maladies du cycle de l’urée. La filière de diagnostic et prise en charge est coordonnée avec le Service d'endocrinologie et de diabétologie pédiatriques et maladies héréditaires du métabolisme et le laboratoire du CHU de Lyon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubles comportementaux alimentaires (TCA) </t>
+  </si>
+  <si>
+    <r>
+      <t>nadia.boutahar@univ-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lise.thibaudin@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amelie.moreau@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diane.nehar@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>estelle.moschetti@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Notre laboratoire réalise les explorations biochimiques et endocriniennes permettant le diagnostic et le suivi des patients présentant des troubles comportementaux alimentaires (TCA) en lien avec le centre de référence du CHU.</t>
+  </si>
+  <si>
+    <t>Pathologies du globules rouges </t>
+  </si>
+  <si>
+    <r>
+      <t>Lise.thibaudin@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diane.nehar@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yannick.tholance@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>philippe.gonzalo@chu-st-etienne.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Notre laboratoire réalise les explorations phénotypiques des anomalies de l’hémoglobine et d’autres pathologies du globule rouge telles que les déficits enzymatiques dans le cadre de la Filière MCGRE avec le centre de compétence des syndromes drépanocytaires majeurs, thalassémies et autres pathologies rares du globule rouge et de l’érythropoïèse. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1043,6 +1980,35 @@
       <name val="Symbol"/>
       <charset val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1071,7 +2037,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1082,6 +2048,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1298,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="5" customWidth="1"/>
@@ -2405,7 +3393,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>227</v>
       </c>
@@ -2428,7 +3416,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>227</v>
       </c>
@@ -2451,7 +3439,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>227</v>
       </c>
@@ -2474,7 +3462,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>227</v>
       </c>
@@ -2497,7 +3485,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>227</v>
       </c>
@@ -2520,7 +3508,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>227</v>
       </c>
@@ -2543,7 +3531,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>227</v>
       </c>
@@ -2566,7 +3554,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>227</v>
       </c>
@@ -2589,7 +3577,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>227</v>
       </c>
@@ -2612,7 +3600,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>227</v>
       </c>
@@ -2635,7 +3623,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>227</v>
       </c>
@@ -2658,7 +3646,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>227</v>
       </c>
@@ -2680,6 +3668,606 @@
       <c r="G60" s="1" t="s">
         <v>208</v>
       </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G61" t="s">
+        <v>234</v>
+      </c>
+      <c r="H61" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" t="s">
+        <v>241</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="13"/>
+      <c r="E66" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" t="s">
+        <v>259</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69"/>
+      <c r="E69" t="s">
+        <v>265</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G69"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" t="s">
+        <v>268</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E72" t="s">
+        <v>277</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" t="s">
+        <v>280</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H85"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2723,6 +4311,18 @@
     <hyperlink ref="F57" r:id="rId38" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{8A25F254-1F07-EF40-8A77-B07CC1210C87}"/>
     <hyperlink ref="F59" r:id="rId39" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{04465399-95C2-B841-9AF9-41E159622525}"/>
     <hyperlink ref="F60" r:id="rId40" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{C0D93B2A-4E80-7845-AF7F-85D71C50AE65}"/>
+    <hyperlink ref="F62" r:id="rId41" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{215E0BAC-3F91-4441-A5EE-05CD86C520E8}"/>
+    <hyperlink ref="F63" r:id="rId42" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{5164F7E5-B132-4547-8D67-1DD37119DF76}"/>
+    <hyperlink ref="F64" r:id="rId43" xr:uid="{2F90BF34-1DC0-9F4C-A116-B82EE7E57018}"/>
+    <hyperlink ref="F65" r:id="rId44" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{34CBAC6B-3856-274A-9972-0B1B2683E0E5}"/>
+    <hyperlink ref="F66" r:id="rId45" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{869DA3A7-90C0-F041-A2A2-9FDD665D47E5}"/>
+    <hyperlink ref="H66" r:id="rId46" xr:uid="{F50B2023-9B84-CA4B-9093-712A67157BB0}"/>
+    <hyperlink ref="F67" r:id="rId47" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{35C73C37-160A-AF45-BBB5-37B45AA74546}"/>
+    <hyperlink ref="F68" r:id="rId48" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{1512DEA5-946F-A948-A724-D2FEFF49B882}"/>
+    <hyperlink ref="F69" r:id="rId49" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{0379C5AD-F64A-7749-B2BE-594941FF6B51}"/>
+    <hyperlink ref="F75" r:id="rId50" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{CB1A3546-0683-2E4C-9133-DF98427D1832}"/>
+    <hyperlink ref="F76" r:id="rId51" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{AC460DD2-B32F-F943-A6E1-14BC5C716C06}"/>
+    <hyperlink ref="F77" r:id="rId52" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{6D3E2DFD-4026-6E46-AAA0-D1889CEDC6E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C850462-F81E-9241-953B-C25575513373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE64E446-65B6-F14C-A009-BB9D8BF2AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="2880" windowWidth="27280" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="440">
   <si>
     <t>Villes</t>
   </si>
@@ -1886,6 +1886,324 @@
   </si>
   <si>
     <t xml:space="preserve">Notre laboratoire réalise les explorations phénotypiques des anomalies de l’hémoglobine et d’autres pathologies du globule rouge telles que les déficits enzymatiques dans le cadre de la Filière MCGRE avec le centre de compétence des syndromes drépanocytaires majeurs, thalassémies et autres pathologies rares du globule rouge et de l’érythropoïèse. </t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>Endocrinologie</t>
+  </si>
+  <si>
+    <t>Etudes des pathologies endocrines (hypophyse) et des lésions endocrines dépendantes (méningiomes). https://www.marseille-medical-genetics.org/fr/</t>
+  </si>
+  <si>
+    <t>MMG Marseille Medical Genetics</t>
+  </si>
+  <si>
+    <t>anne.barlier@univ-amu.fr</t>
+  </si>
+  <si>
+    <t>Nous travaillons sur la physiopathologie de pathologies endocrines en particulier touchant l'hypophyse et les lésions endocrines dépendantes (méningiomes) pour comprendre les mécanismes moléculaires impliqués dans ces pathologies et identifier de nouvelles stratégies thérapeutiques. Le manque de modèles in vitro pour les pathologies du développement hypophysaire ou des tumeurs hypophysaires nous a amenés, au cours des cinq dernières années, à mettre au point un protocole de différenciation des cellules iPS humaines (hiPSC) en organoïdes hypophysaires capable de sécréter des hormones. Leur caractérisation nous permet de déterminer le rôle de facteurs identifiés dans l'analyse génétique des patients porteurs de déficits hypophysaires, ou de tumeurs hypophysaires </t>
+  </si>
+  <si>
+    <t>Médecine moléculaire</t>
+  </si>
+  <si>
+    <t>Génétique constitutionnelle</t>
+  </si>
+  <si>
+    <t>GEnOPé (Génétique Endocrinienne, Oncologique et Pharmacogénétique) </t>
+  </si>
+  <si>
+    <t>anne.barlier@ap-hm.fr</t>
+  </si>
+  <si>
+    <t>Le service GEnOPé (Génétique Endocrinienne, Oncologique et Pharmacogénétique) assure le diagnostic en génétique constitutionnelle des tumeurs fréquentes et de syndromes tumoraux rares, des pathologies endocriniennes rares, de l’hémochromatose et des surcharges en fer et en cuivre, des hypercholesterolémies, de la pharmacogénétique. Nous travaillons en interaction avec le CRMR HYPO (Maladies rares de l’Hypophyse, Marseille Pr Brue) et CEDRA (dyslipidemies rares, Marseille, Pr S Belliard)</t>
+  </si>
+  <si>
+    <t>Cardiovasculaire</t>
+  </si>
+  <si>
+    <t>Physiopathologie des agressions et dysfonctions cardiaques</t>
+  </si>
+  <si>
+    <t>Centre de Recherche en Cardiovasculaire et Nutrition (C2VN) - Equipe 5</t>
+  </si>
+  <si>
+    <t>regis.guieu@univ-amu.fr</t>
+  </si>
+  <si>
+    <t>Les travaux de l'équipe 5 du C2VN porte sur 2 axes : 1) le rôle du système adénosinergique en physiopathologie cardiovasculaire (syndrome coronarien chronique, syncope réflexe, fibrillation atriale) ; 2) les mécanismes de l'insuffisance cardiaque dans le contexte de myocardites induites par les immunothérapies anticancéreuses. Nos objectifs sont : 1) D'identifier de nouveaux biomarqueurs issus du système adénosinergique pour le dépistage et le suivi des maladies cardiovasculaires; 2) Identifier des biomarqueurs précoces et innovants des cardiotoxicités inuites par les thérapies anti-cancéreuses.</t>
+  </si>
+  <si>
+    <t>LBMR : Maladies héréditaires du métabolisme (phénotype) : métabolisme des acides aminés (aciduries organiques, aminocidopathies, cycle de l'urée, cétogenèse et cétolyse)</t>
+  </si>
+  <si>
+    <t>Laboratoire de Biochimie Métabolique et de Biochimie Spécialisée - Hôpitaux Universitaires de Marseille</t>
+  </si>
+  <si>
+    <t>Marguerite.GASTALDI@ap-hm.fr; julia-sophie.dodivers@ap-hm.fr</t>
+  </si>
+  <si>
+    <t>Maladies héréditaires du métabolisme (phénotype et génotype) : métabolisme des métaux (cuivre)</t>
+  </si>
+  <si>
+    <t>julien.fromonot@ap-hm.fr; julia-sophie.dodivers@ap-hm.fr</t>
+  </si>
+  <si>
+    <t>Notre laboratoire appartient au Centre de compétence pour le diagnostic et le suivi de la maladie de Wilson. Le développement du dosage du cuivre échangeable et le séquence du gène ATP7B nous permettent d'améliorer la prise en charge de cette pathologie pour l'ensemble de notre territoire de santé,</t>
+  </si>
+  <si>
+    <t>Diagnostic différentiel du syndrome polyuro-polydipsique de l'enfant</t>
+  </si>
+  <si>
+    <t>julien.fromonot@ap-hm.fr</t>
+  </si>
+  <si>
+    <t>En collaboration avec le service d'endocrinologie pédiatrique, notre laboratoire participe au programme national de recherche clinique pour l'utilisation de la cinétique de copeptine dans le diagnostic différentiel du syndrome polyuropolydipsique de l'enfant,</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Etude du neurodéveloppement et des processus neurodégénératifs</t>
+  </si>
+  <si>
+    <t>Institut de Neurosciences de Montpellier UMR Inserm UM 1298</t>
+  </si>
+  <si>
+    <t>sylvain.lehmann@umontpellier.fr</t>
+  </si>
+  <si>
+    <t>L’Institut des Neurosciences  de Montpellier (INM) est une Unité Mixte de Recherche Inserm-Université de Montpellier. L'INM a pour objectif conduire une recherche fondamentale et translationnelle pour étudier le développement, la plasticité et l'intégration synaptique et les processus neurodégénératifs conduisant à des troubles du système central et sensori-moteur.</t>
+  </si>
+  <si>
+    <t>Muscles et déficiences d’organes</t>
+  </si>
+  <si>
+    <t>Mécanismes de la fonction musculaire dans des conditions de déficience d'organes ( insuffisance rénale). https://www.phymedexp.com/</t>
+  </si>
+  <si>
+    <t>PhyMedExp : Physiologie et médecine expérimentale du cœur et des muscles (INSERM, CNRS, Université de Montpellier)</t>
+  </si>
+  <si>
+    <t>jp-cristol@chu-montpellier.fr</t>
+  </si>
+  <si>
+    <t>PhyMedex est une Unité Mixte de Recherche CNRS-Inserm-Université de Montpellier qui a pour objectif la caractérisation des mécanismes moléculaires et cellulaires associés à la fonction musculaire dans différentes conditions de déficience d’organes dont l’insuffisance rénale chronique.</t>
+  </si>
+  <si>
+    <t>LBMR Maladies Neurodégénératives et Neuroinflammatoires</t>
+  </si>
+  <si>
+    <t>LBMR : Laboratoire de Biochimie Protéomique clinique (LBPC)</t>
+  </si>
+  <si>
+    <t>s-lehmann@chu-montpellier.fr</t>
+  </si>
+  <si>
+    <t>Le LBPC est responsable de la mesure des biomarqueurs pour le diagnostic de différentes maladies neurologiques (Alzheimer, SLA, SEP..). Il utilise pour sa partie R&amp;D des approches de spectrométrie de masse et d’immunodétection ultrasensible et multiplexe.</t>
+  </si>
+  <si>
+    <t>Laboratoire de Biochimie et Hormonologie, CHU Montpellier</t>
+  </si>
+  <si>
+    <t>s-badiou@chu-montpellier.fr</t>
+  </si>
+  <si>
+    <t>L’activité dans le domaine des MHM s’appuie sur des méthodes séparatives avec détection par spectrométrie de masse. Cette activité permet les confirmations du dépistage néonatal ainsi que l’orientation diagnostique en soins courant avec une organisation en regard de l’urgence métabolique ainsi que le suivi régulier des patients avec MHM. </t>
+  </si>
+  <si>
+    <t>Néphrologie</t>
+  </si>
+  <si>
+    <t>LBMR Biochimie des pathologies rénales (phénotype)</t>
+  </si>
+  <si>
+    <t>Les méthodes maîtrisées au laboratoire permettent de dépister et classifier les maladies rénales chroniques (MRC) (créatinine, albuminurie) mais aussi de répondre à des besoins diagnostics précis (cystatine, Iohexol, cristallurie, aminoacidopathies …). Le laboratoire explore les comorbidités associées à la MRC comme les cardiopathies, les myopathies urémiques et les désordres métaboliques et énergétiques.</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Vieillissement moléculaire et modifications des protéines</t>
+  </si>
+  <si>
+    <t>UMR CNRS 7369 MEDyC – équipe 2</t>
+  </si>
+  <si>
+    <t>sjaisson@chu-reims.fr</t>
+  </si>
+  <si>
+    <t>Les protéines subissent au cours de leur vie biologique des modifications dites non enzymatiques qui concourent à leur vieillissement moléculaire qui se traduit par une altération de leurs propriétés structurales et fonctionnelles. Les produits issus de ces modifications peuvent servir de biomarqueurs pour le suivi de la progression de maladies chroniques comme la maladie rénale chronique ou le diabète.</t>
+  </si>
+  <si>
+    <t>LBMR Marqueurs protéiques de diagnostic et suivi du diabète sucré</t>
+  </si>
+  <si>
+    <t>CHU de Reims</t>
+  </si>
+  <si>
+    <t>Notre laboratoire a développé une expertise pour les méthodes analytiques de dosage des produits de glycation des protéines par LC-MS/MS (HbA1c et AGEs) et fait partie du réseau international IFCC de laboratoires de référence pour le dosage de l’HbA1c.</t>
+  </si>
+  <si>
+    <t>LBMR Biochimie endocrine (phénotype) : axe surrénalien</t>
+  </si>
+  <si>
+    <t>dmarot@chu-reims.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic étiologique du syndrome de Cushing ACTH-dépendant (adénome corticotrope ou sécrétion ectopique) ou ACTH-indépendant (hyperplasies bilatérales des surrénales, adénome surrénalien et le corticosurrénalome). Diagnostic de l'insuffisance surrénale. Membre du groupe Hormonologie FIRENDO.</t>
+  </si>
+  <si>
+    <t>Intérêt des molécules matricielles plasmatiques vésiculaires comme nouveau biomarqueur du cancer.</t>
+  </si>
+  <si>
+    <t>UMR CNRS 7369 MEDyC – équipe 1</t>
+  </si>
+  <si>
+    <t>lramont@chu-reims.fr</t>
+  </si>
+  <si>
+    <t>La recherche de marqueurs biochimiques dans le sang des patients dans un but de dépistage et/ou diagnostique n’a pas donné de résultats satisfaisants à ce jour. Les cellules cancéreuses libèrent des vésicules extracellulaires qui contiennent des protéines. L’utilisation de protéines vésiculaires comme nouveaux marqueurs tumoraux semble prometteuse.</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Infectiologie</t>
+  </si>
+  <si>
+    <t>Biomarqueurs Biochimiques des Infections</t>
+  </si>
+  <si>
+    <t>NUMECAN</t>
+  </si>
+  <si>
+    <t>Claude.bendavid@univ-rennes.fr</t>
+  </si>
+  <si>
+    <t>Au sein de l’équipe NUMECAN équipe EXPRES le laboratoire participe en lien avec nos collègues rhumatologues et pneumologues à l’étude ciblée et non ciblée de liquides articulaires et pleuraux afin d’identifier de nouveaux biomarqueurs précoces d’infection</t>
+  </si>
+  <si>
+    <t>Hépatolo-Gastro-Entérologie</t>
+  </si>
+  <si>
+    <t>Biomarqueurs de l’ACLF : « acute on chronic liver failure »</t>
+  </si>
+  <si>
+    <t>Au sein de l’equipe NUMECAN équipe EXPRES, nous étudions par des méthodes ciblées et non ciblées deux cohortes de patients à différents stades d’ACLF et ce de façon longitudinale afin d’améliorer le diagnostic et pronostic de cette pathologie hépatique grave, et aussi d’en identifier les ressorts physiopathologiques</t>
+  </si>
+  <si>
+    <t>Néonatalogie</t>
+  </si>
+  <si>
+    <t>Marqueurs néonataux émergents et environnementaux</t>
+  </si>
+  <si>
+    <t>IRSET équipe 1 </t>
+  </si>
+  <si>
+    <t>Caroline.moreau@univ-rennes.fr</t>
+  </si>
+  <si>
+    <t>Lors du renouvellement de l’unité et dans le cadre de l’équipe GENISYS, l’objectif est de développer les apports du dépistage Néonatal dans le cadre des pathologies en lien avec les expositions environnementales, et notamment sur les anomalies de développement sexuel.</t>
+  </si>
+  <si>
+    <t>Glioblastome, hétérogénéité génétique et cible thérapeutique</t>
+  </si>
+  <si>
+    <t>INSERM U1242 OSS, équipe @tomics</t>
+  </si>
+  <si>
+    <t>jean.mosser@univ-rennes.fr</t>
+  </si>
+  <si>
+    <t>Nous investiguons rôle du facteur de transcription EMX2 dans la glioblastomagenèse en (1) recherchant le réseau génique qu’il module, les nœuds d’interaction convergents  et les surrogates associés spécifiquement à l’action antitumorale, (2) évaluant l’effet de EMX2 sur la survie in vivo, (3) décrivant les évolutions clonales des cellules tumorales en réponse à l’inhibition de l’UPR associée non à l’expression de EMX2.</t>
+  </si>
+  <si>
+    <t>Expression des gènes et oncogenèse : mélanome et  LAL B de l’enfant</t>
+  </si>
+  <si>
+    <t>Institut de Génétique et Développement de Rennes, IGDR UMR 6290 CNRS, Université de Rennes, ERL Inserm U1305</t>
+  </si>
+  <si>
+    <t>marie-dominique-galibert-anne@univ-rennes.fr</t>
+  </si>
+  <si>
+    <t>L’équipe GEO étudie les mécanismes génétiques et cellulaires des cellules tumorales en se concentrant sur les mécanismes qui régissent la plasticité tumorale, les rechutes, l’objectif ultime étant l’identification de vulnérabilités thérapeutiques afin de proposer des approches innovantes de thérapie ARN. Ses recherches portent principalement sur deux cancers : le mélanome et la leucémie aiguë lymphoblastique B de l’enfant.</t>
+  </si>
+  <si>
+    <t>Génétique des Pathologies du Développement du Neurectoderme</t>
+  </si>
+  <si>
+    <t>Institut de Génétique et Développement de Rennes</t>
+  </si>
+  <si>
+    <t>marie.detayrac@univ-rennes.fr; christele.dubourg@univ-rennes.fr</t>
+  </si>
+  <si>
+    <t>Notre équipe de recherche étudie les processus biologiques qui régissent la mise en place du cerveau au cours des premières étapes du développement en situation normale, et se concentre également sur les maladies rares du développement du système nerveux afin d’établir leurs causes et leurs conséquences au niveau moléculaire, cellulaire et organique.</t>
+  </si>
+  <si>
+    <t>LBMR Fer et surcharge en fer rares d’origine génétique </t>
+  </si>
+  <si>
+    <t>CHU RENNES</t>
+  </si>
+  <si>
+    <t>houda.hamdi@chu-rennes.fr (génétique) ; Martine.ROPERT-BOUCHET@chu-rennes.fr (biochimie)</t>
+  </si>
+  <si>
+    <t>Prise en charge intégrée phénotype/génotype, reposant sur des analyses spécialisées et innovantes en biochimie (dosage d’hepcidine, formes anormales de fer, analyses multi-métaux,..) et en génétique (analyses de panels, d’exome, tests fonctionnels,…) ainsi que des discussions pluridisciplinaires en lien avec le Centre de Référence National de Rennes, pour affiner le diagnostic, mieux caractériser les formes complexes et améliorer la prise en charge des patients et le conseil aux prescripteurs.</t>
+  </si>
+  <si>
+    <t>Analyse génétique des obésités monogéniques </t>
+  </si>
+  <si>
+    <t>houda.hamdi@chu-rennes.fr</t>
+  </si>
+  <si>
+    <t>Les obésités monogéniques sont des formes rares d’obésité sévère, généralement précoces, liées à des mutations affectant des gènes clés de la régulation de l’appétit et du métabolisme énergétique (notamment la voie leptine–mélanocortine). Elles se manifestent souvent dès l’enfance par une hyperphagie et une prise de poids rapide. Leur identification est essentielle, car certaines bénéficient aujourd’hui de traitements ciblés. Le laboratoire de génétique du CHU de Rennes fait partie d’un réseau de 5 laboratoires en France à  proposer l’analyse d’un panel de gènes impliqués dans cette pathologie.</t>
+  </si>
+  <si>
+    <t>Bioinformatique</t>
+  </si>
+  <si>
+    <t>Bioinformatique médicale</t>
+  </si>
+  <si>
+    <t>marie.de.tayrac@chu-rennes.fr</t>
+  </si>
+  <si>
+    <t>Notre laboratoire accompagne l’ensemble des activités du pôle Biologie du CHU de Rennes dans ses activités de bioinformatique à visée de soin. Il développe des approches d’intelligence artitificielle pour intégrer les données cliniques et biologiques et faciliter le travail des biologistes.</t>
+  </si>
+  <si>
+    <t>CCMR maladies héréditaires du métabolisme</t>
+  </si>
+  <si>
+    <t>Le laboratoire réalise et développe une activité de diagnostic et suivi des maladies héréditaires du métabolisme pour lesquelles nous sommes actuellement centre de compétence avec l’ambition de monter centre de référence au prochain appel à candidature. Nous proposons en soins et recherche  les panels rédox et en spectrométrie de masse (Acides aminés, acyls carnitines, acides organiques) avec des approches </t>
+  </si>
+  <si>
+    <t>LBMR « Diagnostic génétique de l’holoprosencéphalie »</t>
+  </si>
+  <si>
+    <t>christele.dubourg@chu-rennes.fr</t>
+  </si>
+  <si>
+    <t>L'holoprosencéphalie (HPE) est une malformation cérébrale complexe due à un défaut de clivage médian du prosencéphale, survenant entre le 18e et le 28e jour de gestation, touchant le cerveau antérieur et la face. Le CHU de Rennes est le centre de référence national pour cette pathologie. </t>
+  </si>
+  <si>
+    <t>Diagnostic génétique des troubles du neurodéveloppement</t>
+  </si>
+  <si>
+    <t>Les troubles du neurodéveloppement (TND) se caractérisent par un retard de développement et se traduisent principalement par des atteintes cognitives et comportementales. Ils regroupent des pathologies très diverses (handicap intellectuel, autisme, déficit de l’attention…) et touchent 1 à 2% de la population générale. Du fait de leur hétérogénéité, les outils de séquençage à haut débit tels que l’exome sont particulièrement adaptés pour en rechercher les causes génétiques. </t>
+  </si>
+  <si>
+    <t>Diagnostic génétique de l’épilepsie</t>
+  </si>
+  <si>
+    <t>L’objectif est d’identifier un facteur génétique chez tout patient présentant une encéphalopathie épileptique ou bien certaines formes d’épilepsie focale ou multifocale. L’analyse porte dans un premier temps sur un panel de gènes in silico puis est étendue à l’ensemble des données.</t>
   </si>
 </sst>
 </file>
@@ -2286,7 +2604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="5" customWidth="1"/>
@@ -4268,6 +4586,648 @@
         <v>333</v>
       </c>
       <c r="H85"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE64E446-65B6-F14C-A009-BB9D8BF2AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CBBE24-EDD0-5949-9B01-8B8EA5BC2ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="2880" windowWidth="27280" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="440">
   <si>
     <t>Villes</t>
   </si>
@@ -197,9 +197,6 @@
   </si>
   <si>
     <t>Les porphyries sont des maladies héréditaires du métabolisme de l’hème. L’équipe du service de biochimie en lien avec le service de médecine interne (Hôpital Saint-André, Bordeaux) assure le diagnostic, le soin et la recherche (Equipe BioGO, physiopathologie et thérapeutique) pour ce groupe de maladies rares.</t>
-  </si>
-  <si>
-    <t>Medecine Moléculaire</t>
   </si>
   <si>
     <t>Biomarqueurs des pathologies neurodégénératives</t>
@@ -2204,17 +2201,27 @@
   </si>
   <si>
     <t>L’objectif est d’identifier un facteur génétique chez tout patient présentant une encéphalopathie épileptique ou bien certaines formes d’épilepsie focale ou multifocale. L’analyse porte dans un premier temps sur un panel de gènes in silico puis est étendue à l’ensemble des données.</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2353,40 +2360,43 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2689,7 +2699,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
@@ -2701,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>18</v>
@@ -2718,16 +2728,16 @@
         <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2735,7 +2745,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
@@ -2744,13 +2754,13 @@
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2764,7 +2774,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -2787,7 +2797,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -2813,7 +2823,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>32</v>
@@ -2842,7 +2852,7 @@
         <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -2905,10 +2915,10 @@
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>42</v>
@@ -2928,7 +2938,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>36</v>
@@ -2951,7 +2961,7 @@
         <v>28</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>37</v>
@@ -2974,7 +2984,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>38</v>
@@ -2997,7 +3007,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>39</v>
@@ -3008,7 +3018,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>15</v>
@@ -3017,21 +3027,21 @@
         <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
@@ -3040,44 +3050,44 @@
         <v>46</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>15</v>
@@ -3086,21 +3096,21 @@
         <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>15</v>
@@ -3109,21 +3119,21 @@
         <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
@@ -3132,21 +3142,21 @@
         <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>13</v>
@@ -3155,21 +3165,21 @@
         <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>15</v>
@@ -3178,21 +3188,21 @@
         <v>46</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>15</v>
@@ -3201,19 +3211,19 @@
         <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>15</v>
@@ -3222,19 +3232,19 @@
         <v>47</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>15</v>
@@ -3243,63 +3253,63 @@
         <v>47</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>339</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="G30" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>13</v>
@@ -3308,21 +3318,21 @@
         <v>46</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -3331,21 +3341,21 @@
         <v>46</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>15</v>
@@ -3354,21 +3364,21 @@
         <v>46</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>15</v>
@@ -3377,44 +3387,44 @@
         <v>47</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="G34" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -3423,44 +3433,44 @@
         <v>47</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="G37" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>15</v>
@@ -3469,67 +3479,67 @@
         <v>54</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F38" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="G39" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="6" t="s">
+      <c r="G40" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>15</v>
@@ -3538,21 +3548,21 @@
         <v>47</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>15</v>
@@ -3561,21 +3571,21 @@
         <v>46</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="G42" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>13</v>
@@ -3584,21 +3594,21 @@
         <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="G43" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>15</v>
@@ -3607,44 +3617,44 @@
         <v>46</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="G45" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>13</v>
@@ -3653,21 +3663,21 @@
         <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
@@ -3676,21 +3686,21 @@
         <v>46</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -3699,44 +3709,44 @@
         <v>47</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="G49" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>15</v>
@@ -3745,90 +3755,90 @@
         <v>46</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>13</v>
@@ -3837,21 +3847,21 @@
         <v>46</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>13</v>
@@ -3860,113 +3870,113 @@
         <v>47</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F56" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="G56" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="G57" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F58" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F59" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>15</v>
@@ -3975,47 +3985,47 @@
         <v>47</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F60" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="C61" t="s">
         <v>229</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="G61" t="s">
         <v>233</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>234</v>
-      </c>
-      <c r="H61" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>7</v>
@@ -4024,24 +4034,24 @@
         <v>54</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="G62" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>7</v>
@@ -4049,21 +4059,23 @@
       <c r="C63" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="E63" t="s">
+        <v>240</v>
+      </c>
+      <c r="F63" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="G63" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="H63"/>
     </row>
     <row r="64" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>7</v>
@@ -4071,113 +4083,123 @@
       <c r="C64" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D64" s="1"/>
+      <c r="D64" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="E64" t="s">
+        <v>243</v>
+      </c>
+      <c r="F64" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="G64" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="H64"/>
     </row>
     <row r="65" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="C65" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="D65" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="G65" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="H65" s="1" t="s">
+    </row>
+    <row r="66" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" s="10" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>254</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="14" t="s">
+      <c r="D66" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="F66" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="G66" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="G66" s="14" t="s">
-        <v>257</v>
-      </c>
       <c r="H66" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B67" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E67" t="s">
         <v>258</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D67" s="1"/>
-      <c r="E67" t="s">
+      <c r="F67" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="G67" s="14" t="s">
         <v>260</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>261</v>
       </c>
       <c r="H67"/>
     </row>
     <row r="68" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D68"/>
+      <c r="D68" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="E68" t="s">
+        <v>261</v>
+      </c>
+      <c r="F68" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="G68" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="H68"/>
     </row>
     <row r="69" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>15</v>
@@ -4185,19 +4207,21 @@
       <c r="C69" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D69"/>
+      <c r="D69" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="E69" t="s">
+        <v>264</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>15</v>
@@ -4206,24 +4230,24 @@
         <v>46</v>
       </c>
       <c r="D70" t="s">
+        <v>267</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>15</v>
@@ -4232,24 +4256,24 @@
         <v>46</v>
       </c>
       <c r="D71" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="H71" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>15</v>
@@ -4258,22 +4282,22 @@
         <v>47</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E72" t="s">
         <v>276</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="H72"/>
     </row>
     <row r="73" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>15</v>
@@ -4282,46 +4306,46 @@
         <v>46</v>
       </c>
       <c r="D73" t="s">
+        <v>279</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="H73"/>
     </row>
     <row r="74" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B74" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="H74"/>
     </row>
     <row r="75" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>15</v>
@@ -4330,24 +4354,24 @@
         <v>46</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="F75" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="G75" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>7</v>
@@ -4356,70 +4380,70 @@
         <v>54</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="G76" s="15" t="s">
         <v>297</v>
-      </c>
-      <c r="G76" s="15" t="s">
-        <v>298</v>
       </c>
       <c r="H76"/>
     </row>
     <row r="77" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D77" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="G77" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="H77"/>
     </row>
     <row r="78" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="E78" s="16" t="s">
+      <c r="F78" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="G78" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="H78"/>
     </row>
     <row r="79" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>7</v>
@@ -4428,24 +4452,24 @@
         <v>46</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="G79" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>7</v>
@@ -4454,70 +4478,70 @@
         <v>47</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F80" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="G80" s="17" t="s">
         <v>316</v>
-      </c>
-      <c r="G80" s="17" t="s">
-        <v>317</v>
       </c>
       <c r="H80"/>
     </row>
     <row r="81" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F81" s="11" t="s">
+      <c r="G81" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="H81"/>
     </row>
     <row r="82" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B82" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F82" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F82" s="11" t="s">
+      <c r="G82" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="H82"/>
     </row>
     <row r="83" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>15</v>
@@ -4526,139 +4550,139 @@
         <v>47</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F83" s="11" t="s">
+      <c r="G83" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="H83"/>
     </row>
     <row r="84" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F84" s="11" t="s">
+      <c r="G84" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="H84"/>
     </row>
     <row r="85" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F85" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F85" s="11" t="s">
+      <c r="G85" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="H85"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="F86" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="G86" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="G87" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="G88" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>15</v>
@@ -4667,19 +4691,19 @@
         <v>47</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>15</v>
@@ -4688,44 +4712,44 @@
         <v>47</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F91" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="F91" s="7" t="s">
+      <c r="G91" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
@@ -4734,44 +4758,44 @@
         <v>46</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="F92" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="G92" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="F93" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="G93" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
@@ -4780,21 +4804,21 @@
         <v>47</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="F94" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>15</v>
@@ -4803,90 +4827,90 @@
         <v>47</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F95" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="G95" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G98" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>21</v>
@@ -4895,21 +4919,21 @@
         <v>47</v>
       </c>
       <c r="D99" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F99" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F99" s="7" t="s">
+      <c r="G99" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>13</v>
@@ -4918,90 +4942,90 @@
         <v>46</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="G100" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="F101" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="G101" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G102" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="F103" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="G103" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>13</v>
@@ -5010,21 +5034,21 @@
         <v>46</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="F104" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="G104" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>13</v>
@@ -5033,21 +5057,21 @@
         <v>46</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="F105" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="G105" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>7</v>
@@ -5056,21 +5080,21 @@
         <v>46</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>15</v>
@@ -5079,67 +5103,67 @@
         <v>47</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="F107" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F108" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F108" s="7" t="s">
+      <c r="G108" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F109" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F109" s="7" t="s">
+      <c r="G109" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>15</v>
@@ -5148,85 +5172,85 @@
         <v>47</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F111" s="7" t="s">
+      <c r="G111" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8525A1A-7D92-D448-9583-1ED95586C0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDE8EF8-D735-BE49-8EDC-7757B4E30543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="2880" windowWidth="27280" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="463">
   <si>
     <t>Villes</t>
   </si>
@@ -106,9 +106,6 @@
     <t>Métabolisme des acides aminés - Métabolisme de la créatine - Oxydation mitochondriale des acides gras</t>
   </si>
   <si>
-    <t>Hémoglobinopathies et biochimie du globule rouge (phénotype et génotype)</t>
-  </si>
-  <si>
     <t>Biochimie endocrine : axe gonadotrope et axe surrénalien (phénotype)</t>
   </si>
   <si>
@@ -172,27 +169,15 @@
     <t>recherche multidisciplinaire sur différents mécanismes pouvant favoriser la cancerogenèse, comme la reprogrammation métabolique dans les tumeurs neuroendocrines pancréatiques</t>
   </si>
   <si>
-    <t>LMBR/ CRMR Maladies du globule rouge (genotype et phenotype)</t>
-  </si>
-  <si>
-    <t>Laboratoire de Biochimie, CHU de Bordeaux</t>
-  </si>
-  <si>
     <t>julian.boutin@u-bordeaux.fr</t>
   </si>
   <si>
-    <t>Soin/Recherche</t>
-  </si>
-  <si>
     <t>Exploration et traitements innovants de la biosynthèse de l'hème et porphyries héréditaires</t>
   </si>
   <si>
     <t>INSERM U1312, Equipe BioGO, Laboratoire de Biochimie CHU Bordeaux</t>
   </si>
   <si>
-    <t>Emmanuel.richard@u-bordeaux.fr; jean-marc-blouin@u-bordeaux.fr</t>
-  </si>
-  <si>
     <t>Les porphyries sont des maladies héréditaires du métabolisme de l’hème. L’équipe du service de biochimie en lien avec le service de médecine interne (Hôpital Saint-André, Bordeaux) assure le diagnostic, le soin et la recherche (Equipe BioGO, physiopathologie et thérapeutique) pour ce groupe de maladies rares.</t>
   </si>
   <si>
@@ -211,9 +196,6 @@
     <t>Etude des vaisseaux au sein de l’unité neurovasculaire, aussi bien au cours du développement, que dans diverses pathologies neurovasculaires ou neurodégénératives (maladie des petits vaisseaux cérébraux, AVC, hypertension artérielle, maladie d’Alzheimer). Pour explorer les mécanismes physiopathologiques impliqués, l’équipe s’appuie sur une expertise reconnue dans le développement de modèles animaux. L’implication des voies de signalisation Wnt fait également partie des axes d’étude.</t>
   </si>
   <si>
-    <t>Génétique des Dystrophies rétiniennes héréditaires et des Surdités héréditaires </t>
-  </si>
-  <si>
     <t>Epigénomique des maladies neurodégénératives - Biomarqueurs circulants - Etude de cohortes </t>
   </si>
   <si>
@@ -223,9 +205,6 @@
     <t>Laboratoire de Biochimie, CHU de Lille</t>
   </si>
   <si>
-    <t>mariepierre.buisine@chu-lille.fr; pascal.pigny@chu-lille.fr </t>
-  </si>
-  <si>
     <t>Toulouse</t>
   </si>
   <si>
@@ -253,9 +232,6 @@
     <t>Etude des dysrégulations du métabolisme du tissu adipeux dans les lipodystrophies et l’obésité conduisant aux complications communes observées (résistance à l’insuline, stéatose hépatique…).</t>
   </si>
   <si>
-    <t>LBMR Marqueurs sériques maternels pour la prise en charge de la prééclampsie</t>
-  </si>
-  <si>
     <t>Laboratoire de Biochimie, CHU de Toulouse</t>
   </si>
   <si>
@@ -265,15 +241,9 @@
     <t>Expertise dans le dosage des marqueurs placentaires du 1er au 3ème trimestre de la grossesse, participation aux PHRC concernant la grossesse, mise en place d’une collection biologique et d’une base de données ciblées.</t>
   </si>
   <si>
-    <t>LBMR Maladies héréditaires du métabolisme (LBMR et CRMR)</t>
-  </si>
-  <si>
     <t>Exploration des métabolismes des acides aminés, des acides gras, des stérols, de l’hème, du lysosome, du peroxysome pour le diagnostic des déficits héréditaires de ces voies. Dosage des glycosaminoglycanes et oligosaccharides par LC-MS/MS, génétique moléculaire des maladies lysosomales</t>
   </si>
   <si>
-    <t>LBMR Biochimie du métabolisme osseux et phosphocalcique (phénotype et génotype)</t>
-  </si>
-  <si>
     <t>gennero.i@chu-toulouse.fr</t>
   </si>
   <si>
@@ -286,9 +256,6 @@
     <t>Des tests fonctionnels in vitro de variants nouvellement identifiés sont également en place permettant d’éclairer les mécanismes pathogéniques complexes. Deux niveaux d’expertise existent pour des mécanismes physiopathologiques associés à des nouveaux variants de gènes connus mais aussi à de nouveaux gènes récemment identifiés.</t>
   </si>
   <si>
-    <t>LBMR Cancer de la thyroïde</t>
-  </si>
-  <si>
     <t>Deux niveaux d’expertise existent pour l’étude des mécanismes physiopathologiques associés à de nouveaux variants de gènes connus mais aussi associés à de nouveaux gènes identifiés par approche exome. Des tests fonctionnels in vitro de variants nouvellement identifiés sont en place permettant d’éclairer les mécanismes pathogéniques complexes. Les cancers thyroïdiens familiaux peuvent être de souche folliculaire ou issus des cellules C.</t>
   </si>
   <si>
@@ -298,36 +265,21 @@
     <t>Nutrition-Genetique et exposition aux risques environnementaux</t>
   </si>
   <si>
-    <t>INSERM 1256, NGERE</t>
-  </si>
-  <si>
     <t>abderrahim.oussalah@univ-lorraine.fr; rosa-maria.rodriguez-gueant@univ-lorraine.fr; catherine.malaplate@univ-lorraine.fr, i.rotaru@chru-nancy.fr; bernard.namour@univ-lorraine.fr</t>
   </si>
   <si>
-    <t>LBMR Maladies héréditaires du métabolisme (phénotype et génotype)</t>
-  </si>
-  <si>
     <t>Laboratoire de Biochimie, CHU de Nancy</t>
   </si>
   <si>
     <t>abderrahim.oussalah@univ-lorraine.fr; rosa-maria.rodriguez-gueant@univ-lorraine.fr; i.rotaru@chru-nancy.fr; bernard.namour@univ-lorraine.fr</t>
   </si>
   <si>
-    <t>LBMR Explorations Biochimiques et Moléculaires des Pathologies Uro-néphrologiques</t>
-  </si>
-  <si>
     <t>abderrahim.oussalah@univ-lorraine.fr</t>
   </si>
   <si>
-    <t>LBMR Maladies neurodégénératives centrales: Alzheimer et démences apparentées, neuroinflammation</t>
-  </si>
-  <si>
     <t>c.malaplate@chru-nancy.fr</t>
   </si>
   <si>
-    <t>LBMR Médecine génomique : Diagnostic moléculaire par séquençage haut débit de l’exome clinique et analyse du méthylome</t>
-  </si>
-  <si>
     <t>Amiens</t>
   </si>
   <si>
@@ -367,9 +319,6 @@
     <t>Notre équipe se concentre sur l'élucidation des étapes clés du trafic intracellulaire et notamment de la morphogenèse du virus de l'immunodéficience humaine (VIH), des différents virus de l'hépatite (VHB, VHC, VHE), et des virus émergents</t>
   </si>
   <si>
-    <t>LBMR Maladies héréditaires du métabolisme (phénotype)</t>
-  </si>
-  <si>
     <t>Laboratoire de Biochimie, CHU de Tours</t>
   </si>
   <si>
@@ -379,21 +328,12 @@
     <t>Ce LBMR est spécialisé dans le diagnostic et le suivi des maladies métaboliques héréditaires, souvent rares et complexes, nécessitant une expertise multidisciplinaire. Il réalise notamment le dosage de marqueurs biochimiques spécifiques à l’aide de techniques de biochimie spécialisée. Les pathologies prises en charge incluent les aciduries organiques, les aminoacidopathies, les troubles du cycle de l’urée, ainsi que les déficits de la cétogenèse et de la cétolyse.</t>
   </si>
   <si>
-    <t>LBMR Marqueurs sériques maternels des grossesses pathologiques (phénotype) : prééclampsie</t>
-  </si>
-  <si>
     <t>piver_e@med.univ-tours.fr</t>
   </si>
   <si>
-    <t>LBMR Diagnostic génétique de la sclérose latérale amyotrophique</t>
-  </si>
-  <si>
     <t>patrick.vourch@univ-tours.fr</t>
   </si>
   <si>
-    <t>LBMR Diagnostic génétique des maladies vasculaires rares : lymphœdèmes et angiomes plans</t>
-  </si>
-  <si>
     <t>charlotte.veyratdurebex@univ-tours.fr</t>
   </si>
   <si>
@@ -401,9 +341,6 @@
   </si>
   <si>
     <t>Métabolomique et lipidomique clinique</t>
-  </si>
-  <si>
-    <t>aurelie.bedel@u-bordeaux.fr; julian.boutin@u-bordeaux.fr</t>
   </si>
   <si>
     <r>
@@ -822,9 +759,6 @@
     <t>Laboratoire de Biochimie</t>
   </si>
   <si>
-    <t>Le LBMR, Génétique Somatique : Cancers broncho-pulmonaire, digestif et mélanome, réalise l’analyse moléculaire de panels de gènes à visée théranostique ou pronostique dans les tumeur solides (y compris la recherche des transcrits de fusion et l’étude de l’ADN circulant).</t>
-  </si>
-  <si>
     <t>Equipe PROTECT, INSERM U 955 ; Institut Mondor de Recherche Biomédicale</t>
   </si>
   <si>
@@ -931,9 +865,6 @@
   </si>
   <si>
     <t>coulbault-l@chu-caen.fr</t>
-  </si>
-  <si>
-    <t>nalyses pour le suivi nutritionnel des patients des vitamines et éléments traces par des approches de chromatographie classique (LC), de LC-MS/MS et d’ICP-MS</t>
   </si>
   <si>
     <t>CHU Caen Biochimie métabolique</t>
@@ -1038,9 +969,6 @@
     <t>Toxicologie</t>
   </si>
   <si>
-    <t>prise en charge des intoxications au protoxyde d’azote</t>
-  </si>
-  <si>
     <t>CHU DIJON - Centre de Compétences PROTOSIDE (Plateformes et Réseaux pour l’Orientation, le Traitement et l’Organisation des Soins des Intoxications au N20, Diagnostic et Education)</t>
   </si>
   <si>
@@ -1068,9 +996,6 @@
     <t>https://www.gemeli-uga.fr/</t>
   </si>
   <si>
-    <t>Maladies Neuromusculaires</t>
-  </si>
-  <si>
     <t>CHU Grenoble - LBMR Maladies neuromusculaires</t>
   </si>
   <si>
@@ -1092,9 +1017,6 @@
     <t>Immunologie</t>
   </si>
   <si>
-    <t>Déficits immunitaires innés des phagocytes</t>
-  </si>
-  <si>
     <r>
       <t>mjstasia@chu-grenoble.fr</t>
     </r>
@@ -1745,9 +1667,6 @@
     <t>Marseille</t>
   </si>
   <si>
-    <t>Etudes des pathologies endocrines (hypophyse) et des lésions endocrines dépendantes (méningiomes). https://www.marseille-medical-genetics.org/fr/</t>
-  </si>
-  <si>
     <t>MMG Marseille Medical Genetics</t>
   </si>
   <si>
@@ -1769,9 +1688,6 @@
     <t>Le service GEnOPé (Génétique Endocrinienne, Oncologique et Pharmacogénétique) assure le diagnostic en génétique constitutionnelle des tumeurs fréquentes et de syndromes tumoraux rares, des pathologies endocriniennes rares, de l’hémochromatose et des surcharges en fer et en cuivre, des hypercholesterolémies, de la pharmacogénétique. Nous travaillons en interaction avec le CRMR HYPO (Maladies rares de l’Hypophyse, Marseille Pr Brue) et CEDRA (dyslipidemies rares, Marseille, Pr S Belliard)</t>
   </si>
   <si>
-    <t>Cardiovasculaire</t>
-  </si>
-  <si>
     <t>Physiopathologie des agressions et dysfonctions cardiaques</t>
   </si>
   <si>
@@ -1784,9 +1700,6 @@
     <t>Les travaux de l'équipe 5 du C2VN porte sur 2 axes : 1) le rôle du système adénosinergique en physiopathologie cardiovasculaire (syndrome coronarien chronique, syncope réflexe, fibrillation atriale) ; 2) les mécanismes de l'insuffisance cardiaque dans le contexte de myocardites induites par les immunothérapies anticancéreuses. Nos objectifs sont : 1) D'identifier de nouveaux biomarqueurs issus du système adénosinergique pour le dépistage et le suivi des maladies cardiovasculaires; 2) Identifier des biomarqueurs précoces et innovants des cardiotoxicités inuites par les thérapies anti-cancéreuses.</t>
   </si>
   <si>
-    <t>LBMR : Maladies héréditaires du métabolisme (phénotype) : métabolisme des acides aminés (aciduries organiques, aminocidopathies, cycle de l'urée, cétogenèse et cétolyse)</t>
-  </si>
-  <si>
     <t>Laboratoire de Biochimie Métabolique et de Biochimie Spécialisée - Hôpitaux Universitaires de Marseille</t>
   </si>
   <si>
@@ -1826,9 +1739,6 @@
     <t>L’Institut des Neurosciences  de Montpellier (INM) est une Unité Mixte de Recherche Inserm-Université de Montpellier. L'INM a pour objectif conduire une recherche fondamentale et translationnelle pour étudier le développement, la plasticité et l'intégration synaptique et les processus neurodégénératifs conduisant à des troubles du système central et sensori-moteur.</t>
   </si>
   <si>
-    <t>Mécanismes de la fonction musculaire dans des conditions de déficience d'organes ( insuffisance rénale). https://www.phymedexp.com/</t>
-  </si>
-  <si>
     <t>PhyMedExp : Physiologie et médecine expérimentale du cœur et des muscles (INSERM, CNRS, Université de Montpellier)</t>
   </si>
   <si>
@@ -1838,9 +1748,6 @@
     <t>PhyMedex est une Unité Mixte de Recherche CNRS-Inserm-Université de Montpellier qui a pour objectif la caractérisation des mécanismes moléculaires et cellulaires associés à la fonction musculaire dans différentes conditions de déficience d’organes dont l’insuffisance rénale chronique.</t>
   </si>
   <si>
-    <t>LBMR Maladies Neurodégénératives et Neuroinflammatoires</t>
-  </si>
-  <si>
     <t>LBMR : Laboratoire de Biochimie Protéomique clinique (LBPC)</t>
   </si>
   <si>
@@ -1862,9 +1769,6 @@
     <t>Néphrologie</t>
   </si>
   <si>
-    <t>LBMR Biochimie des pathologies rénales (phénotype)</t>
-  </si>
-  <si>
     <t>Les méthodes maîtrisées au laboratoire permettent de dépister et classifier les maladies rénales chroniques (MRC) (créatinine, albuminurie) mais aussi de répondre à des besoins diagnostics précis (cystatine, Iohexol, cristallurie, aminoacidopathies …). Le laboratoire explore les comorbidités associées à la MRC comme les cardiopathies, les myopathies urémiques et les désordres métaboliques et énergétiques.</t>
   </si>
   <si>
@@ -1883,27 +1787,18 @@
     <t>Les protéines subissent au cours de leur vie biologique des modifications dites non enzymatiques qui concourent à leur vieillissement moléculaire qui se traduit par une altération de leurs propriétés structurales et fonctionnelles. Les produits issus de ces modifications peuvent servir de biomarqueurs pour le suivi de la progression de maladies chroniques comme la maladie rénale chronique ou le diabète.</t>
   </si>
   <si>
-    <t>LBMR Marqueurs protéiques de diagnostic et suivi du diabète sucré</t>
-  </si>
-  <si>
     <t>CHU de Reims</t>
   </si>
   <si>
     <t>Notre laboratoire a développé une expertise pour les méthodes analytiques de dosage des produits de glycation des protéines par LC-MS/MS (HbA1c et AGEs) et fait partie du réseau international IFCC de laboratoires de référence pour le dosage de l’HbA1c.</t>
   </si>
   <si>
-    <t>LBMR Biochimie endocrine (phénotype) : axe surrénalien</t>
-  </si>
-  <si>
     <t>dmarot@chu-reims.fr</t>
   </si>
   <si>
     <t>Diagnostic étiologique du syndrome de Cushing ACTH-dépendant (adénome corticotrope ou sécrétion ectopique) ou ACTH-indépendant (hyperplasies bilatérales des surrénales, adénome surrénalien et le corticosurrénalome). Diagnostic de l'insuffisance surrénale. Membre du groupe Hormonologie FIRENDO.</t>
   </si>
   <si>
-    <t>Intérêt des molécules matricielles plasmatiques vésiculaires comme nouveau biomarqueur du cancer.</t>
-  </si>
-  <si>
     <t>UMR CNRS 7369 MEDyC – équipe 1</t>
   </si>
   <si>
@@ -1931,9 +1826,6 @@
     <t>Au sein de l’équipe NUMECAN équipe EXPRES le laboratoire participe en lien avec nos collègues rhumatologues et pneumologues à l’étude ciblée et non ciblée de liquides articulaires et pleuraux afin d’identifier de nouveaux biomarqueurs précoces d’infection</t>
   </si>
   <si>
-    <t>Biomarqueurs de l’ACLF : « acute on chronic liver failure »</t>
-  </si>
-  <si>
     <t>Au sein de l’equipe NUMECAN équipe EXPRES, nous étudions par des méthodes ciblées et non ciblées deux cohortes de patients à différents stades d’ACLF et ce de façon longitudinale afin d’améliorer le diagnostic et pronostic de cette pathologie hépatique grave, et aussi d’en identifier les ressorts physiopathologiques</t>
   </si>
   <si>
@@ -1961,9 +1853,6 @@
     <t>Nous investiguons rôle du facteur de transcription EMX2 dans la glioblastomagenèse en (1) recherchant le réseau génique qu’il module, les nœuds d’interaction convergents  et les surrogates associés spécifiquement à l’action antitumorale, (2) évaluant l’effet de EMX2 sur la survie in vivo, (3) décrivant les évolutions clonales des cellules tumorales en réponse à l’inhibition de l’UPR associée non à l’expression de EMX2.</t>
   </si>
   <si>
-    <t>Expression des gènes et oncogenèse : mélanome et  LAL B de l’enfant</t>
-  </si>
-  <si>
     <t>Institut de Génétique et Développement de Rennes, IGDR UMR 6290 CNRS, Université de Rennes, ERL Inserm U1305</t>
   </si>
   <si>
@@ -1985,9 +1874,6 @@
     <t>Notre équipe de recherche étudie les processus biologiques qui régissent la mise en place du cerveau au cours des premières étapes du développement en situation normale, et se concentre également sur les maladies rares du développement du système nerveux afin d’établir leurs causes et leurs conséquences au niveau moléculaire, cellulaire et organique.</t>
   </si>
   <si>
-    <t>LBMR Fer et surcharge en fer rares d’origine génétique </t>
-  </si>
-  <si>
     <t>CHU RENNES</t>
   </si>
   <si>
@@ -2018,15 +1904,9 @@
     <t>Notre laboratoire accompagne l’ensemble des activités du pôle Biologie du CHU de Rennes dans ses activités de bioinformatique à visée de soin. Il développe des approches d’intelligence artitificielle pour intégrer les données cliniques et biologiques et faciliter le travail des biologistes.</t>
   </si>
   <si>
-    <t>CCMR maladies héréditaires du métabolisme</t>
-  </si>
-  <si>
     <t>Le laboratoire réalise et développe une activité de diagnostic et suivi des maladies héréditaires du métabolisme pour lesquelles nous sommes actuellement centre de compétence avec l’ambition de monter centre de référence au prochain appel à candidature. Nous proposons en soins et recherche  les panels rédox et en spectrométrie de masse (Acides aminés, acyls carnitines, acides organiques) avec des approches </t>
   </si>
   <si>
-    <t>LBMR « Diagnostic génétique de l’holoprosencéphalie »</t>
-  </si>
-  <si>
     <t>christele.dubourg@chu-rennes.fr</t>
   </si>
   <si>
@@ -2048,9 +1928,6 @@
     <t>.</t>
   </si>
   <si>
-    <t>Centre</t>
-  </si>
-  <si>
     <t>site internet</t>
   </si>
   <si>
@@ -2063,9 +1940,6 @@
     <t>Grossesse et néonatalogie</t>
   </si>
   <si>
-    <t>LBMR Anomalies du développement et de la fonction thyroïdienne</t>
-  </si>
-  <si>
     <t>Médecine moléculaire, génétique</t>
   </si>
   <si>
@@ -2084,60 +1958,27 @@
     <t>Etude du métabolisme dans les lésions rénales aiguës </t>
   </si>
   <si>
-    <t>LBMR Pharmacogénétique</t>
-  </si>
-  <si>
     <t>Notre expertise en pharmacogénomique nous permet de répondre à la problématique de la résistance et de la toxicité d’agents anticancéreux, d’immunosuppresseurs, et de psychotropes notamment, avec une offre combinée de tests génétiques et de phénotypage unique en France. 1. Pharmacogénétique des antiviraux, des immunosuppresseurs et des antithrombotiques (CYP2B6, CYP2C9, CYP2C19, CYP3A4, CYP3A5, TPMT, VKORC1) ; 2. Dosage intraérythrocytaire des métabolites de l'azathioprine ; 3. Pharmacogénétique des anticancéreux (DPD, TPMT) </t>
   </si>
   <si>
     <t>Génétique somatique, ADN tumoral circulant, théranostique et Pharmacogénétique</t>
   </si>
   <si>
-    <t>Cochin</t>
-  </si>
-  <si>
     <t>Vulnérabilité génétique et épigénétique aux troubles psychiatriques</t>
   </si>
   <si>
-    <t>Diagnostic génétique des myopathies des ceintures (LBMR)</t>
-  </si>
-  <si>
     <t>Ophtalmologie</t>
   </si>
   <si>
     <t>Bases moléculaires et physiopathologie des maladies ophtalmologiques de la cornée à la rétine : approche NGS et séquençage du génôme </t>
   </si>
   <si>
-    <t>Métabolisme </t>
-  </si>
-  <si>
     <t>Bases moléculaires et physiopathologie des amyloses héréditaires</t>
   </si>
   <si>
-    <t>Diagnostic prénatal non invasif des maladies monogéniques (DPNI-MM)(LBMR)</t>
-  </si>
-  <si>
-    <t>Inflammation; génétique</t>
-  </si>
-  <si>
-    <t>Diagnostic génétique des maladies auto-inflammatoires (LBMR)</t>
-  </si>
-  <si>
-    <t>Bobigny</t>
-  </si>
-  <si>
     <t>Marqueurs biologiques associés à la progression de la Leucémie lymphoïde Chronique</t>
   </si>
   <si>
-    <t>Carcinome épidermoïde cutané (CEC) : caractérisation moléculaire de formes rares et marqueurs associés à une réponse à l’immunothérapie</t>
-  </si>
-  <si>
-    <t>Génétique somatique des tumeurs</t>
-  </si>
-  <si>
-    <t>Mondor</t>
-  </si>
-  <si>
     <t>Etude des Atteintes cardiaques et circulatoires</t>
   </si>
   <si>
@@ -2153,12 +1994,6 @@
     <t>Exploration et la mise en place de biomarqueurs inflammatoires, métaboliques et urinaires dans des pathologies métabolique</t>
   </si>
   <si>
-    <t>Bichat</t>
-  </si>
-  <si>
-    <t>Fer, Heme et Pathologies de surcharge et Anémies rares</t>
-  </si>
-  <si>
     <t>Biologie Intégrée du Globule Rouge et de l’Erythropoïèse ( BIGR)- UMRS 1134- Université Paris Cité – INSERM – EFS</t>
   </si>
   <si>
@@ -2168,21 +2003,12 @@
     <t>Nous explorons les mécanismes de l’érythropoïèse ainsi que le métabolisme du fer et de l’hème, en physiologie comme en pathologie. Notre expertise s’inscrit dans l’étude et la prise en charge des maladies rares du sang, notamment les différentes formes d’anémies. À travers recherche et innovation, nous faisons avancer la compréhension des pathologies hématologiques rares.</t>
   </si>
   <si>
-    <t>LBMR Anomalies Congénitales de la Glycosylation</t>
-  </si>
-  <si>
     <t>Laboratiore de Biochimie de Bichat</t>
   </si>
   <si>
-    <t>arnaud.bruneel@aphp.fr; https://www.cdg-bichat.com/</t>
-  </si>
-  <si>
     <t>Le CDG-Bichat est un centre d’expertise spécialisé dans le diagnostic des troubles congénitaux de la glycosylation (CDG), le dosage du sorbitol et de la ferritine glycosylée. Basé à l’Hôpital Bichat et en collaboration avec l’Université Paris-Saclay et Paris Cité, il développe des analyses biochimiques avancées pour le diagnostic, le suivi et la recherche sur les maladies métaboliques rares.</t>
   </si>
   <si>
-    <t>LBMR Maladies héréditaires du métabolisme (phénotype et génotype) : métabolisme des métaux (Fer)</t>
-  </si>
-  <si>
     <t>katell.peoch@aphp.fr</t>
   </si>
   <si>
@@ -2192,9 +2018,6 @@
     <t>Clermont-Ferrand </t>
   </si>
   <si>
-    <t>Recherche translationnelle </t>
-  </si>
-  <si>
     <t>La thématique centrale de l’équipe est de comprendre les mécanismes cellulaires et moléculaires de l’agression épithéliale appliquée à des pathologiques courantes afin d’en optimiser le diagnostic, le pronostic et la thérapeutique. </t>
   </si>
   <si>
@@ -2237,22 +2060,214 @@
     <t>Dosage des stérols plasmatiques (cholestanol, 7-déhydrocholestérol et phytostérols) par GC-MS à visée diagnostique de la xanthomatose cérébrotendineuse, du syndrome de Smith-Lemli-Opitz et des phytostérolémies.  </t>
   </si>
   <si>
-    <t>Pseudo Obstruction Intestinale Chronique </t>
-  </si>
-  <si>
     <t>CHU Grenoble - LBMR Déficits immunitaires innés des phagocytes</t>
   </si>
   <si>
-    <t>Troubles comportementaux alimentaires (TCA) </t>
-  </si>
-  <si>
     <t>Notre laboratoire réalise les explorations phénotypiques des anomalies de l’hémoglobine et d’autres pathologies du globule rouge telles que les déficits enzymatiques dans le cadre de la Filière MCGRE avec le centre de compétence des syndromes drépanocytaires majeurs, thalassémies et autres pathologies rares du globule rouge et de l’érythropoïèse. </t>
   </si>
   <si>
-    <t>Muscles; nephrologie</t>
-  </si>
-  <si>
     <t>Hépato-Gastro-Entérologie</t>
+  </si>
+  <si>
+    <t>Translationnel</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Pellegrin</t>
+  </si>
+  <si>
+    <t>Campus Carreire</t>
+  </si>
+  <si>
+    <t>Haut-Lévèque</t>
+  </si>
+  <si>
+    <t>Cochin - Port Royal</t>
+  </si>
+  <si>
+    <t>Avicenne</t>
+  </si>
+  <si>
+    <t>Henri-Mondor</t>
+  </si>
+  <si>
+    <t>Bichat - Claude-Bernard</t>
+  </si>
+  <si>
+    <t>Service de Biochimie, CHU de Bordeaux</t>
+  </si>
+  <si>
+    <t>aurelie.bedel@u-bordeaux.fr ; julian.boutin@u-bordeaux.fr</t>
+  </si>
+  <si>
+    <t>Servcie de Biochimie, CHU de Bordeaux</t>
+  </si>
+  <si>
+    <t>mariepierre.buisine@chu-lille.fr ; pascal.pigny@chu-lille.fr </t>
+  </si>
+  <si>
+    <t>https://www.chu-bordeaux.fr/Patient-proches/Maladies-rares/Centre-de-r%C3%A9f%C3%A9rence-des-porphyries-et-an%C3%A9mies-rares-du-m%C3%A9tabolisme-du-fer/</t>
+  </si>
+  <si>
+    <t>emmanuel.richard@u-bordeaux.fr ; jean-marc-blouin@u-bordeaux.fr</t>
+  </si>
+  <si>
+    <t>INSERM UMR1256, NGERE</t>
+  </si>
+  <si>
+    <t>Fer, Hème et Pathologies de surcharge et Anémies rares</t>
+  </si>
+  <si>
+    <t>arnaud.bruneel@aphp.fr</t>
+  </si>
+  <si>
+    <t>https://www.cdg-bichat.com/</t>
+  </si>
+  <si>
+    <t>LMBR/CRMR - Maladies du globule rouge (genotype et phenotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Biochimie du métabolisme osseux et phosphocalcique (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Anomalies du développement et de la fonction thyroïdienne</t>
+  </si>
+  <si>
+    <t>LBMR - Cancer de la thyroïde</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies héréditaires du métabolisme (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Explorations Biochimiques et Moléculaires des Pathologies Uro-néphrologiques</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies neurodégénératives centrales: Alzheimer et démences apparentées, neuroinflammation</t>
+  </si>
+  <si>
+    <t>LBMR - Médecine génomique : Diagnostic moléculaire par séquençage haut débit de l’exome clinique et analyse du méthylome</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies héréditaires du métabolisme (phénotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Marqueurs sériques maternels des grossesses pathologiques (phénotype) : prééclampsie</t>
+  </si>
+  <si>
+    <t>LBMR - Diagnostic génétique de la sclérose latérale amyotrophique</t>
+  </si>
+  <si>
+    <t>LBMR - Diagnostic génétique des maladies vasculaires rares : lymphœdèmes et angiomes plans</t>
+  </si>
+  <si>
+    <t>LBMR - Diagnostic génétique des myopathies des ceintures</t>
+  </si>
+  <si>
+    <t>LBMR - Diagnostic prénatal non invasif des maladies monogéniques (DPNI-MM)</t>
+  </si>
+  <si>
+    <t>LBMR - Diagnostic génétique des maladies auto-inflammatoires</t>
+  </si>
+  <si>
+    <t>Carcinome épidermoïde cutané : caractérisation moléculaire de formes rares et marqueurs associés à une réponse à l’immunothérapie</t>
+  </si>
+  <si>
+    <t>LBMR - Anomalies Congénitales de la Glycosylation</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies héréditaires du métabolisme (phénotype et génotype) : métabolisme des métaux (Fer)</t>
+  </si>
+  <si>
+    <t>Troubles comportementaux alimentaires</t>
+  </si>
+  <si>
+    <t>Etudes des pathologies endocrines (hypophyse) et des lésions endocrines dépendantes (méningiomes)</t>
+  </si>
+  <si>
+    <t>https://www.marseille-medical-genetics.org/fr/</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies héréditaires du métabolisme (phénotype) : métabolisme des acides aminés (aciduries organiques, aminocidopathies, cycle de l'urée, cétogenèse et cétolyse)</t>
+  </si>
+  <si>
+    <t>Mécanismes de la fonction musculaire dans des conditions de déficience d'organes (insuffisance rénale)</t>
+  </si>
+  <si>
+    <t>https://www.phymedexp.com/</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies Neurodégénératives et Neuroinflammatoires</t>
+  </si>
+  <si>
+    <t>LBMR - Biochimie des pathologies rénales (phénotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Marqueurs protéiques de diagnostic et suivi du diabète sucré</t>
+  </si>
+  <si>
+    <t>LBMR - Biochimie endocrine (phénotype) : axe surrénalien</t>
+  </si>
+  <si>
+    <t>Intérêt des molécules matricielles plasmatiques vésiculaires comme nouveau biomarqueur du cancer</t>
+  </si>
+  <si>
+    <t>Biomarqueurs de l’ACLF : « acute-on-chronic liver failure »</t>
+  </si>
+  <si>
+    <t>LBMR - Fer et surcharge en fer rares d’origine génétique </t>
+  </si>
+  <si>
+    <t>CCMR - Maladies héréditaires du métabolisme</t>
+  </si>
+  <si>
+    <t>LBMR - « Diagnostic génétique de l’holoprosencéphalie »</t>
+  </si>
+  <si>
+    <t>LBMR - Génétique des Dystrophies rétiniennes héréditaires et des Surdités héréditaires </t>
+  </si>
+  <si>
+    <t>LBMR - Hémoglobinopathies et biochimie du globule rouge (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>LBMR - Marqueurs sériques maternels pour la prise en charge de la prééclampsie</t>
+  </si>
+  <si>
+    <t>LBMR/CRMR - Maladies héréditaires du métabolisme</t>
+  </si>
+  <si>
+    <t>LBMR - Pharmacogénétique</t>
+  </si>
+  <si>
+    <t>LBMR - Génétique somatique des tumeurs</t>
+  </si>
+  <si>
+    <t>Le LBMR Génétique Somatique : Cancers broncho-pulmonaire, digestif et mélanome, réalise l’analyse moléculaire de panels de gènes à visée théranostique ou pronostique dans les tumeur solides (y compris la recherche des transcrits de fusion et l’étude de l’ADN circulant).</t>
+  </si>
+  <si>
+    <t>Prise en charge des intoxications au protoxyde d’azote</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies Neuromusculaires</t>
+  </si>
+  <si>
+    <t>LBMR - Pseudo Obstruction Intestinale Chronique </t>
+  </si>
+  <si>
+    <t>LBMR - Déficits immunitaires innés des phagocytes</t>
+  </si>
+  <si>
+    <t>Expression des gènes et oncogenèse : mélanome et LAL B de l’enfant</t>
+  </si>
+  <si>
+    <t>Génétique</t>
+  </si>
+  <si>
+    <t>Analyses pour le suivi nutritionnel des patients des vitamines et éléments traces par des approches de chromatographie classique (LC), de LC-MS/MS et d’ICP-MS</t>
+  </si>
+  <si>
+    <t>Myologie</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2411,6 +2426,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
@@ -2629,13 +2645,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1"/>
     <col min="2" max="2" width="18" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="4" customWidth="1"/>
-    <col min="4" max="4" width="88.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="4" customWidth="1"/>
     <col min="5" max="5" width="55.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="79.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="213" style="4" bestFit="1" customWidth="1"/>
@@ -2643,18 +2659,18 @@
     <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -2669,70 +2685,87 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>390</v>
+        <v>349</v>
       </c>
       <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>398</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>405</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>398</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>56</v>
+        <v>410</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>409</v>
+      </c>
       <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
@@ -2741,69 +2774,82 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>127</v>
+        <v>406</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>398</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>407</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2812,10 +2858,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>448</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -2828,8 +2874,11 @@
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2838,10 +2887,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
@@ -2854,8 +2903,11 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2864,24 +2916,27 @@
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2890,24 +2945,27 @@
         <v>13</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -2916,24 +2974,27 @@
         <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2942,24 +3003,27 @@
         <v>13</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -2968,24 +3032,27 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>67</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2994,24 +3061,27 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -3020,24 +3090,27 @@
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -3046,2791 +3119,3119 @@
         <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>28</v>
+        <v>449</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>451</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>88</v>
+        <v>418</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>92</v>
+        <v>411</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>94</v>
+        <v>419</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>97</v>
+        <v>420</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>99</v>
+        <v>421</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>101</v>
+        <v>422</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>397</v>
+        <v>355</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="H33" s="8" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>115</v>
+        <v>423</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>119</v>
+        <v>424</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>121</v>
+        <v>425</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>123</v>
+        <v>426</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>153</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G42" s="6"/>
       <c r="H42" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I42" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>399</v>
+        <v>357</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>400</v>
+        <v>358</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>401</v>
+        <v>452</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>402</v>
+        <v>359</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>409</v>
+        <v>15</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>415</v>
+        <v>365</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>185</v>
+        <v>454</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>296</v>
+        <v>354</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>422</v>
+        <v>369</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>409</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>409</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>426</v>
+        <v>371</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>427</v>
+        <v>372</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>428</v>
+        <v>373</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>409</v>
+        <v>15</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="H62" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5" t="s">
-        <v>434</v>
+        <v>376</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>437</v>
+        <v>177</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>438</v>
+        <v>379</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>439</v>
+        <v>380</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+    </row>
+    <row r="66" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>443</v>
+        <v>384</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E69" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="I69" s="12"/>
+      <c r="J69" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="I69" s="11"/>
-      <c r="J69" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="I70" s="11"/>
-      <c r="J70" s="12"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="5"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="I71" s="11"/>
-      <c r="J71" s="12"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+      <c r="I71" s="12"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>449</v>
+        <v>390</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="1"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>222</v>
+        <v>461</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>242</v>
+        <v>455</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>252</v>
+        <v>456</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>53</v>
+        <v>396</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>260</v>
+        <v>458</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>455</v>
+        <v>394</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>288</v>
+        <v>434</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I91" s="1"/>
+        <v>264</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>435</v>
+      </c>
       <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>301</v>
+        <v>436</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>315</v>
+        <v>437</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I98" s="1"/>
+        <v>288</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>438</v>
+      </c>
       <c r="J98" s="1"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>319</v>
+        <v>439</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>115</v>
+        <v>423</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>327</v>
+        <v>440</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>334</v>
+        <v>441</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>337</v>
+        <v>442</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>340</v>
+        <v>443</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>457</v>
+        <v>395</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>360</v>
+        <v>459</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>362</v>
+        <v>325</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>368</v>
+        <v>445</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>378</v>
+        <v>340</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>379</v>
+        <v>446</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="11">
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="E69:E71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
     <mergeCell ref="I69:I71"/>
     <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{E2AE3D23-6BA8-F34A-9DEA-6792A31781C2}"/>
-    <hyperlink ref="G4" r:id="rId2" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{B046796F-8285-C042-BA7C-378FB72DBFF6}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{B873E00A-CB89-9143-903F-7234C0F6DEBA}"/>
-    <hyperlink ref="G5" r:id="rId4" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{8307A68A-5A3E-514A-985E-86E0E3D83B11}"/>
-    <hyperlink ref="G6" r:id="rId5" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{2B67929A-558E-1342-8FEC-7BD06CEF2CB0}"/>
-    <hyperlink ref="G7" r:id="rId6" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{C7781EFB-60AA-1148-B807-45B79F7BA528}"/>
-    <hyperlink ref="G8" r:id="rId7" display="mailto:vincent.huin@inserm.fr" xr:uid="{C8FAC5A2-B67E-5F44-A3DB-7DF398848BBE}"/>
-    <hyperlink ref="G9" r:id="rId8" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{361D0882-1818-7E49-8F40-C423E6E1AA1E}"/>
-    <hyperlink ref="G10" r:id="rId9" display="mailto:julie.leclerc@inserm.fr" xr:uid="{66409AD5-E8A9-6D4A-A598-1542216AE9C4}"/>
-    <hyperlink ref="G11" r:id="rId10" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{76BFAD84-4846-0B4F-A8BF-CE61A027400B}"/>
-    <hyperlink ref="G12" r:id="rId11" display="mailto:lucie.coppin@inserm.fr" xr:uid="{19323FB7-E02E-5741-815E-02F6169B6C8B}"/>
-    <hyperlink ref="G14" r:id="rId12" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{620935CF-1F71-CC49-9355-F18607FAB693}"/>
-    <hyperlink ref="G17" r:id="rId13" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{350B585D-A5A2-CD4B-AF65-F9A732909942}"/>
-    <hyperlink ref="G18" r:id="rId14" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{2922E47A-23EF-504B-9D81-0F856449FF89}"/>
-    <hyperlink ref="G20" r:id="rId15" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{2A19B0EB-F9D2-4444-840B-4BC4409413A6}"/>
-    <hyperlink ref="G22" r:id="rId16" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{EEAD9112-B860-3240-BBB7-497068B112BC}"/>
-    <hyperlink ref="G23" r:id="rId17" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{2B61C5C2-6EAB-4E46-B941-4385F6A87230}"/>
-    <hyperlink ref="G24" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{39A72696-2727-DF44-9BA4-5FADE910636B}"/>
-    <hyperlink ref="G27" r:id="rId19" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{2D993324-F563-C449-8264-E62048F725A0}"/>
-    <hyperlink ref="G28" r:id="rId20" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{568F19CD-2BE7-A947-BDC1-B9F6350AA000}"/>
-    <hyperlink ref="G29" r:id="rId21" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{2D331CD7-9D55-634E-BCD9-4E5828427367}"/>
-    <hyperlink ref="G30" r:id="rId22" display="mailto:said.kamel@u-picardie.fr" xr:uid="{024ACFC2-9171-A042-8020-53031B3C3854}"/>
-    <hyperlink ref="G31" r:id="rId23" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{20B780FA-7480-D243-AA07-B4D807B06742}"/>
-    <hyperlink ref="G35" r:id="rId24" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{2663B759-A798-F14D-8845-6E62B4E7C785}"/>
-    <hyperlink ref="G36" r:id="rId25" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{80D7EC3E-09C9-9F4D-8807-5655DC565EC9}"/>
-    <hyperlink ref="G37" r:id="rId26" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{9841F99F-BC55-C343-ACC5-79A5BAE27BD0}"/>
-    <hyperlink ref="G39" r:id="rId27" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{7D433C7C-0034-5540-BAFA-77F4294738DE}"/>
-    <hyperlink ref="G40" r:id="rId28" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{74C38D93-291C-434C-A0F0-2B14E0ECD728}"/>
-    <hyperlink ref="G41" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{59222B18-B84A-3F41-887F-58666D26FF3E}"/>
-    <hyperlink ref="G42" r:id="rId30" xr:uid="{7A7ABE83-F3AC-CE44-8694-E441111C263B}"/>
-    <hyperlink ref="G43" r:id="rId31" display="mailto:helene.blons@aphp.fr" xr:uid="{4E097BEB-3253-114F-B1E5-DDA5AF02F6E6}"/>
-    <hyperlink ref="G44" r:id="rId32" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{7D6DF553-7336-B146-9E84-4D00B16863E8}"/>
-    <hyperlink ref="G45" r:id="rId33" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{2D35E462-DF86-6947-A95D-983EF7874952}"/>
-    <hyperlink ref="G46" r:id="rId34" display="mailto:helene.blons@aphp.fr" xr:uid="{6AFF6A5B-81A0-CD40-87B2-719B04A81516}"/>
-    <hyperlink ref="G49" r:id="rId35" display="mailto:sophie.valleix@aphp.fr" xr:uid="{0F777091-C2A7-6D47-8ABA-E5C4875429A5}"/>
-    <hyperlink ref="G50" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{894BC5E6-87AE-9648-A070-E69249853246}"/>
-    <hyperlink ref="G52" r:id="rId37" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{315923FD-C93C-A545-BD55-B9C717E2A895}"/>
-    <hyperlink ref="G56" r:id="rId38" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{7A4F2CE2-E80D-3743-89AD-9597BB8E2856}"/>
-    <hyperlink ref="G57" r:id="rId39" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{98DE53AE-18C2-EC40-AE8A-B6BF3301A944}"/>
-    <hyperlink ref="G59" r:id="rId40" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{751D8271-7D29-3640-A4AA-F8F903B9A243}"/>
-    <hyperlink ref="G60" r:id="rId41" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{FD017AF9-CC90-DA4B-8B7F-C89F525B5983}"/>
-    <hyperlink ref="G61" r:id="rId42" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{51322BB8-C401-7147-9D7A-51D50B1414AF}"/>
-    <hyperlink ref="G62" r:id="rId43" display="mailto:arnaud.bruneel@aphp.fr; https://www.cdg-bichat.com/" xr:uid="{0F9FE9EB-EF35-0F49-808D-95158AB3670D}"/>
-    <hyperlink ref="G63" r:id="rId44" display="mailto:katell.peoch@aphp.fr" xr:uid="{24EE0FC3-FF00-1D47-A2A4-09600A797BAD}"/>
-    <hyperlink ref="J64" r:id="rId45" xr:uid="{ECAE20F2-852E-FB4A-A02A-FF31F4887486}"/>
-    <hyperlink ref="G65" r:id="rId46" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{B5DB4A9B-922B-284A-B0C3-B5DF1422ED86}"/>
-    <hyperlink ref="J65" r:id="rId47" xr:uid="{55E53692-D3AC-CA48-AEF4-1616EECA1C3D}"/>
-    <hyperlink ref="G66" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{B9DF2BED-F0A3-8F47-9EFB-44529565F667}"/>
-    <hyperlink ref="G67" r:id="rId49" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{11EBED8C-36DE-A748-85C5-CBB2CE530861}"/>
-    <hyperlink ref="G68" r:id="rId50" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{AD34203C-7D5C-8B4C-8867-D2108B144DFC}"/>
-    <hyperlink ref="J68" r:id="rId51" xr:uid="{F6C97433-EDE7-504A-BEE9-BB1260634179}"/>
-    <hyperlink ref="G69" r:id="rId52" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{6B11DE33-AFD2-7D46-A3DC-A196675CF879}"/>
-    <hyperlink ref="J69" r:id="rId53" xr:uid="{F84C8866-445D-9F44-A250-B12EE0EFEF5F}"/>
-    <hyperlink ref="G72" r:id="rId54" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{F6A56745-858A-6841-B22F-45A9F35D5EFE}"/>
-    <hyperlink ref="G73" r:id="rId55" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{BF4DB8E8-138B-3B49-92E3-CA21179AB0B8}"/>
-    <hyperlink ref="G74" r:id="rId56" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{C6C73372-4951-A644-8526-21097969C789}"/>
-    <hyperlink ref="J75" r:id="rId57" xr:uid="{EF26A033-D812-8E42-B572-5A3EEB864ABA}"/>
-    <hyperlink ref="J76" r:id="rId58" xr:uid="{984D35B9-555F-8849-BD22-6526F37C6721}"/>
-    <hyperlink ref="G78" r:id="rId59" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{101C4579-7EA3-0C44-85ED-B322DC607AD2}"/>
-    <hyperlink ref="G80" r:id="rId60" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{B7DF53EB-B569-7546-AA03-3E88C4D0A97C}"/>
-    <hyperlink ref="J80" r:id="rId61" xr:uid="{8389F68B-B274-B34C-8C44-9E79069400E8}"/>
-    <hyperlink ref="G81" r:id="rId62" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{E9F05570-7FEC-7840-B6D6-02D683EA50E8}"/>
-    <hyperlink ref="G82" r:id="rId63" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{BD12F029-7313-AB4C-BBFF-CFE0445ADA63}"/>
-    <hyperlink ref="J84" r:id="rId64" xr:uid="{F0194297-4E1B-814E-8DAD-689C8D2F28E4}"/>
-    <hyperlink ref="G91" r:id="rId65" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{58A3B5BF-DE31-0643-88F8-B94E6EB4501C}"/>
-    <hyperlink ref="G92" r:id="rId66" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{D675EE75-417F-9547-8106-8D8F818B860E}"/>
-    <hyperlink ref="G93" r:id="rId67" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{00D4A746-B9FB-A14D-8035-253DCF0B7CD4}"/>
-    <hyperlink ref="G96" r:id="rId68" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{80DA09CF-F9E6-1E41-8CC8-04C5B78271CC}"/>
-    <hyperlink ref="G97" r:id="rId69" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{5C78EF7D-DB8C-B240-8BF0-86DD14CAB297}"/>
-    <hyperlink ref="G98" r:id="rId70" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{728A9D68-4D0F-6A44-AFBF-A20360539120}"/>
-    <hyperlink ref="G99" r:id="rId71" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{66712564-10C5-CC4E-9792-9994751E2786}"/>
-    <hyperlink ref="G100" r:id="rId72" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{ABDA347E-2B17-914C-A2E6-D93410A99F14}"/>
-    <hyperlink ref="G101" r:id="rId73" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{F025E27C-F226-7B41-A4CB-B3FD49405F0E}"/>
-    <hyperlink ref="G102" r:id="rId74" display="mailto:sjaisson@chu-reims.fr" xr:uid="{56F58EC2-715E-764A-AC49-280A2D870DC2}"/>
-    <hyperlink ref="G103" r:id="rId75" display="mailto:sjaisson@chu-reims.fr" xr:uid="{BDACB92A-25FA-7040-B97F-2BDC713770DA}"/>
-    <hyperlink ref="G104" r:id="rId76" display="mailto:dmarot@chu-reims.fr" xr:uid="{B5153EA2-5DD5-2240-BA68-705489C05FEA}"/>
-    <hyperlink ref="G105" r:id="rId77" display="mailto:lramont@chu-reims.fr" xr:uid="{45D74875-9324-004F-863A-39B8A70BAF1A}"/>
-    <hyperlink ref="G106" r:id="rId78" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{4F3C77F7-AED6-A04D-B319-68359C3B40B8}"/>
-    <hyperlink ref="G107" r:id="rId79" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{C3586ED5-B8C2-F845-887C-BDDD59B35057}"/>
-    <hyperlink ref="G108" r:id="rId80" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{342633B6-24F7-C845-BE79-CDA6222043CE}"/>
-    <hyperlink ref="G109" r:id="rId81" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{A6478EC5-7E18-304F-B28A-CBFA5B8419B5}"/>
-    <hyperlink ref="G110" r:id="rId82" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{BB5FAB08-EA83-F747-A281-D324A651E02D}"/>
-    <hyperlink ref="G113" r:id="rId83" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{7BA9BB8D-1B06-0045-B7F5-B3C7F2BAFD24}"/>
-    <hyperlink ref="G114" r:id="rId84" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{D9ED31AB-8E8C-1F47-BD82-2748EE64BF19}"/>
-    <hyperlink ref="G115" r:id="rId85" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{FA336397-0A92-3342-B961-17EC1130E45D}"/>
-    <hyperlink ref="G116" r:id="rId86" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{AA91B48B-0C5A-FB4E-9C4C-E4DC6A24BFD7}"/>
-    <hyperlink ref="G117" r:id="rId87" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{34A3B964-9C9D-BC4D-B4D1-6B08D090BD3A}"/>
-    <hyperlink ref="G118" r:id="rId88" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{C31F2741-EC2B-EE46-978C-2103BD8925CE}"/>
+    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{BECE8CF2-0490-7A47-9A41-0656A1077714}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{05DEBDEA-5744-E141-B21D-44ED99EA85AE}"/>
+    <hyperlink ref="G4" r:id="rId3" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{10E18B9C-36CA-AE46-9FFD-57FA6E67F38F}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{F63A4C3A-4CDB-C341-B7A6-7C74A40F7AB8}"/>
+    <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{67A962E2-668C-5344-94E4-1EC6DFEF8203}"/>
+    <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{1B41749A-CB5C-2546-BD08-6B758F14D101}"/>
+    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{65E7FD78-21C5-B847-990E-2DAD69A49EDA}"/>
+    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{9334F2AD-3318-9847-8A3D-C10C40F2E23D}"/>
+    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{40D0837F-8AA9-834C-ADEB-1A0A14FC66C1}"/>
+    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{0AC9D3DF-B4EE-2B47-A362-010CF44183EC}"/>
+    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{BDB9F7EF-DEB7-F946-AC4D-08E94CAF4009}"/>
+    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{8247C51A-C026-4047-9245-17A62FF1BFEA}"/>
+    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{347627A6-1668-A245-9EB9-CE0C0ADB782D}"/>
+    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{CA35FB74-B96C-3C4B-9596-88338397D323}"/>
+    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{DE45C52D-1690-C945-83E3-11C09373AFA9}"/>
+    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{2C8EF82B-A37E-6047-B8DB-221BF9CD112F}"/>
+    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{12085339-E0D9-7F45-8415-24991C29B496}"/>
+    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{84D3A1A7-7B69-B645-957F-92ACA9F98788}"/>
+    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{5A5DA6BD-9E05-5B48-AEF8-8FC5F4400BDE}"/>
+    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{C10E2064-438B-4245-9762-755A08F9D065}"/>
+    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{FE31F27F-3506-E346-A7B0-4DBC0276054C}"/>
+    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{0E016276-8CBE-7441-AC14-E6EA01963935}"/>
+    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{334E7D4B-467B-CF40-B676-E72B2880B411}"/>
+    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{3B35314F-5901-6641-AFB2-A849DA1A5DA9}"/>
+    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{A359737B-E389-464B-BA8E-996224AFC809}"/>
+    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{55F1D805-500A-7D4C-8952-79F133BE35BF}"/>
+    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{D8321FC6-227D-B14E-A3CB-FD9256AE0E50}"/>
+    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{38D65A69-06F4-2240-AD73-335CE3B1CE3E}"/>
+    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{54F44914-6520-B348-A07E-A4F879073C5A}"/>
+    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{B8C43AAB-9CE5-0447-A4BB-0BC6E01215AD}"/>
+    <hyperlink ref="I42" r:id="rId31" xr:uid="{98E9E07F-5CFD-9548-838F-CDDA799C9D4D}"/>
+    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{EE9BC22F-DBA7-AC43-B88C-04AC69DB03F5}"/>
+    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{17BD6FA3-1BAF-6D48-A68C-ABFE77468836}"/>
+    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{E7357D05-2B7E-3642-9F5C-9C7F3141D354}"/>
+    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{210898B7-070A-B249-B3D3-5F87EC0ABEED}"/>
+    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{DB74F793-0FB2-DA42-B877-3E3A44B990D5}"/>
+    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{403F2DD4-9E41-A94D-BFBF-6E21F77269C3}"/>
+    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{0EF8D8AF-4FDF-9A4F-A969-686A257BD73E}"/>
+    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{147B1B47-0285-B04D-B523-F2657D64678F}"/>
+    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{B7F4C06C-8ED5-F04C-A01C-E45AC877D38D}"/>
+    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{9FE6EE95-03B4-A54F-A54D-44FE95CC36B7}"/>
+    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{6F81145E-B562-424F-8619-9FAB035CEE9E}"/>
+    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{FA6E2218-5A07-464F-9A1C-D2E4083E90CC}"/>
+    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{282EB162-951C-6B44-A265-9541E44E7A2E}"/>
+    <hyperlink ref="I62" r:id="rId45" xr:uid="{C99CC80F-D1D1-BE43-987A-CEF2049DCE1D}"/>
+    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{D519D47B-1838-2346-AC56-DD3E6815BAC6}"/>
+    <hyperlink ref="J64" r:id="rId47" xr:uid="{64D622A4-08EA-FB44-9847-6F32ADA84A36}"/>
+    <hyperlink ref="G65" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{BBB5B0AD-1BF0-E64B-8D11-AF3087E144D4}"/>
+    <hyperlink ref="J65" r:id="rId49" xr:uid="{FF925F57-BA58-C348-A9A0-3D0937470FA4}"/>
+    <hyperlink ref="G66" r:id="rId50" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{B551A4F6-EE75-A44A-8014-841069B2FCB7}"/>
+    <hyperlink ref="G67" r:id="rId51" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{1DAE0668-8388-D44C-B55A-DE62538ABA00}"/>
+    <hyperlink ref="G68" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{1820AC45-B034-1349-AA05-3964774F0C07}"/>
+    <hyperlink ref="J68" r:id="rId53" xr:uid="{AC7AD16D-241D-8540-96DF-4ED7D49F34B9}"/>
+    <hyperlink ref="G69" r:id="rId54" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{5AFF1513-FA56-DE44-B316-117D220FAE64}"/>
+    <hyperlink ref="J69" r:id="rId55" xr:uid="{E71D53A6-7457-7144-8894-EE123DD1E67D}"/>
+    <hyperlink ref="G72" r:id="rId56" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{3CD5F7AC-C428-734F-9279-B10573B73294}"/>
+    <hyperlink ref="G73" r:id="rId57" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{A344CF3E-1546-EF43-A9CE-21857736F0E0}"/>
+    <hyperlink ref="G74" r:id="rId58" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{706A8DAD-026F-634B-9169-5DD3CCC50856}"/>
+    <hyperlink ref="J75" r:id="rId59" xr:uid="{63856CE4-F28F-CB42-BFB9-F9395BA76676}"/>
+    <hyperlink ref="J76" r:id="rId60" xr:uid="{DC26C6F3-6C48-6F42-9D76-9C660920B5CE}"/>
+    <hyperlink ref="G78" r:id="rId61" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{14683BA3-758A-CE4D-A58B-C54064F7BE56}"/>
+    <hyperlink ref="G80" r:id="rId62" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{7657620D-E570-8D46-9C04-51F488C2A753}"/>
+    <hyperlink ref="J80" r:id="rId63" xr:uid="{AC0BBA8E-C8F9-434F-BF47-3E38B57D0854}"/>
+    <hyperlink ref="G81" r:id="rId64" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{329B437D-5895-4547-AB9C-E5919A64E037}"/>
+    <hyperlink ref="G82" r:id="rId65" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{0D7AB262-F7D7-C34B-9ED0-1A329891B072}"/>
+    <hyperlink ref="J84" r:id="rId66" xr:uid="{DBCB2E75-C6F0-8344-8B47-15FC3A4DCDC6}"/>
+    <hyperlink ref="G91" r:id="rId67" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{DE119583-F713-364D-9EFB-AB6891D361B7}"/>
+    <hyperlink ref="I91" r:id="rId68" xr:uid="{06560E31-AD3F-E248-A0F5-80291911BA6F}"/>
+    <hyperlink ref="G92" r:id="rId69" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{C874ABD6-CF1A-7A4E-B66D-FEB64DF66C89}"/>
+    <hyperlink ref="G93" r:id="rId70" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{76AEA358-ED2E-BA40-A22D-697598D71CE2}"/>
+    <hyperlink ref="G96" r:id="rId71" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{DADDE89C-6E40-C94A-960E-B2CF47FEDDF8}"/>
+    <hyperlink ref="G97" r:id="rId72" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{E26D4202-BF99-BE4A-9C67-5CDBA9B11D92}"/>
+    <hyperlink ref="G98" r:id="rId73" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{5AE12DD8-6346-014D-997C-BEBFDCBE6C37}"/>
+    <hyperlink ref="I98" r:id="rId74" xr:uid="{C7A4F43C-C1A4-7148-937B-DC7BEC0D90C3}"/>
+    <hyperlink ref="G99" r:id="rId75" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{0F8657B5-386F-9D4F-859F-71A3096A3326}"/>
+    <hyperlink ref="G100" r:id="rId76" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{2981AF24-C245-D746-8227-7183AB9A2D76}"/>
+    <hyperlink ref="G101" r:id="rId77" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{3BDF4EE5-834B-4A4C-9336-8ED2F3D7020E}"/>
+    <hyperlink ref="G102" r:id="rId78" display="mailto:sjaisson@chu-reims.fr" xr:uid="{C6544B40-4CD1-F34E-A347-BC2857AD24BC}"/>
+    <hyperlink ref="G103" r:id="rId79" display="mailto:sjaisson@chu-reims.fr" xr:uid="{92205705-C38C-4741-92B2-505D49263184}"/>
+    <hyperlink ref="G104" r:id="rId80" display="mailto:dmarot@chu-reims.fr" xr:uid="{4935634E-A474-A146-A35B-2A4D89304B5F}"/>
+    <hyperlink ref="G105" r:id="rId81" display="mailto:lramont@chu-reims.fr" xr:uid="{649060D2-9075-8747-90E2-B8EB288FF037}"/>
+    <hyperlink ref="G106" r:id="rId82" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{B1D1BB65-4C13-E542-8B75-066A5FEC5883}"/>
+    <hyperlink ref="G107" r:id="rId83" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{95789C02-089A-0C49-B1A9-30456A3B3F6E}"/>
+    <hyperlink ref="G108" r:id="rId84" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{1838E7AB-0FD8-AB4A-AAE0-6FCE9311FF05}"/>
+    <hyperlink ref="G109" r:id="rId85" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{22C5E581-CFFC-A347-8E40-647EE43C1B82}"/>
+    <hyperlink ref="G110" r:id="rId86" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{D91885D5-A612-5345-80A1-1180D64353CE}"/>
+    <hyperlink ref="G113" r:id="rId87" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{9D6C849D-D397-3C45-BC32-07F962DE03A3}"/>
+    <hyperlink ref="G114" r:id="rId88" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{90E5EA69-B15F-2341-B7F2-AB3DD84BF469}"/>
+    <hyperlink ref="G115" r:id="rId89" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{DC2741EE-4235-F045-BF3D-A299BF8B866E}"/>
+    <hyperlink ref="G116" r:id="rId90" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{DC9680C7-437A-2A4E-936C-F10A59A04674}"/>
+    <hyperlink ref="G117" r:id="rId91" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{35CF8A5B-3069-F244-B1D2-1E2F431337EE}"/>
+    <hyperlink ref="G118" r:id="rId92" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{7A1C890D-26CA-1D47-9C69-5983B5CD0F43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDE8EF8-D735-BE49-8EDC-7757B4E30543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B290B9BB-F8E6-E243-8A70-823D27B57227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1046,9 +1046,6 @@
     <t>L’Unité Fonctionnelle est un LBMR pour le diagnostic fonctionnel et génétique de la Granulomatose Septique Chronique et du déficit en Rac2. Une forte expertise de recherche est également associée à l’activité de soin concernant les pathologies liées au déficit en NADPH oxydase NOX2 des phagocytes</t>
   </si>
   <si>
-    <t>Saint-Etienne</t>
-  </si>
-  <si>
     <t>Neuropathies périphériques dysimmunes et pathologies neuromusculaires</t>
   </si>
   <si>
@@ -2015,9 +2012,6 @@
     <t>Etude du métabolisme des anémies rares congénitales, des surcharges en Fer et des formes biologiques circulantes du fer. Nos études vont du gène a la protéine, incluant les modification post traductionelles ainsi que les métaux.</t>
   </si>
   <si>
-    <t>Clermont-Ferrand </t>
-  </si>
-  <si>
     <t>La thématique centrale de l’équipe est de comprendre les mécanismes cellulaires et moléculaires de l’agression épithéliale appliquée à des pathologiques courantes afin d’en optimiser le diagnostic, le pronostic et la thérapeutique. </t>
   </si>
   <si>
@@ -2268,6 +2262,12 @@
   </si>
   <si>
     <t>Myologie</t>
+  </si>
+  <si>
+    <t>Clermont-Ferrand</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
   </si>
 </sst>
 </file>
@@ -2426,9 +2426,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2697,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -2706,10 +2706,10 @@
         <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>49</v>
@@ -2726,13 +2726,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>50</v>
@@ -2741,13 +2741,13 @@
         <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2759,7 +2759,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>117</v>
@@ -2774,13 +2774,13 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2792,7 +2792,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>54</v>
@@ -2823,7 +2823,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -2861,7 +2861,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -3041,7 +3041,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>40</v>
@@ -3122,7 +3122,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>60</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>45</v>
@@ -3232,13 +3232,13 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>70</v>
@@ -3267,7 +3267,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>70</v>
@@ -3296,7 +3296,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>70</v>
@@ -3319,13 +3319,13 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
@@ -3354,7 +3354,7 @@
         <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -3386,7 +3386,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>81</v>
@@ -3412,7 +3412,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>82</v>
@@ -3439,7 +3439,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
@@ -3466,7 +3466,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
@@ -3487,13 +3487,13 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -3514,13 +3514,13 @@
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>87</v>
@@ -3636,7 +3636,7 @@
         <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>99</v>
@@ -3659,13 +3659,13 @@
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>99</v>
@@ -3694,7 +3694,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>99</v>
@@ -3717,13 +3717,13 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>99</v>
@@ -3749,7 +3749,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>106</v>
@@ -3890,7 +3890,7 @@
         <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>13</v>
@@ -3899,7 +3899,7 @@
         <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>135</v>
@@ -3921,7 +3921,7 @@
         <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>15</v>
@@ -3930,7 +3930,7 @@
         <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>135</v>
@@ -3952,7 +3952,7 @@
         <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>140</v>
@@ -3961,7 +3961,7 @@
         <v>45</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>141</v>
@@ -3970,7 +3970,7 @@
         <v>142</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -3983,7 +3983,7 @@
         <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -3992,7 +3992,7 @@
         <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>141</v>
@@ -4014,7 +4014,7 @@
         <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>7</v>
@@ -4023,7 +4023,7 @@
         <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>144</v>
@@ -4045,7 +4045,7 @@
         <v>176</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
@@ -4054,7 +4054,7 @@
         <v>45</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>147</v>
@@ -4076,16 +4076,16 @@
         <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>150</v>
@@ -4107,7 +4107,7 @@
         <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>15</v>
@@ -4116,7 +4116,7 @@
         <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>150</v>
@@ -4138,16 +4138,16 @@
         <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>147</v>
@@ -4169,16 +4169,16 @@
         <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
@@ -4200,7 +4200,7 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>157</v>
@@ -4209,7 +4209,7 @@
         <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>158</v>
@@ -4231,7 +4231,7 @@
         <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>13</v>
@@ -4240,7 +4240,7 @@
         <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>161</v>
@@ -4262,7 +4262,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -4271,7 +4271,7 @@
         <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>163</v>
@@ -4280,7 +4280,7 @@
         <v>159</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4293,16 +4293,16 @@
         <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>164</v>
@@ -4324,7 +4324,7 @@
         <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>157</v>
@@ -4333,7 +4333,7 @@
         <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>167</v>
@@ -4355,7 +4355,7 @@
         <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>157</v>
@@ -4364,7 +4364,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>163</v>
@@ -4386,7 +4386,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>157</v>
@@ -4395,7 +4395,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>163</v>
@@ -4417,7 +4417,7 @@
         <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>15</v>
@@ -4426,7 +4426,7 @@
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>163</v>
@@ -4448,7 +4448,7 @@
         <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>15</v>
@@ -4457,16 +4457,16 @@
         <v>44</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="H61" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4479,7 +4479,7 @@
         <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>15</v>
@@ -4488,19 +4488,19 @@
         <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="I62" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -4512,7 +4512,7 @@
         <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -4521,14 +4521,14 @@
         <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -4538,14 +4538,14 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>378</v>
+        <v>461</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>178</v>
@@ -4557,7 +4557,7 @@
         <v>180</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="5" t="s">
@@ -4569,20 +4569,20 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>378</v>
+        <v>461</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>182</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>183</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="66" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>378</v>
+        <v>461</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
@@ -4610,16 +4610,16 @@
         <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>186</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>378</v>
+        <v>461</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -4639,7 +4639,7 @@
         <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>187</v>
@@ -4662,13 +4662,13 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>191</v>
@@ -4688,71 +4688,71 @@
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11" t="s">
+      <c r="B69" s="12"/>
+      <c r="C69" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="11" t="s">
-        <v>348</v>
+      <c r="E69" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="F69" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="G69" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="H69" s="9" t="s">
+      <c r="I69" s="13"/>
+      <c r="J69" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G70" s="11"/>
+      <c r="H70" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="I70" s="13"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="I69" s="12"/>
-      <c r="J69" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="I70" s="12"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="I71" s="12"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -4760,16 +4760,16 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>197</v>
@@ -4795,16 +4795,16 @@
         <v>45</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>199</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -4824,7 +4824,7 @@
         <v>45</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>200</v>
@@ -4922,7 +4922,7 @@
         <v>213</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -4971,7 +4971,7 @@
         <v>45</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>219</v>
@@ -5028,10 +5028,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>228</v>
@@ -5054,13 +5054,13 @@
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>231</v>
@@ -5086,13 +5086,13 @@
         <v>234</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>235</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
@@ -5118,20 +5118,20 @@
         <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="H84" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -5149,16 +5149,16 @@
         <v>45</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5168,7 +5168,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
@@ -5178,16 +5178,16 @@
         <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G86" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G86" s="10" t="s">
+      <c r="H86" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5197,26 +5197,26 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="H87" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
@@ -5236,16 +5236,16 @@
         <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G88" s="10" t="s">
+      <c r="H88" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
@@ -5265,16 +5265,16 @@
         <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -5294,16 +5294,16 @@
         <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G90" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>260</v>
-      </c>
       <c r="H90" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5313,29 +5313,29 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F91" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G91" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="H91" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="I91" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5344,26 +5344,26 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="H92" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -5373,26 +5373,26 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="H93" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
@@ -5412,13 +5412,13 @@
         <v>45</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -5439,16 +5439,16 @@
         <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -5458,26 +5458,26 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G96" s="5" t="s">
+      <c r="H96" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
@@ -5497,16 +5497,16 @@
         <v>44</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="H97" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -5516,29 +5516,29 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F98" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G98" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="H98" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="I98" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -5547,7 +5547,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
@@ -5557,16 +5557,16 @@
         <v>45</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F99" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G99" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="H99" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
@@ -5586,16 +5586,16 @@
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="H100" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -5605,26 +5605,26 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
@@ -5644,16 +5644,16 @@
         <v>44</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="H102" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -5663,26 +5663,26 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -5692,26 +5692,26 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G104" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
@@ -5731,16 +5731,16 @@
         <v>44</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F105" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G105" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="H105" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -5750,26 +5750,26 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="H106" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -5779,26 +5779,26 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G107" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>313</v>
-      </c>
       <c r="H107" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -5808,26 +5808,26 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="G108" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="H108" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
@@ -5847,16 +5847,16 @@
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="H109" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
@@ -5876,16 +5876,16 @@
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F110" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G110" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="H110" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
@@ -5905,16 +5905,16 @@
         <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="H111" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -5924,7 +5924,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
@@ -5934,16 +5934,16 @@
         <v>45</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -5953,26 +5953,26 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G113" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G113" s="5" t="s">
+      <c r="H113" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -5982,26 +5982,26 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G114" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G114" s="5" t="s">
+      <c r="H114" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6011,7 +6011,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
@@ -6021,16 +6021,16 @@
         <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6040,26 +6040,26 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G116" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H116" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6069,26 +6069,26 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -6098,26 +6098,26 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H118" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -6127,111 +6127,111 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="C69:C71"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:E71"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{BECE8CF2-0490-7A47-9A41-0656A1077714}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{05DEBDEA-5744-E141-B21D-44ED99EA85AE}"/>
-    <hyperlink ref="G4" r:id="rId3" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{10E18B9C-36CA-AE46-9FFD-57FA6E67F38F}"/>
-    <hyperlink ref="I4" r:id="rId4" xr:uid="{F63A4C3A-4CDB-C341-B7A6-7C74A40F7AB8}"/>
-    <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{67A962E2-668C-5344-94E4-1EC6DFEF8203}"/>
-    <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{1B41749A-CB5C-2546-BD08-6B758F14D101}"/>
-    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{65E7FD78-21C5-B847-990E-2DAD69A49EDA}"/>
-    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{9334F2AD-3318-9847-8A3D-C10C40F2E23D}"/>
-    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{40D0837F-8AA9-834C-ADEB-1A0A14FC66C1}"/>
-    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{0AC9D3DF-B4EE-2B47-A362-010CF44183EC}"/>
-    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{BDB9F7EF-DEB7-F946-AC4D-08E94CAF4009}"/>
-    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{8247C51A-C026-4047-9245-17A62FF1BFEA}"/>
-    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{347627A6-1668-A245-9EB9-CE0C0ADB782D}"/>
-    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{CA35FB74-B96C-3C4B-9596-88338397D323}"/>
-    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{DE45C52D-1690-C945-83E3-11C09373AFA9}"/>
-    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{2C8EF82B-A37E-6047-B8DB-221BF9CD112F}"/>
-    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{12085339-E0D9-7F45-8415-24991C29B496}"/>
-    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{84D3A1A7-7B69-B645-957F-92ACA9F98788}"/>
-    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{5A5DA6BD-9E05-5B48-AEF8-8FC5F4400BDE}"/>
-    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{C10E2064-438B-4245-9762-755A08F9D065}"/>
-    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{FE31F27F-3506-E346-A7B0-4DBC0276054C}"/>
-    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{0E016276-8CBE-7441-AC14-E6EA01963935}"/>
-    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{334E7D4B-467B-CF40-B676-E72B2880B411}"/>
-    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{3B35314F-5901-6641-AFB2-A849DA1A5DA9}"/>
-    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{A359737B-E389-464B-BA8E-996224AFC809}"/>
-    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{55F1D805-500A-7D4C-8952-79F133BE35BF}"/>
-    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{D8321FC6-227D-B14E-A3CB-FD9256AE0E50}"/>
-    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{38D65A69-06F4-2240-AD73-335CE3B1CE3E}"/>
-    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{54F44914-6520-B348-A07E-A4F879073C5A}"/>
-    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{B8C43AAB-9CE5-0447-A4BB-0BC6E01215AD}"/>
-    <hyperlink ref="I42" r:id="rId31" xr:uid="{98E9E07F-5CFD-9548-838F-CDDA799C9D4D}"/>
-    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{EE9BC22F-DBA7-AC43-B88C-04AC69DB03F5}"/>
-    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{17BD6FA3-1BAF-6D48-A68C-ABFE77468836}"/>
-    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{E7357D05-2B7E-3642-9F5C-9C7F3141D354}"/>
-    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{210898B7-070A-B249-B3D3-5F87EC0ABEED}"/>
-    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{DB74F793-0FB2-DA42-B877-3E3A44B990D5}"/>
-    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{403F2DD4-9E41-A94D-BFBF-6E21F77269C3}"/>
-    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{0EF8D8AF-4FDF-9A4F-A969-686A257BD73E}"/>
-    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{147B1B47-0285-B04D-B523-F2657D64678F}"/>
-    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{B7F4C06C-8ED5-F04C-A01C-E45AC877D38D}"/>
-    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{9FE6EE95-03B4-A54F-A54D-44FE95CC36B7}"/>
-    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{6F81145E-B562-424F-8619-9FAB035CEE9E}"/>
-    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{FA6E2218-5A07-464F-9A1C-D2E4083E90CC}"/>
-    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{282EB162-951C-6B44-A265-9541E44E7A2E}"/>
-    <hyperlink ref="I62" r:id="rId45" xr:uid="{C99CC80F-D1D1-BE43-987A-CEF2049DCE1D}"/>
-    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{D519D47B-1838-2346-AC56-DD3E6815BAC6}"/>
-    <hyperlink ref="J64" r:id="rId47" xr:uid="{64D622A4-08EA-FB44-9847-6F32ADA84A36}"/>
-    <hyperlink ref="G65" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{BBB5B0AD-1BF0-E64B-8D11-AF3087E144D4}"/>
-    <hyperlink ref="J65" r:id="rId49" xr:uid="{FF925F57-BA58-C348-A9A0-3D0937470FA4}"/>
-    <hyperlink ref="G66" r:id="rId50" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{B551A4F6-EE75-A44A-8014-841069B2FCB7}"/>
-    <hyperlink ref="G67" r:id="rId51" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{1DAE0668-8388-D44C-B55A-DE62538ABA00}"/>
-    <hyperlink ref="G68" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{1820AC45-B034-1349-AA05-3964774F0C07}"/>
-    <hyperlink ref="J68" r:id="rId53" xr:uid="{AC7AD16D-241D-8540-96DF-4ED7D49F34B9}"/>
-    <hyperlink ref="G69" r:id="rId54" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{5AFF1513-FA56-DE44-B316-117D220FAE64}"/>
-    <hyperlink ref="J69" r:id="rId55" xr:uid="{E71D53A6-7457-7144-8894-EE123DD1E67D}"/>
-    <hyperlink ref="G72" r:id="rId56" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{3CD5F7AC-C428-734F-9279-B10573B73294}"/>
-    <hyperlink ref="G73" r:id="rId57" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{A344CF3E-1546-EF43-A9CE-21857736F0E0}"/>
-    <hyperlink ref="G74" r:id="rId58" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{706A8DAD-026F-634B-9169-5DD3CCC50856}"/>
-    <hyperlink ref="J75" r:id="rId59" xr:uid="{63856CE4-F28F-CB42-BFB9-F9395BA76676}"/>
-    <hyperlink ref="J76" r:id="rId60" xr:uid="{DC26C6F3-6C48-6F42-9D76-9C660920B5CE}"/>
-    <hyperlink ref="G78" r:id="rId61" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{14683BA3-758A-CE4D-A58B-C54064F7BE56}"/>
-    <hyperlink ref="G80" r:id="rId62" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{7657620D-E570-8D46-9C04-51F488C2A753}"/>
-    <hyperlink ref="J80" r:id="rId63" xr:uid="{AC0BBA8E-C8F9-434F-BF47-3E38B57D0854}"/>
-    <hyperlink ref="G81" r:id="rId64" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{329B437D-5895-4547-AB9C-E5919A64E037}"/>
-    <hyperlink ref="G82" r:id="rId65" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{0D7AB262-F7D7-C34B-9ED0-1A329891B072}"/>
-    <hyperlink ref="J84" r:id="rId66" xr:uid="{DBCB2E75-C6F0-8344-8B47-15FC3A4DCDC6}"/>
-    <hyperlink ref="G91" r:id="rId67" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{DE119583-F713-364D-9EFB-AB6891D361B7}"/>
-    <hyperlink ref="I91" r:id="rId68" xr:uid="{06560E31-AD3F-E248-A0F5-80291911BA6F}"/>
-    <hyperlink ref="G92" r:id="rId69" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{C874ABD6-CF1A-7A4E-B66D-FEB64DF66C89}"/>
-    <hyperlink ref="G93" r:id="rId70" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{76AEA358-ED2E-BA40-A22D-697598D71CE2}"/>
-    <hyperlink ref="G96" r:id="rId71" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{DADDE89C-6E40-C94A-960E-B2CF47FEDDF8}"/>
-    <hyperlink ref="G97" r:id="rId72" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{E26D4202-BF99-BE4A-9C67-5CDBA9B11D92}"/>
-    <hyperlink ref="G98" r:id="rId73" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{5AE12DD8-6346-014D-997C-BEBFDCBE6C37}"/>
-    <hyperlink ref="I98" r:id="rId74" xr:uid="{C7A4F43C-C1A4-7148-937B-DC7BEC0D90C3}"/>
-    <hyperlink ref="G99" r:id="rId75" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{0F8657B5-386F-9D4F-859F-71A3096A3326}"/>
-    <hyperlink ref="G100" r:id="rId76" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{2981AF24-C245-D746-8227-7183AB9A2D76}"/>
-    <hyperlink ref="G101" r:id="rId77" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{3BDF4EE5-834B-4A4C-9336-8ED2F3D7020E}"/>
-    <hyperlink ref="G102" r:id="rId78" display="mailto:sjaisson@chu-reims.fr" xr:uid="{C6544B40-4CD1-F34E-A347-BC2857AD24BC}"/>
-    <hyperlink ref="G103" r:id="rId79" display="mailto:sjaisson@chu-reims.fr" xr:uid="{92205705-C38C-4741-92B2-505D49263184}"/>
-    <hyperlink ref="G104" r:id="rId80" display="mailto:dmarot@chu-reims.fr" xr:uid="{4935634E-A474-A146-A35B-2A4D89304B5F}"/>
-    <hyperlink ref="G105" r:id="rId81" display="mailto:lramont@chu-reims.fr" xr:uid="{649060D2-9075-8747-90E2-B8EB288FF037}"/>
-    <hyperlink ref="G106" r:id="rId82" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{B1D1BB65-4C13-E542-8B75-066A5FEC5883}"/>
-    <hyperlink ref="G107" r:id="rId83" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{95789C02-089A-0C49-B1A9-30456A3B3F6E}"/>
-    <hyperlink ref="G108" r:id="rId84" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{1838E7AB-0FD8-AB4A-AAE0-6FCE9311FF05}"/>
-    <hyperlink ref="G109" r:id="rId85" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{22C5E581-CFFC-A347-8E40-647EE43C1B82}"/>
-    <hyperlink ref="G110" r:id="rId86" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{D91885D5-A612-5345-80A1-1180D64353CE}"/>
-    <hyperlink ref="G113" r:id="rId87" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{9D6C849D-D397-3C45-BC32-07F962DE03A3}"/>
-    <hyperlink ref="G114" r:id="rId88" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{90E5EA69-B15F-2341-B7F2-AB3DD84BF469}"/>
-    <hyperlink ref="G115" r:id="rId89" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{DC2741EE-4235-F045-BF3D-A299BF8B866E}"/>
-    <hyperlink ref="G116" r:id="rId90" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{DC9680C7-437A-2A4E-936C-F10A59A04674}"/>
-    <hyperlink ref="G117" r:id="rId91" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{35CF8A5B-3069-F244-B1D2-1E2F431337EE}"/>
-    <hyperlink ref="G118" r:id="rId92" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{7A1C890D-26CA-1D47-9C69-5983B5CD0F43}"/>
+    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{D5A287CC-F3DB-AB4E-A6A7-30A455C45191}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{DAC52750-6C95-424D-8E24-E5E1F57165D8}"/>
+    <hyperlink ref="G4" r:id="rId3" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{7D231BCA-F4ED-B340-AE5F-F713A44F46D8}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{853B4FE4-A56B-B345-BE9E-5B9439A0E1D1}"/>
+    <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{E1C82F55-9724-AF48-9F9F-94DE117CA57A}"/>
+    <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{6F599EA3-6C18-6A4F-B83B-B1BFF986C046}"/>
+    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{EAD6269A-B1A9-3249-AE44-CF813FD72994}"/>
+    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{ACE60A29-4C84-BA40-AF8F-A9895BC6E74B}"/>
+    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{077906EC-AF41-484C-BE29-C796CEC91A8D}"/>
+    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{7F98454A-D76F-3748-8AD5-60659E5EAFBA}"/>
+    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{71878D64-C723-CD4E-9ED3-7AAE7DE3FB72}"/>
+    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{8A1B2178-5941-124C-90C0-4943CC9BDCEC}"/>
+    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{4C62C2C0-8C0C-1D46-A60C-82DF34F952F4}"/>
+    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{19463E8C-16D5-E94E-A25F-50BD3376BF29}"/>
+    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{9464A30E-9537-D043-8FC0-34D4F7AC08A9}"/>
+    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{528A6581-D640-D34C-9CE0-F2D6EAFEBF0C}"/>
+    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{3A9500E0-D9C7-044C-94FA-6EAFF1877A60}"/>
+    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{22B1A9F9-3952-3442-A26E-6A492D52264D}"/>
+    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{7716A5C2-E7DD-1E4E-B60E-89CDB6EB7DDA}"/>
+    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{72CEB3A0-2D44-8B45-9EFB-7375660C28BA}"/>
+    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{EBC7FDA7-05A8-F944-9B37-78E02BFF24AB}"/>
+    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{89926BFF-4008-3C42-90A5-053D950841FA}"/>
+    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{994FF440-58C5-754E-B36B-DBE9D3B2F6C4}"/>
+    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{ABE7FF62-E065-EE40-AA0E-FB9772F7F13E}"/>
+    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{75336746-604B-4D4C-829B-0A6CCAC91E2B}"/>
+    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{D2AF785F-2C5B-044C-8CC8-354D650CF1A0}"/>
+    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{3A5FD94E-4E6A-7A4C-998E-FB408BBDCB2A}"/>
+    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{577081D2-B82E-0344-B7D8-1E6C685CA5D2}"/>
+    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{FD520663-2FF9-E44C-B224-5F2839AC7306}"/>
+    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{839F5651-D675-2D4A-A466-F1A9183DAC56}"/>
+    <hyperlink ref="I42" r:id="rId31" xr:uid="{EC60B6D3-ABB8-7143-8183-075A2D572C9A}"/>
+    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{126CA9BA-E2D8-6D4C-BB0B-45DC651BF7A8}"/>
+    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{6906BA22-3157-C446-9487-B153C6C57BBD}"/>
+    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{6BE15206-19E6-474B-A7B4-1234187D872C}"/>
+    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{E1D0A185-2D5A-7345-810B-B87D6933CFFA}"/>
+    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{A6E0244C-C880-FA4C-88F4-F241F2548D0D}"/>
+    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{19E6FC41-47A2-124C-94D9-570797D95A7B}"/>
+    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{02CA18D2-ECA0-B04D-9CAF-0D5CE592B0EF}"/>
+    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{B5E1A3DB-460F-864A-A9A9-BB9D592A7140}"/>
+    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{44C9CD03-631E-5B45-934A-8B2AE14F1C6C}"/>
+    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{684471D6-7354-4F4A-A97B-627FB94EA97F}"/>
+    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{6694A3DF-1B07-AD4A-BF16-79346CC23557}"/>
+    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{F39DA42A-0EF4-3740-84E1-A6A62B0769F3}"/>
+    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{35083460-75F3-9243-8C23-8B1E08FC4CC1}"/>
+    <hyperlink ref="I62" r:id="rId45" xr:uid="{62BD73B8-0204-3D4E-9C38-6CD591F31713}"/>
+    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{4A02BDDE-6857-3A46-9924-3164A036D883}"/>
+    <hyperlink ref="J64" r:id="rId47" xr:uid="{CD276749-77DC-A647-B15E-C84583931DE6}"/>
+    <hyperlink ref="G65" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{F30ED4AE-EF4C-6141-852E-E585A269EEB4}"/>
+    <hyperlink ref="J65" r:id="rId49" xr:uid="{B7BDF381-9DA8-3D41-8EE7-B3E118953DFD}"/>
+    <hyperlink ref="G66" r:id="rId50" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{946DE2A5-3133-ED45-88A9-7DDDE88DF57E}"/>
+    <hyperlink ref="G67" r:id="rId51" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{205DA997-52F9-5649-8BA9-87468137FCE3}"/>
+    <hyperlink ref="G68" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{5E9E5653-314D-EB49-8F35-728C96CD8D56}"/>
+    <hyperlink ref="J68" r:id="rId53" xr:uid="{527F5591-0038-4B49-8961-80ACBC03C6ED}"/>
+    <hyperlink ref="G69" r:id="rId54" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{765C5C5A-5F47-F94A-A798-378E345E63AC}"/>
+    <hyperlink ref="J69" r:id="rId55" xr:uid="{BD344E66-F045-3A48-A001-A98E3A0C2093}"/>
+    <hyperlink ref="G72" r:id="rId56" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{2C600862-D1B8-0F48-9490-F19F8E219136}"/>
+    <hyperlink ref="G73" r:id="rId57" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{9636385F-A5ED-854A-A340-C7BF70887E67}"/>
+    <hyperlink ref="G74" r:id="rId58" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{D08D7EBC-31C7-D64A-A9CD-2AAAEBF11A46}"/>
+    <hyperlink ref="J75" r:id="rId59" xr:uid="{0E4DBD39-E9AA-7844-8123-AE0D946470A4}"/>
+    <hyperlink ref="J76" r:id="rId60" xr:uid="{27C93922-39FC-A248-B928-04EA23FBD317}"/>
+    <hyperlink ref="G78" r:id="rId61" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{6B4459B5-0E17-4340-99F7-A07417BE8132}"/>
+    <hyperlink ref="G80" r:id="rId62" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{D02C05EB-CBD5-D442-8A7D-5B63F3F6A8FE}"/>
+    <hyperlink ref="J80" r:id="rId63" xr:uid="{AED65EBB-80E5-4C4D-92B8-EC77803B3DBE}"/>
+    <hyperlink ref="G81" r:id="rId64" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{02543C15-B1EA-EE4E-8F6A-62AB8F3C6927}"/>
+    <hyperlink ref="G82" r:id="rId65" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{2399221C-A872-9C4F-917A-7F67F874D35B}"/>
+    <hyperlink ref="J84" r:id="rId66" xr:uid="{D76E39F6-8744-9148-B80B-6F8F34458C1B}"/>
+    <hyperlink ref="G91" r:id="rId67" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{753A0B41-A099-FF4C-85A2-E76B90277A0A}"/>
+    <hyperlink ref="I91" r:id="rId68" xr:uid="{8F5139B4-57DE-3A4A-B1A1-77E7442F6741}"/>
+    <hyperlink ref="G92" r:id="rId69" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{DE5E29A6-295C-B641-8145-EA258E0CB6C2}"/>
+    <hyperlink ref="G93" r:id="rId70" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{90F3B849-B036-2F4D-9CC0-048B2C8269A7}"/>
+    <hyperlink ref="G96" r:id="rId71" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{04E52A32-0705-D04F-AC1E-0EE76FC197C8}"/>
+    <hyperlink ref="G97" r:id="rId72" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{F53877F0-DC05-A349-80EC-5617F1503152}"/>
+    <hyperlink ref="G98" r:id="rId73" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{BC597FB6-502E-DF46-9A1D-3B3154018F19}"/>
+    <hyperlink ref="I98" r:id="rId74" xr:uid="{9A76F5C3-635B-A94C-AA00-B5B412F071BC}"/>
+    <hyperlink ref="G99" r:id="rId75" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{1541119C-C700-5846-A13A-470E49164C2E}"/>
+    <hyperlink ref="G100" r:id="rId76" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{BDE8E49B-A252-E84B-A17B-712891D4F28F}"/>
+    <hyperlink ref="G101" r:id="rId77" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{5CD5710A-5F42-7F47-A40D-80550F005597}"/>
+    <hyperlink ref="G102" r:id="rId78" display="mailto:sjaisson@chu-reims.fr" xr:uid="{F24AD5B8-1A92-7B4C-809C-EFF853926847}"/>
+    <hyperlink ref="G103" r:id="rId79" display="mailto:sjaisson@chu-reims.fr" xr:uid="{147B9E7F-DB97-604F-B2E7-83CF926F535D}"/>
+    <hyperlink ref="G104" r:id="rId80" display="mailto:dmarot@chu-reims.fr" xr:uid="{E2B8F2F5-F9A2-2740-9528-4E766948A6C2}"/>
+    <hyperlink ref="G105" r:id="rId81" display="mailto:lramont@chu-reims.fr" xr:uid="{1AB0B99B-A776-D649-904D-E73F8A612B1C}"/>
+    <hyperlink ref="G106" r:id="rId82" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{AA5771E3-EC46-BD47-8365-0DA3FF3B493E}"/>
+    <hyperlink ref="G107" r:id="rId83" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{1343F3CE-1879-4746-B10C-F980B6C339F9}"/>
+    <hyperlink ref="G108" r:id="rId84" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{399B020A-2DBF-CC42-8866-B9A1531D4E18}"/>
+    <hyperlink ref="G109" r:id="rId85" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{8D68F755-110A-DD43-A4E3-1FD19C076FA0}"/>
+    <hyperlink ref="G110" r:id="rId86" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{DD44DAE1-8771-CB4D-A8F1-3FF172D6E9C1}"/>
+    <hyperlink ref="G113" r:id="rId87" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{6ADBC28F-FFC7-394B-9361-1240407E4F1D}"/>
+    <hyperlink ref="G114" r:id="rId88" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{42CBB318-E1DB-6149-B14F-E36D541EB65A}"/>
+    <hyperlink ref="G115" r:id="rId89" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{6D6BE7BB-C231-2749-8025-8C9BB55B6545}"/>
+    <hyperlink ref="G116" r:id="rId90" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{36DB08BF-3C8D-EA4E-A459-A6053CE9A5F3}"/>
+    <hyperlink ref="G117" r:id="rId91" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{46966F6C-B2E2-AB46-B36E-0290DA921865}"/>
+    <hyperlink ref="G118" r:id="rId92" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{626800B6-221C-A34D-977C-3F340982B5E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B290B9BB-F8E6-E243-8A70-823D27B57227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB5BF8A-A210-164C-A8A8-0F419DB00E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="604">
   <si>
     <t>Villes</t>
   </si>
@@ -810,9 +810,6 @@
     <t>vincent.sapin@uca.fr; loic.blanchon@uca.fr</t>
   </si>
   <si>
-    <t>https://www.igred.fr/equipe/approche-translationnelle-des-lesions-epitheliales-et-de-leur-reparation-2/</t>
-  </si>
-  <si>
     <t>Recherche et développement de biomarqueurs du traumatisme cranien léger</t>
   </si>
   <si>
@@ -822,9 +819,6 @@
     <t>thématique centrale de l’UIC est d’appliquer des nouveaux biomarqueurs sanguins du Traumatisme cranien léger pour optimiser la gestion des patients dans la population générale et dans des populations spécifiques comme les enfants, les personnes âgées ou les sportifs</t>
   </si>
   <si>
-    <t>https://www.chu-clermontferrand.fr/liste-services/direction-de-la-recherche-clinique-et-de-linnovation-drci</t>
-  </si>
-  <si>
     <t>vsapin@chu-clermontferrand.fr</t>
   </si>
   <si>
@@ -847,9 +841,6 @@
   </si>
   <si>
     <t>Le rôle de la mitophagie lors d’un accident vasculaire cérébral reste encore mal compris, notamment en ce qui concerne ses effets délétères ou bénéfiques sur la survie neuronale. Nous travaillons sur la caractérisation des voies moléculaires de la mitophagie et leur modulation dans ce contexte d’hypoxie/réoxygénation.</t>
-  </si>
-  <si>
-    <t>https://www.unicaen.fr/laboratoire/umrs-1237-physiopathologie-et-imagerie-des-troubles-neurologiques-phind</t>
   </si>
   <si>
     <t>Nutrition</t>
@@ -933,9 +924,6 @@
     </r>
   </si>
   <si>
-    <t>https://ctm.ube.fr/</t>
-  </si>
-  <si>
     <t>Physiopathologie des dyslipidémies dans le diabète de type 1, de type 2 et le syndrome métabolique.</t>
   </si>
   <si>
@@ -993,9 +981,6 @@
     <t>Dotée d’un équipement performant (Q-Exactive Thermo Haute Résolution) notre plateforme mixte (UGA/CHU) permet la réalisation de projets de recherche bio-clinique d’analyse du métabolome dans les liquides biologiques.</t>
   </si>
   <si>
-    <t>https://www.gemeli-uga.fr/</t>
-  </si>
-  <si>
     <t>CHU Grenoble - LBMR Maladies neuromusculaires</t>
   </si>
   <si>
@@ -1112,9 +1097,6 @@
     <t>L’équipe s’intéresse aux anticorps associés aux neuropathies périphériques dysimmunes. L’un des objectifs est d’identifier de nouveaux autoanticorps par des méthodes protéomiques puis de caractériser les cibles protéiques, les autoanticorps et les patients présentant ces autoanticorps sur le plan clinique. Un autre axe de recherche est le développement de modèles in vitro de cultures cellulaires pour tester l’effet pathogène des anticorps identifiés.</t>
   </si>
   <si>
-    <t>https://www.univ-st-etienne.fr/fr/synatac.html</t>
-  </si>
-  <si>
     <t>Biologie des maladies neurologiques inflammatoires</t>
   </si>
   <si>
@@ -1937,9 +1919,6 @@
     <t>Grossesse et néonatalogie</t>
   </si>
   <si>
-    <t>Médecine moléculaire, génétique</t>
-  </si>
-  <si>
     <t>Cardio-vasculaire</t>
   </si>
   <si>
@@ -2268,13 +2247,594 @@
   </si>
   <si>
     <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Limoges</t>
+  </si>
+  <si>
+    <t>Neurologie</t>
+  </si>
+  <si>
+    <t>Etudes des mécanismes physiopathologiques en lien avec le développement des neuropathies périphériques</t>
+  </si>
+  <si>
+    <t>UR 20218 Neuropathies Périphériques et Innovations Thérapeutiques</t>
+  </si>
+  <si>
+    <t>franck.sturtz@unilim.fr ; frederic.favreau@unilim.fr ; anne-sophie.lia@unilim.fr ; pierre-antoine.faye@unilim.fr ; pauline.chazelas@unilim.fr</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L’Unité de Recherche NEURIT s’attache à étudier les mécanismes impliqués dans le développement des neuropathies périphériques qu’elles soient d’origine génétique comme la maladie de Charcot Marie Tooth, d’origine traumatique, d’origine médicamenteuse comme les traitements anticancéreux ou métabolique comme le diabète. L’unité utilise des modèles </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in vivo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in vitro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> en particulier grâce à la technologie IPSc pour mettre en lumière des traitements novateurs destinés à ces pathologies où les traitements efficaces sont quasi inexistants</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.unilim.fr/ur20218-neurit/</t>
+  </si>
+  <si>
+    <t>Modèles in vitro adaptés à l’étude des neuropathies périphériques</t>
+  </si>
+  <si>
+    <t>pierre-antoine.faye@unilim.fr ; anne-sophie.lia@unilim.fr</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Une partie des membres de l’Unité de Recherche NEURIT s’attache à développer des modèles cellulaires pour étudier les mécanismes associés aux neuropathies périphériques d’origine génétique. La technologie IPSc a permis de mettre en place des modèles de motoneurones et de cellules de Schwann en culture caractérisés par une mutation préalablement retrouvée chez le patient source. Ces modèles permettent de tester de nouvelles thérapies et notamment la technologie de translecture ou d’inhibiteur du NMD. Un autre aspect est de reproduire </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in vitro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> la jonction neuromusculaire en combinant les différents types cellulaires d’intérêt issus de la technologie IPSc.</t>
+    </r>
+  </si>
+  <si>
+    <t>Etude du syndrome de CANVAS</t>
+  </si>
+  <si>
+    <r>
+      <t>pauline.chazelas@unilim.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>anne-sophie.lia@unilim.fr</t>
+    </r>
+  </si>
+  <si>
+    <t>Le Dr Pauline CHAZELAS s’attache à étudier les mécanismes en cause dans le développement du syndrome de CANVAS. Elle est impliquée dans des études de cohorte et participe activement à l’amélioration du diagnostic de cette pathologie invalidante.</t>
+  </si>
+  <si>
+    <t>LBMR : Diagnostic moléculaire de la maladie de Charcot Marie Tooth (CMT) </t>
+  </si>
+  <si>
+    <t>UF 8852 Biochimie et Génétique Moléculaire</t>
+  </si>
+  <si>
+    <t>franck.sturtz@unilim.fr ; anne-sophie.lia@unilim.fr ; pauline.chazelas@unilim.fr</t>
+  </si>
+  <si>
+    <t>Le LBMR Maladie de Charcot Marie Tooth, localisé au sein du service de Biochimie et Génétique Moléculaire du CHU de Limoges, a une expertise reconnue dans le diagnostic moléculaire de la CMT en utilisant des techniques de pointe de biologie moléculaire à la recherche de mutations ponctuelles ou de variants de structure.</t>
+  </si>
+  <si>
+    <t>Maladie de Charcot Marie Tooth, NGS</t>
+  </si>
+  <si>
+    <t>Poitiers</t>
+  </si>
+  <si>
+    <t>Ischémie Reperfusion en Transplantation</t>
+  </si>
+  <si>
+    <t>Recherche Fondamentale</t>
+  </si>
+  <si>
+    <t>U1313 IRMETIST (Ischémie Reperfusion, Métabolisme et Inflammation Stérile en Transplantation)</t>
+  </si>
+  <si>
+    <t>secretariat.insermu1313@chu-poitiers.fr</t>
+  </si>
+  <si>
+    <t>Les thématiques de recherche de l’unité s’articulent autour de l’amélioration des conditions de la transplantation d’organes, principalement le rein et le foie, et autour de l’étude des phénomènes lésionnels liées à l’ischémie-reperfusion (IR).</t>
+  </si>
+  <si>
+    <t>https://irmetist.labo.univ-poitiers.fr/</t>
+  </si>
+  <si>
+    <t>Canaux Ioniques dans les Cellules Souches et les Cancers</t>
+  </si>
+  <si>
+    <t>UR 22751 4CS (Canaux et Connexines dans les Cancers et les Cellules Souches)</t>
+  </si>
+  <si>
+    <t>valerie.coronas@univ-poitiers.fr ; nicolas.bourmeyster@chu-poitiers.fr</t>
+  </si>
+  <si>
+    <t>Les objectifs de l’unité sont de caractériser le rôle des canaux ioniques dans les propriétés physiologiques et la plasticité cellulaire des cellules souches et des cellules invasives de différents organes. Nous étudions également le remodelage pathologique de la signalisation calcique dans les cancers (Mélanomes, glioblastomes, </t>
+  </si>
+  <si>
+    <t>https://4cs.labo.univ-poitiers.fr/</t>
+  </si>
+  <si>
+    <t>Recherche et développement de biomarqueurs</t>
+  </si>
+  <si>
+    <t>CHU Poitiers</t>
+  </si>
+  <si>
+    <t>raphael.thuillier@univ-poitiers.fr</t>
+  </si>
+  <si>
+    <t>Nous débutons la mise en place au sein de la biochimie d’une plateforme de métabolomique visant à découvrir de nouveaux biomarqueurs dans des problématiques cliniques en manque d’outils d’aide à la décision. Nous avons validé un protocole d’extraction de signaux à partir de plasma très performant (Lepoittevin et al. 2023) qui génère une image robuste de chaque échantillon comprenant des centaines de signaux. Pour mieux l’analyser, nous avons mis au point un workflow d’intelligence artificielle nous permettant de réaliser et évaluer la performance des étapes clés du développement d’algorithmes d’aide à la décision : transformation des données, sélection des variables clés, formulation d’algorithmes à travers un apprentissage automatique (bootstrap, validation croisée, etc.), évaluation des performances sur un échantillon test (AUC de la courbe ROC, Brier Score, Youden’s index, etc.). Ces outils ont déjà montré leurs performance dans une petite étude (Lepoittevin et al. 2024), et nous sommes actuellement dans une démarche de construction de bio banque avec nos collègues cliniciens pour déployer ces méthodes sur d’autres problématiques cliniques d’intérêt. Pour le moment il s’agit d’un projet en émergence</t>
+  </si>
+  <si>
+    <t> Métabolomique, spectrométrie de masse à haute résolution, intelligence artificielle</t>
+  </si>
+  <si>
+    <t>Protéomique clinique</t>
+  </si>
+  <si>
+    <t>CRMR - Pour le moment l’équipement doit être installé en biochimie et il apportera au centre de référence amylose AL de Limoges et Poitiers un support en lien avec l’anatomie pathologie.</t>
+  </si>
+  <si>
+    <t>nicolas.bourmeyster@chu-poitiers.fr ; thierry.hauet@chu-poitiers.fr</t>
+  </si>
+  <si>
+    <t>Nous développons au sein du Service de Biochimie une plateforme de protéomique visant à compléter la recherche diagnostique dans les amyloses rénales. Cette plateforme se développera également dans l’avenir pour étudier la maladie résiduelle dans les myélomes multiples et les gammapathies monoclonales.</t>
+  </si>
+  <si>
+    <t>Protéomique, spectométrie de masse à haute résolution, Amyloses</t>
+  </si>
+  <si>
+    <t>Exploration de la fonction rénale </t>
+  </si>
+  <si>
+    <t>Expertise sur les explorations biologiques en clinique </t>
+  </si>
+  <si>
+    <t>Pour le moment ce projet est en phase de mis en place</t>
+  </si>
+  <si>
+    <t>CHU Poitiers - U1313 IRMETIST (Ischémie Reperfusion, Métabolisme et Inflammation Stérile en Transplantation)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">clara.steichen@univ-poitiers.fr ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thierry.hauet@chu-poitiers.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>    </t>
+    </r>
+  </si>
+  <si>
+    <t>Angers</t>
+  </si>
+  <si>
+    <t>Soin - Recherche</t>
+  </si>
+  <si>
+    <t>Métabolisme,  métabolomique pathologies mitochondriales et neuropathies optiques héréditaires</t>
+  </si>
+  <si>
+    <t>équipe Mitolab de l’Unité MITOVASC (INSERM U 1083, CNRS 6015)</t>
+  </si>
+  <si>
+    <t>deprunier@chu-angers.fr</t>
+  </si>
+  <si>
+    <t>Nous menons des études sur la physiopathologie ou la recherche thérapeutique dans les pathologies mitochondriales. Nous avons une expertise sur le métabolisme, la métabolomique, les études fonctionnelles de la chaine respiratoires mitochondriales, la génomique mitochondriale</t>
+  </si>
+  <si>
+    <t>https://mitovasc.univ-angers.fr/en/index.html ; https://mitovasc.univ-angers.fr/en/discover-our-teams/research-themes.html</t>
+  </si>
+  <si>
+    <t>Pathologies Mitochondriales</t>
+  </si>
+  <si>
+    <t>pathologies mitochondriales et neuropathies optiques héréditaires LBMR pour « cytopathie mitochondriale » et LBMR pour « Neuropathies optiques héréditaires »</t>
+  </si>
+  <si>
+    <t>CHU Angers</t>
+  </si>
+  <si>
+    <t>JMChaoDeLaBarca@chu-angers.fr</t>
+  </si>
+  <si>
+    <t>Notre service est adossé aux centres de références (maladies neurogénétiques et mitochondriales de l’adulte)  Il a une expertise pour l’étude des pathologies mitochondriales du fonctionnel à la génétique :  génome, séquencage Long read, épigénétique de l’ADN mitochondriale et étude fonctionnelle de la chaine respiratoire mitochondriale (oxygraphie, enzymologie, western Blot …) </t>
+  </si>
+  <si>
+    <t>https://www.chu-angers.fr/offre-de-soins/biochimie-et-biologie-moleculaire-133984.kjsp</t>
+  </si>
+  <si>
+    <t>Endocrinologie</t>
+  </si>
+  <si>
+    <t>Pathologies rares endocriniennes - LBMR « Dysthyroïdies: explorations hormonologique et moléculaire » et « néoplasies endocriniennes rares »</t>
+  </si>
+  <si>
+    <t>Notre service est adossé aux centres de références (maladies rares de la receptivité hormonale), notamment pour les dysthyroïdies (resistances, hyperthyroidies non autoimmunes, hypothyroïdies congénitales…) et les néoplasies endocriniennes multiples de type 2. Nous avons l’expertise  pour les analyses  :  génome, séquencage Long read, épigénétique et interférences analytiques.</t>
+  </si>
+  <si>
+    <t>Nantes</t>
+  </si>
+  <si>
+    <t>Grossesses pathologiques</t>
+  </si>
+  <si>
+    <t>LBMR - Marqueurs sériques maternels des grossesses pathologiques : Trisomie 21 fœtale &amp; pré-éclampsie</t>
+  </si>
+  <si>
+    <t>CHU Nantes</t>
+  </si>
+  <si>
+    <t>damien.masson@chu-nantes.fr ; aurore.catteau@chu-nantes.fr ; nolwenn.graveline@chu-nantes.fr ; alizee.violin@chu-nantes.fr</t>
+  </si>
+  <si>
+    <t>Dépistage de la Trisomie 21 fœtale au 1er trimestre de la grossesse par les marqueurs sériques maternels et Identification des patientes à forte probabilité de pré-éclampsie dès le 1er trimestre de la grossesse (dépistage combiné à celui de la Trisomie 21) ou à partir de la 20ème semaine d’aménorrhée selon l’association de critères cliniques (mesure du ratio sFlt-1/ PlGF).</t>
+  </si>
+  <si>
+    <t>Dépistage, Trisomie 21, pré-éclampsie</t>
+  </si>
+  <si>
+    <t>LBMR - Biochimie endocrine : axe surrénalien - Diagnostic et suivi des pathologies endocriniennes rares d’origine surrénalienne ou hypophysaire.</t>
+  </si>
+  <si>
+    <t>kalyane.bach@chu-nantes.fr ; nolwenn.graveline@chu-nantes.fr ; alizee.violin@chu-nantes.fr</t>
+  </si>
+  <si>
+    <t>Exploration biologiques spécialisées (stimulation ou freinage, cathétérismes veineux surrénaliens ou des sinus pétreux) des pathologies surrénaliennes réalisées en concertation avec les praticiens des Services d’Endocrinologie Adulte et Pédiatrique, de Radiologie Interventionnelle et d’Oncologie et de Chirurgie Endocrinienne du CHU de Nantes. Le Laboratoire d’Hormonologie est associé au Centre de Compétence des Maladies Endocriniennes rares de l’enfant et de l’adulte du CHU de Nantes (Dr Sabine Baron (réseau FIRENDO), Drs Delphine Drui et Maëlle Le Bras (Réseaux RENATEN et ENDOCAN-COMETE). Le laboratoire est en lien avec l’association de patients souffrant de pathologies surrénaliennes (Association SURRENALES).</t>
+  </si>
+  <si>
+    <t>Cushing, HAP (hyperaldostéronisme primaire), HCS (hyperplasie congénitale des surrénales), hyperandrogénie, Phéochromocytome</t>
+  </si>
+  <si>
+    <t>LBMR - Biochimie des gammapathies monoclonales </t>
+  </si>
+  <si>
+    <t>Thomas.dejoie@chu-nantes.fr ; Helene.caillon@chu-nantes.fr ; Alizee.violin@chu-nantes.fr ; marc.denis@chu-nantes.fr</t>
+  </si>
+  <si>
+    <t>Biologistes référents de l’intergroupe francophone du myélome (IFM), Laboratoire central pour les essais cliniques d’enregistrement promus par l’IFM depuis 2015. Plateforme Maldi tof EXENT exploration des gammapathies.</t>
+  </si>
+  <si>
+    <t>Oncogénétique</t>
+  </si>
+  <si>
+    <t>LBMR – Génétique somatique des Tumeurs solides</t>
+  </si>
+  <si>
+    <t>bp-oncogenomique@chu-nantes.fr ; marc.denis@chu-nantes.fr ; chloe.sauzay@chu-nantes.fr</t>
+  </si>
+  <si>
+    <t>Le Laboratoire de Biologie Médicale de Référence « Génétique somatique des tumeurs solides » réalise des analyses moléculaires à visée diagnostique, pronostique et théranostique sur les tumeurs solides. Ces analyses sont effectuées à partir d’ADN et d’ARN tumoraux extraits de tissus fixés au formol et inclus en paraffine (FFPE), ou à partir de plasma (ADN tumoral circulant).Les profils moléculaires ainsi obtenus, permettent d’orienter les stratégies thérapeutiques personnalisées.</t>
+  </si>
+  <si>
+    <t>Oncogénomique, ADN tumoral circulant, marqueurs théranostiques, DNAseq, RNAseq</t>
+  </si>
+  <si>
+    <t>Analyse protéinologique spécialisée du Liquide cérébro-spinal incluant l’exploration des pathologies inflammatoires et neurodégénératives pour le GHT, et diagnostic biologique des brèches méningées au niveau national.</t>
+  </si>
+  <si>
+    <t>edith.bigot@chu-nantes.fr ; maxime.carpentier-A030746@chu-nantes.fr ; pierreolivier.bertho@chu-nantes.fr</t>
+  </si>
+  <si>
+    <t>Exploration dans le cadre des pathologies inflammatoires (dosage des protéines : albumine, Immunoglobulines, Chaînes légères libres Kappa et Lambda, calcul des index et recherche de bandes oligoclonales d’IgG par isoélectrofocalisation.</t>
+  </si>
+  <si>
+    <t>Exploration des pathologies neurodégénératives : dosages dans le LCS des peptides amyloïdes beta 1-40, 1-42, protéines TAU totale et hyperphosphorylées, phénotypage apoE.</t>
+  </si>
+  <si>
+    <t>Brêches ostéo-méningées : sur microprélèvement (10 µL) recherche par électrophorèse et immuno-transfert de beta2 transferrine (spécifique du LCS)</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t>LBMR : Biochimie des pathologies rénales et des pathologies lithiasiques urinaires (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>Hospices Civils de Lyon / Service de Biochimie et Biologie Moléculaire Multisites</t>
+  </si>
+  <si>
+    <t>claire.goursaud@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic moléculaire pré et post-natal de pathologies rénales constitutionnelles dont les pathologies kystiques et la maladie lithiasique familiale. Diagnostic phénotypique des tubulopathies et de la lithiase urinaire et analyse morpho-constitutionnelle des calculs urinaires.</t>
+  </si>
+  <si>
+    <t>https://www.chu-lyon.fr/laboratoire-biologie</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1- LBMR : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Syndrome métabolique, dyslipidémies (phénotype et génotype), insulinorésistance (phénotype et génotype) et pathologies nutritionnelles et digestives </t>
+    </r>
+  </si>
+  <si>
+    <t>2- Unité Médicale Dyslipidémies, Dysfonctions Nutritionnelles et Digestives (D2ND)</t>
+  </si>
+  <si>
+    <t>emilie.blond@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic phénotypique et/ou génotypique des patients atteints de dyslipidémies, de diabètes, d’obésités, et/ou dysmétaboliques nécessitant l’exploration de marqueurs de l’insulino-sécrétion, l’insulino-résistance et de la satiété </t>
+  </si>
+  <si>
+    <t>Nutrition, Cardiovasculaire, Diabète et Métabolisme</t>
+  </si>
+  <si>
+    <t>Laboratoire CarMeN Cardiovasculaire, Métabolisme, Diabète et Nutrition, Unités INSERM U1060, INRAE U1397, Université Lyon1 / Centre de Recherche en Nutrition Humaine Rhône Alpes (CRNH) / Centre Européen Nutrition et Santé (CENS)</t>
+  </si>
+  <si>
+    <t>Au sein de la plateforme METANUTRIBIOTA, de l’unité CarMeN et du CRNH, expertise dans l’exploration biochimique des mécanismes de l’insulino-résistance, du diabète, des dyslipidémies, de la stéatose hépatique et de l’interaction microbiote intestinal/nutrition/maladies métaboliques.</t>
+  </si>
+  <si>
+    <t>https://carmen.univ-lyon1.fr/</t>
+  </si>
+  <si>
+    <t>LBMR  : axe surrénalien, axe gonadotrope (dont les pathologies de la différenciation sexuelle et exploration des infertilités) (phénotype et génotype); axe thyréotrope, axe somatotrope, pathologies hypophysaires, Pathologies du sommeil (phénotype). </t>
+  </si>
+  <si>
+    <t>florence.roucher@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic des pathologies hormonales fréquentes et rares, du phénotype au génotype</t>
+  </si>
+  <si>
+    <t>Thématique : Surrénales Gonades</t>
+  </si>
+  <si>
+    <t>Unité 1208 INSERM Institut Cellules Souches Cerveau SBRI, équipe Pluripotent Stem Cell in mammals </t>
+  </si>
+  <si>
+    <t>Développement d’organoïdes testiculaires et de cellules stéroïdogènes like à partir de cellules souches pluripotentes induites de patients, afin d'étudier le développement des gonades et des glandes surrénales ainsi que les troubles de la fertilité. Modélisation des troubles du développement sexuel et de l'insuffisance surrénalienne congénitale par technologie CRISPR/Cas9. </t>
+  </si>
+  <si>
+    <t>https://sbri.fr/ </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thématique : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pathologies Cancéreuses</t>
+    </r>
+  </si>
+  <si>
+    <t>jonathan.lopez@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Génétique somatique (WGS, WTS, méthylome, lpWGS, Nanopore, fragmentomique…).et marqueurs biochimiques des tumeurs solides (cancers fréquents/rares) : diagnostic, personnalisation thérapeutique, maladie résiduelle. Approches moléculaires globales et innovantes sur tumeurs et biopsies liquides. Affiliation à plusieurs LBMR d’oncologie molculaire</t>
+  </si>
+  <si>
+    <t>Radiobiologie Cellulaire et Moléculaire</t>
+  </si>
+  <si>
+    <t>UMR CNRS 5822 IP2I – équipe RCM</t>
+  </si>
+  <si>
+    <t>claire.rodriguez-lafrasse@univ-lyon1.fr</t>
+  </si>
+  <si>
+    <t>Mécanismes cellulaires et moléculaires spécifiquement impliqués dans la réponse tumorale (cancer des VADS) aux radiothérapies (RT) innovantes (hadronthérapie par ions carbone, photons, hélium ; radiothérapie Flash, IRM-LINAC) par rapport à la RT conventionnelle et prédiction de la réponse tumorale à la RT.</t>
+  </si>
+  <si>
+    <t>https://www.ip2i.in2p3.fr/equipes/(sante)</t>
+  </si>
+  <si>
+    <t>Plasticité tumorale dans le mélanome</t>
+  </si>
+  <si>
+    <t>Centre de Recherche en Cancérologie de Lyon (CRCL), UMR_INSERM U1052 / CNRS UMR5286</t>
+  </si>
+  <si>
+    <t>Plasticité phénotypique exacerbée des mélanomes cutanés à l’origine d’une résistance aux immunothérapies. Mécanismes transcriptionnels/ épigénétiques, hétérogénéité tumorale, interactions avec le microenvironnement immunitaire. Méthodes innovantes : scRNAseq, transcriptomique spatiale, ATACseq... Modèles in vitro/in vivo, échantillons humains.</t>
+  </si>
+  <si>
+    <t>https://www.crcl.fr/equipes-de-recherche/plasticite-tumorale-dans-le-melanome/</t>
+  </si>
+  <si>
+    <t>LBMR : Maladies héréditaires du métabolisme (phénotype et génotype) ; Maladies métaboliques à révélation anténatale : approche phénotypique et génotypique Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
+  </si>
+  <si>
+    <t>cecile.acquaviva-bourdain@chu-lyon.fr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostic génotypique et phénotypique des patients atteints de MHM (maladies du métabolisme intermédiaire et énergétique, maladies lysosomales, maladies peroxysomales…) en biochimie et en biologie moléculaire. </t>
+  </si>
+  <si>
+    <t>LBMR : Hémoglobinopathies et biochimie du globule rouge (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
+  </si>
+  <si>
+    <t>Recherche dans le domaine des maladies cardiovasculaires, du métabolisme, de la diabétologie et de la nutrition</t>
+  </si>
+  <si>
+    <t>Laboratoire CarMeN – INSERM U1060/ INRAE U1397/ Université Lyon 1</t>
+  </si>
+  <si>
+    <t>david.cheillan@chu-lyon.fr </t>
+  </si>
+  <si>
+    <t>Développement d’une plateforme de sphingolipidomique par spectrométrie de masse en tandem appliquée au phénotypage et à l’identification de biomarqueurs pour le diagnostic des maladies métaboliques.</t>
+  </si>
+  <si>
+    <t>Présentation - Laboratoire CarMeN Lyon </t>
+  </si>
+  <si>
+    <t>Thématique : Rhéologie sanguine et pathologies du globule rouge</t>
+  </si>
+  <si>
+    <t>Biologie Vasculaire du Globule Rouge (Laboratoire LIBM UR7424 ; UCBL))</t>
+  </si>
+  <si>
+    <t>philippe.joly@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Travail sur 3 thématiques principales : 1) hémoglobinopathies et autres maladies du globule rouge ; 2) effets de l’hypoxie aigue/chronique et 3) effets de l’exercice/activité physique. Nous avons étudié principalement la physiologie des globules rouges et les conséquences vasculaires dans le cadre de ces 3 thématiques pour répondre à des questionnements mécanistiques, cliniques ou pré-cliniques.</t>
+  </si>
+  <si>
+    <t>https://libm.univ-st-etienne.fr/fr/equipes/vbrbc/projet-vbrbc.html </t>
+  </si>
+  <si>
+    <t>Pathologies Neurologiques, musculaires et cardiaques</t>
+  </si>
+  <si>
+    <t>6 LMBR : Maladies neurodégénératives centrales (phénotype) ; Cardiomyopathies héréditaires ; Troubles du rythme cardiaque héréditaires ; Diagnostic génétique des maladies neurodégénératives à expansions (dont maladie de Huntington - MH, maladie de Steinert - DM1, dystrophie myotonique proximale - DM2 ou PROMM, maladie de Kennedy - SK) ; Diagnostic génétique des neuropathies périphériques de Charcot Marie et Tooth et apparentées ; Diagnostic génétique des myopathies</t>
+  </si>
+  <si>
+    <t>isabelle.quadrio@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Comprendre les mécanismes de neurodégénérescence cérébrale en développant des biomarqueurs protéiques et d’imagerie des maladies neurodégénératives, du modèle animal à l’étude clinique dans une approche translationnelle. </t>
+  </si>
+  <si>
+    <t> Mécanismes physiopathologiques d’agrégation des protéines impliquées dans les maladies neurodégénératives</t>
+  </si>
+  <si>
+    <t>Centre de Recherche en Neurosciences de Lyon (CNRL), Equipe BIORAN </t>
+  </si>
+  <si>
+    <t>Comprendre dans le contexte de la différenciation et de la maturation musculaire (fibres musculaires squelettiques ou cellules cardiaques), les mécanismes de réarrangements des cytosquelettes contrôlant l’expression du génome et donc le destin des cellules musculaires. </t>
+  </si>
+  <si>
+    <t>BIORAN | Centre de Recherche en Neurosciences de Lyon</t>
+  </si>
+  <si>
+    <t>Cardiologie</t>
+  </si>
+  <si>
+    <t>Mécanismes physiopathologique des cardiomyopathies héréditaires</t>
+  </si>
+  <si>
+    <t>Physiopathologie et génétique du neurone et du muscle (PGNM), Equipe Architecture du noyau</t>
+  </si>
+  <si>
+    <t>gilles.millat@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic et suivi des patients atteints de troubles neurocognitifs comme la Maladie d’Alzheimer et les maladies apparentées par des biomarqueurs protéiques et moléculaires.</t>
+  </si>
+  <si>
+    <t>Diagnostic des neuropathies périphériques, des cardiomyopathies et troubles du rythme héréditaire et des myopathies par biologie moléculaire (panels de gènes, techniques spécifiques ciblées pour les maladies à expansions). </t>
+  </si>
+  <si>
+    <t>GACHE - INMG - PGNM </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2386,6 +2946,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF0000CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF153142"/>
+      <name val="Noto Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C292F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2414,7 +3016,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2426,9 +3028,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2645,7 +3253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1"/>
@@ -2664,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -2685,7 +3293,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2697,7 +3305,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -2706,10 +3314,10 @@
         <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>49</v>
@@ -2726,13 +3334,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>50</v>
@@ -2741,13 +3349,13 @@
         <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2759,7 +3367,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>117</v>
@@ -2774,13 +3382,13 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -2792,7 +3400,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -2804,7 +3412,7 @@
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>54</v>
@@ -2823,7 +3431,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -2861,7 +3469,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -3041,7 +3649,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>40</v>
@@ -3122,7 +3730,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>60</v>
@@ -3145,7 +3753,7 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>45</v>
@@ -3232,13 +3840,13 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>70</v>
@@ -3267,7 +3875,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>70</v>
@@ -3296,7 +3904,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>70</v>
@@ -3319,13 +3927,13 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
@@ -3354,7 +3962,7 @@
         <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -3386,7 +3994,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>81</v>
@@ -3412,7 +4020,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>82</v>
@@ -3439,7 +4047,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
@@ -3466,7 +4074,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
@@ -3487,13 +4095,13 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -3514,13 +4122,13 @@
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>87</v>
@@ -3636,7 +4244,7 @@
         <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>99</v>
@@ -3659,13 +4267,13 @@
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>99</v>
@@ -3694,7 +4302,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>99</v>
@@ -3717,13 +4325,13 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>99</v>
@@ -3749,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>106</v>
@@ -3890,7 +4498,7 @@
         <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>13</v>
@@ -3899,7 +4507,7 @@
         <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>135</v>
@@ -3921,7 +4529,7 @@
         <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>15</v>
@@ -3930,7 +4538,7 @@
         <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>135</v>
@@ -3952,7 +4560,7 @@
         <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>140</v>
@@ -3961,7 +4569,7 @@
         <v>45</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>141</v>
@@ -3970,7 +4578,7 @@
         <v>142</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -3983,7 +4591,7 @@
         <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -3992,7 +4600,7 @@
         <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>141</v>
@@ -4014,7 +4622,7 @@
         <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>7</v>
@@ -4023,7 +4631,7 @@
         <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>144</v>
@@ -4045,7 +4653,7 @@
         <v>176</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
@@ -4054,7 +4662,7 @@
         <v>45</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>147</v>
@@ -4076,16 +4684,16 @@
         <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>150</v>
@@ -4107,7 +4715,7 @@
         <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>15</v>
@@ -4116,7 +4724,7 @@
         <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>150</v>
@@ -4138,16 +4746,16 @@
         <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>147</v>
@@ -4169,16 +4777,16 @@
         <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
@@ -4200,7 +4808,7 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>157</v>
@@ -4209,7 +4817,7 @@
         <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>158</v>
@@ -4231,7 +4839,7 @@
         <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>13</v>
@@ -4240,7 +4848,7 @@
         <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>161</v>
@@ -4262,7 +4870,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -4271,7 +4879,7 @@
         <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>163</v>
@@ -4280,7 +4888,7 @@
         <v>159</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4293,16 +4901,16 @@
         <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>164</v>
@@ -4324,7 +4932,7 @@
         <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>157</v>
@@ -4333,7 +4941,7 @@
         <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>167</v>
@@ -4355,7 +4963,7 @@
         <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>157</v>
@@ -4364,7 +4972,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>163</v>
@@ -4386,7 +4994,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>157</v>
@@ -4395,7 +5003,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>163</v>
@@ -4417,7 +5025,7 @@
         <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>15</v>
@@ -4426,7 +5034,7 @@
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>163</v>
@@ -4448,7 +5056,7 @@
         <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>15</v>
@@ -4457,16 +5065,16 @@
         <v>44</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -4479,7 +5087,7 @@
         <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>15</v>
@@ -4488,19 +5096,19 @@
         <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -4512,7 +5120,7 @@
         <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -4521,14 +5129,14 @@
         <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -4538,14 +5146,14 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>178</v>
@@ -4557,50 +5165,46 @@
         <v>180</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I64" s="9"/>
-      <c r="J64" s="5" t="s">
-        <v>181</v>
-      </c>
+      <c r="J64" s="5"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="H65" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="5" t="s">
-        <v>185</v>
-      </c>
+      <c r="J65" s="5"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
     <row r="66" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
@@ -4610,16 +5214,16 @@
         <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -4629,7 +5233,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -4639,16 +5243,16 @@
         <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F67" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -4658,124 +5262,120 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="5" t="s">
-        <v>194</v>
-      </c>
+      <c r="J68" s="5"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D69" s="12" t="s">
+      <c r="A69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="12" t="s">
-        <v>347</v>
+      <c r="E69" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>196</v>
+        <v>376</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="I69" s="13"/>
-      <c r="J69" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
+        <v>378</v>
+      </c>
+      <c r="I69" s="12"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
       <c r="F70" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G70" s="11"/>
+        <v>377</v>
+      </c>
+      <c r="G70" s="13"/>
       <c r="H70" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="I70" s="13"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="12"/>
-      <c r="L70" s="12"/>
-      <c r="M70" s="12"/>
+        <v>379</v>
+      </c>
+      <c r="I70" s="12"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="11"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="I71" s="13"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="I71" s="12"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="1"/>
@@ -4785,26 +5385,26 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -4814,7 +5414,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
@@ -4824,13 +5424,13 @@
         <v>45</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -4841,7 +5441,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
@@ -4851,28 +5451,26 @@
         <v>44</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="I75" s="1"/>
-      <c r="J75" s="5" t="s">
-        <v>207</v>
-      </c>
+      <c r="J75" s="5"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
@@ -4882,28 +5480,26 @@
         <v>44</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I76" s="1"/>
-      <c r="J76" s="5" t="s">
-        <v>207</v>
-      </c>
+      <c r="J76" s="5"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
@@ -4913,16 +5509,16 @@
         <v>45</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -4932,7 +5528,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
@@ -4942,16 +5538,16 @@
         <v>44</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -4961,26 +5557,26 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -4990,7 +5586,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
@@ -5000,47 +5596,45 @@
         <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="5" t="s">
-        <v>227</v>
-      </c>
+      <c r="J80" s="5"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5050,26 +5644,26 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5079,26 +5673,26 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5108,7 +5702,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
@@ -5118,28 +5712,26 @@
         <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I84" s="1"/>
-      <c r="J84" s="5" t="s">
-        <v>241</v>
-      </c>
+      <c r="J84" s="5"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -5149,16 +5741,16 @@
         <v>45</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5168,26 +5760,26 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5197,26 +5789,26 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5226,7 +5818,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
@@ -5236,16 +5828,16 @@
         <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5255,26 +5847,26 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5284,7 +5876,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -5294,16 +5886,16 @@
         <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5313,29 +5905,29 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5344,26 +5936,26 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -5373,26 +5965,26 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -5402,7 +5994,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
@@ -5412,13 +6004,13 @@
         <v>45</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -5429,7 +6021,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -5439,16 +6031,16 @@
         <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -5458,26 +6050,26 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F96" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>278</v>
-      </c>
       <c r="H96" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -5487,7 +6079,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
@@ -5497,16 +6089,16 @@
         <v>44</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -5516,29 +6108,29 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -5547,7 +6139,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
@@ -5557,16 +6149,16 @@
         <v>45</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -5576,7 +6168,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
@@ -5586,16 +6178,16 @@
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -5605,26 +6197,26 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -5634,7 +6226,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
@@ -5644,16 +6236,16 @@
         <v>44</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -5663,26 +6255,26 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -5692,26 +6284,26 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -5721,7 +6313,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
@@ -5731,16 +6323,16 @@
         <v>44</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -5750,26 +6342,26 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -5779,26 +6371,26 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -5808,26 +6400,26 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -5837,7 +6429,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
@@ -5847,16 +6439,16 @@
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -5866,7 +6458,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
@@ -5876,16 +6468,16 @@
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -5895,7 +6487,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
@@ -5905,16 +6497,16 @@
         <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -5924,7 +6516,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
@@ -5934,16 +6526,16 @@
         <v>45</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -5953,26 +6545,26 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -5982,26 +6574,26 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6011,7 +6603,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
@@ -6021,16 +6613,16 @@
         <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6040,26 +6632,26 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6069,26 +6661,26 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -6098,26 +6690,26 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -6125,113 +6717,1114 @@
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
     </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J119" s="14"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G120" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J120" s="14"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J121" s="14"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="I122" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="H123" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="J128" s="1"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="J129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="J130" s="1"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J132" s="1"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A135" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B135" s="11"/>
+      <c r="C135" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="I135" s="11"/>
+      <c r="J135" s="11"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I136" s="11"/>
+      <c r="J136" s="11"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="I137" s="11"/>
+      <c r="J137" s="11"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B138" s="9">
+        <v>1</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A139" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="B139" s="12">
+        <v>2</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="G139" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="H139" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="I139" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="J139" s="11"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="11"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F140" s="11"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="12"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="11"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B141" s="9">
+        <v>2</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="J141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B142" s="9">
+        <v>3</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B143" s="9">
+        <v>3</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B144" s="9">
+        <v>4</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J144" s="1"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B145" s="9">
+        <v>4</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B146" s="9">
+        <v>4</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="J146" s="1"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B147" s="9">
+        <v>5</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J147" s="1"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B148" s="9">
+        <v>5</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J148" s="1"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B149" s="9">
+        <v>5</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F149" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="J149" s="1"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B150" s="9">
+        <v>5</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="J150" s="1"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B151" s="9">
+        <v>6</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B152" s="9">
+        <v>6</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A153" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="B153" s="12">
+        <v>6</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E153" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="F153" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="G153" s="18" t="s">
+        <v>600</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="I153" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="J153" s="19"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A154" s="11"/>
+      <c r="B154" s="12"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+      <c r="G154" s="18"/>
+      <c r="H154" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="I154" s="18"/>
+      <c r="J154" s="19"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
+  <mergeCells count="38">
+    <mergeCell ref="F153:F154"/>
+    <mergeCell ref="G153:G154"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="J153:J154"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D153:D154"/>
+    <mergeCell ref="E153:E154"/>
+    <mergeCell ref="F135:F137"/>
+    <mergeCell ref="G135:G137"/>
+    <mergeCell ref="I135:I137"/>
+    <mergeCell ref="J135:J137"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="A135:A137"/>
+    <mergeCell ref="B135:B137"/>
+    <mergeCell ref="C135:C137"/>
+    <mergeCell ref="D135:D137"/>
+    <mergeCell ref="E135:E137"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="C69:C71"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:E71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{D5A287CC-F3DB-AB4E-A6A7-30A455C45191}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{DAC52750-6C95-424D-8E24-E5E1F57165D8}"/>
-    <hyperlink ref="G4" r:id="rId3" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{7D231BCA-F4ED-B340-AE5F-F713A44F46D8}"/>
-    <hyperlink ref="I4" r:id="rId4" xr:uid="{853B4FE4-A56B-B345-BE9E-5B9439A0E1D1}"/>
-    <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{E1C82F55-9724-AF48-9F9F-94DE117CA57A}"/>
-    <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{6F599EA3-6C18-6A4F-B83B-B1BFF986C046}"/>
-    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{EAD6269A-B1A9-3249-AE44-CF813FD72994}"/>
-    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{ACE60A29-4C84-BA40-AF8F-A9895BC6E74B}"/>
-    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{077906EC-AF41-484C-BE29-C796CEC91A8D}"/>
-    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{7F98454A-D76F-3748-8AD5-60659E5EAFBA}"/>
-    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{71878D64-C723-CD4E-9ED3-7AAE7DE3FB72}"/>
-    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{8A1B2178-5941-124C-90C0-4943CC9BDCEC}"/>
-    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{4C62C2C0-8C0C-1D46-A60C-82DF34F952F4}"/>
-    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{19463E8C-16D5-E94E-A25F-50BD3376BF29}"/>
-    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{9464A30E-9537-D043-8FC0-34D4F7AC08A9}"/>
-    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{528A6581-D640-D34C-9CE0-F2D6EAFEBF0C}"/>
-    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{3A9500E0-D9C7-044C-94FA-6EAFF1877A60}"/>
-    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{22B1A9F9-3952-3442-A26E-6A492D52264D}"/>
-    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{7716A5C2-E7DD-1E4E-B60E-89CDB6EB7DDA}"/>
-    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{72CEB3A0-2D44-8B45-9EFB-7375660C28BA}"/>
-    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{EBC7FDA7-05A8-F944-9B37-78E02BFF24AB}"/>
-    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{89926BFF-4008-3C42-90A5-053D950841FA}"/>
-    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{994FF440-58C5-754E-B36B-DBE9D3B2F6C4}"/>
-    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{ABE7FF62-E065-EE40-AA0E-FB9772F7F13E}"/>
-    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{75336746-604B-4D4C-829B-0A6CCAC91E2B}"/>
-    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{D2AF785F-2C5B-044C-8CC8-354D650CF1A0}"/>
-    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{3A5FD94E-4E6A-7A4C-998E-FB408BBDCB2A}"/>
-    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{577081D2-B82E-0344-B7D8-1E6C685CA5D2}"/>
-    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{FD520663-2FF9-E44C-B224-5F2839AC7306}"/>
-    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{839F5651-D675-2D4A-A466-F1A9183DAC56}"/>
-    <hyperlink ref="I42" r:id="rId31" xr:uid="{EC60B6D3-ABB8-7143-8183-075A2D572C9A}"/>
-    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{126CA9BA-E2D8-6D4C-BB0B-45DC651BF7A8}"/>
-    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{6906BA22-3157-C446-9487-B153C6C57BBD}"/>
-    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{6BE15206-19E6-474B-A7B4-1234187D872C}"/>
-    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{E1D0A185-2D5A-7345-810B-B87D6933CFFA}"/>
-    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{A6E0244C-C880-FA4C-88F4-F241F2548D0D}"/>
-    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{19E6FC41-47A2-124C-94D9-570797D95A7B}"/>
-    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{02CA18D2-ECA0-B04D-9CAF-0D5CE592B0EF}"/>
-    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{B5E1A3DB-460F-864A-A9A9-BB9D592A7140}"/>
-    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{44C9CD03-631E-5B45-934A-8B2AE14F1C6C}"/>
-    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{684471D6-7354-4F4A-A97B-627FB94EA97F}"/>
-    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{6694A3DF-1B07-AD4A-BF16-79346CC23557}"/>
-    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{F39DA42A-0EF4-3740-84E1-A6A62B0769F3}"/>
-    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{35083460-75F3-9243-8C23-8B1E08FC4CC1}"/>
-    <hyperlink ref="I62" r:id="rId45" xr:uid="{62BD73B8-0204-3D4E-9C38-6CD591F31713}"/>
-    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{4A02BDDE-6857-3A46-9924-3164A036D883}"/>
-    <hyperlink ref="J64" r:id="rId47" xr:uid="{CD276749-77DC-A647-B15E-C84583931DE6}"/>
-    <hyperlink ref="G65" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{F30ED4AE-EF4C-6141-852E-E585A269EEB4}"/>
-    <hyperlink ref="J65" r:id="rId49" xr:uid="{B7BDF381-9DA8-3D41-8EE7-B3E118953DFD}"/>
-    <hyperlink ref="G66" r:id="rId50" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{946DE2A5-3133-ED45-88A9-7DDDE88DF57E}"/>
-    <hyperlink ref="G67" r:id="rId51" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{205DA997-52F9-5649-8BA9-87468137FCE3}"/>
-    <hyperlink ref="G68" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{5E9E5653-314D-EB49-8F35-728C96CD8D56}"/>
-    <hyperlink ref="J68" r:id="rId53" xr:uid="{527F5591-0038-4B49-8961-80ACBC03C6ED}"/>
-    <hyperlink ref="G69" r:id="rId54" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{765C5C5A-5F47-F94A-A798-378E345E63AC}"/>
-    <hyperlink ref="J69" r:id="rId55" xr:uid="{BD344E66-F045-3A48-A001-A98E3A0C2093}"/>
-    <hyperlink ref="G72" r:id="rId56" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{2C600862-D1B8-0F48-9490-F19F8E219136}"/>
-    <hyperlink ref="G73" r:id="rId57" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{9636385F-A5ED-854A-A340-C7BF70887E67}"/>
-    <hyperlink ref="G74" r:id="rId58" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{D08D7EBC-31C7-D64A-A9CD-2AAAEBF11A46}"/>
-    <hyperlink ref="J75" r:id="rId59" xr:uid="{0E4DBD39-E9AA-7844-8123-AE0D946470A4}"/>
-    <hyperlink ref="J76" r:id="rId60" xr:uid="{27C93922-39FC-A248-B928-04EA23FBD317}"/>
-    <hyperlink ref="G78" r:id="rId61" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{6B4459B5-0E17-4340-99F7-A07417BE8132}"/>
-    <hyperlink ref="G80" r:id="rId62" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{D02C05EB-CBD5-D442-8A7D-5B63F3F6A8FE}"/>
-    <hyperlink ref="J80" r:id="rId63" xr:uid="{AED65EBB-80E5-4C4D-92B8-EC77803B3DBE}"/>
-    <hyperlink ref="G81" r:id="rId64" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{02543C15-B1EA-EE4E-8F6A-62AB8F3C6927}"/>
-    <hyperlink ref="G82" r:id="rId65" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{2399221C-A872-9C4F-917A-7F67F874D35B}"/>
-    <hyperlink ref="J84" r:id="rId66" xr:uid="{D76E39F6-8744-9148-B80B-6F8F34458C1B}"/>
-    <hyperlink ref="G91" r:id="rId67" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{753A0B41-A099-FF4C-85A2-E76B90277A0A}"/>
-    <hyperlink ref="I91" r:id="rId68" xr:uid="{8F5139B4-57DE-3A4A-B1A1-77E7442F6741}"/>
-    <hyperlink ref="G92" r:id="rId69" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{DE5E29A6-295C-B641-8145-EA258E0CB6C2}"/>
-    <hyperlink ref="G93" r:id="rId70" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{90F3B849-B036-2F4D-9CC0-048B2C8269A7}"/>
-    <hyperlink ref="G96" r:id="rId71" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{04E52A32-0705-D04F-AC1E-0EE76FC197C8}"/>
-    <hyperlink ref="G97" r:id="rId72" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{F53877F0-DC05-A349-80EC-5617F1503152}"/>
-    <hyperlink ref="G98" r:id="rId73" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{BC597FB6-502E-DF46-9A1D-3B3154018F19}"/>
-    <hyperlink ref="I98" r:id="rId74" xr:uid="{9A76F5C3-635B-A94C-AA00-B5B412F071BC}"/>
-    <hyperlink ref="G99" r:id="rId75" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{1541119C-C700-5846-A13A-470E49164C2E}"/>
-    <hyperlink ref="G100" r:id="rId76" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{BDE8E49B-A252-E84B-A17B-712891D4F28F}"/>
-    <hyperlink ref="G101" r:id="rId77" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{5CD5710A-5F42-7F47-A40D-80550F005597}"/>
-    <hyperlink ref="G102" r:id="rId78" display="mailto:sjaisson@chu-reims.fr" xr:uid="{F24AD5B8-1A92-7B4C-809C-EFF853926847}"/>
-    <hyperlink ref="G103" r:id="rId79" display="mailto:sjaisson@chu-reims.fr" xr:uid="{147B9E7F-DB97-604F-B2E7-83CF926F535D}"/>
-    <hyperlink ref="G104" r:id="rId80" display="mailto:dmarot@chu-reims.fr" xr:uid="{E2B8F2F5-F9A2-2740-9528-4E766948A6C2}"/>
-    <hyperlink ref="G105" r:id="rId81" display="mailto:lramont@chu-reims.fr" xr:uid="{1AB0B99B-A776-D649-904D-E73F8A612B1C}"/>
-    <hyperlink ref="G106" r:id="rId82" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{AA5771E3-EC46-BD47-8365-0DA3FF3B493E}"/>
-    <hyperlink ref="G107" r:id="rId83" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{1343F3CE-1879-4746-B10C-F980B6C339F9}"/>
-    <hyperlink ref="G108" r:id="rId84" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{399B020A-2DBF-CC42-8866-B9A1531D4E18}"/>
-    <hyperlink ref="G109" r:id="rId85" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{8D68F755-110A-DD43-A4E3-1FD19C076FA0}"/>
-    <hyperlink ref="G110" r:id="rId86" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{DD44DAE1-8771-CB4D-A8F1-3FF172D6E9C1}"/>
-    <hyperlink ref="G113" r:id="rId87" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{6ADBC28F-FFC7-394B-9361-1240407E4F1D}"/>
-    <hyperlink ref="G114" r:id="rId88" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{42CBB318-E1DB-6149-B14F-E36D541EB65A}"/>
-    <hyperlink ref="G115" r:id="rId89" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{6D6BE7BB-C231-2749-8025-8C9BB55B6545}"/>
-    <hyperlink ref="G116" r:id="rId90" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{36DB08BF-3C8D-EA4E-A459-A6053CE9A5F3}"/>
-    <hyperlink ref="G117" r:id="rId91" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{46966F6C-B2E2-AB46-B36E-0290DA921865}"/>
-    <hyperlink ref="G118" r:id="rId92" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{626800B6-221C-A34D-977C-3F340982B5E2}"/>
+    <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{6558C59A-CBC3-C44B-BF9F-F7B6D9255B4D}"/>
+    <hyperlink ref="G4" r:id="rId3" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{E011817A-E213-9B45-8911-31DF8BC24C35}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{BAAAF0CB-3D5A-5949-A37D-A2C50B731AF0}"/>
+    <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{02C0CB78-D29E-3647-B6CB-37D7CECADEFF}"/>
+    <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{B179A81E-13D4-BA4C-AA82-773B4AF2D1E7}"/>
+    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{19818837-D83A-EF46-9A87-56DA857E21BF}"/>
+    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{404568B7-5E84-374C-86CF-5AD4367A7135}"/>
+    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{56D59BBB-465E-5641-A9F7-F2E5A28229DE}"/>
+    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{4E0E266F-A36A-534A-B732-B257A8710410}"/>
+    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{238F2984-E507-AD4C-9ECF-593475C4AD53}"/>
+    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{59075E53-0EBC-4847-9B63-F640FE924229}"/>
+    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{FD096503-D7B9-264C-BCDB-6BD7CB031C27}"/>
+    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{6018113E-52E5-C546-A726-3F07B4FE62D1}"/>
+    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{11482541-6756-4F49-BF84-994EA57212DF}"/>
+    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{DAEFBA44-5260-BA46-A86D-12F5080D70ED}"/>
+    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{85EE1029-98D3-FD47-9068-97CB0579190C}"/>
+    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{97E273A2-52B9-3D40-8872-1FDA66D1E846}"/>
+    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{9ACC63ED-843A-1045-B9B4-12C07C6CEEF8}"/>
+    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{E44DE2B2-25F7-B24B-A4C8-DB3BCCB7115A}"/>
+    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{C52AC72E-5EC3-8F41-98E3-28B2046ECD73}"/>
+    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{C417B978-A9E9-5447-B082-5172C07882E5}"/>
+    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{01A97F3F-1FE0-EC4D-99BE-5C9365E3A43D}"/>
+    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{5A0CDA27-8A97-3B48-B26C-414861879147}"/>
+    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{1F8902C9-7758-2940-B6B9-A168EDA21EAF}"/>
+    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{929EE593-D0FD-D445-B1BA-A3F8FDE6676B}"/>
+    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{F8EAC02E-BC4B-1743-837D-130A329FD052}"/>
+    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{234156F7-C14A-5241-8C74-AC721D0B56D3}"/>
+    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{4104F0D0-6CA0-7745-9468-257A4D0EB98A}"/>
+    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{B3F0F384-6218-3C46-94BE-75DF28DEDE7D}"/>
+    <hyperlink ref="I42" r:id="rId31" xr:uid="{0003CCF9-EA24-0144-80EF-A2FF95FFB6BB}"/>
+    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{8C451BC4-2DFB-5349-809D-05DE4C13DC67}"/>
+    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{455F44C0-7170-FB4F-8C6C-AB8C917AA32A}"/>
+    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{93ECACD7-0694-B648-AFEC-19945C5C57B3}"/>
+    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{E3A16A9D-DB36-2242-8C7D-12538308719E}"/>
+    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{04B47570-CEC1-044B-AC1A-8CBC673D5394}"/>
+    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{E10E3A24-FD55-3742-8FB8-E26FA664F94B}"/>
+    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{A8019C87-9474-4640-BCD9-2055202E563E}"/>
+    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{0F757E56-F0FF-2F42-BF04-27A891E0C555}"/>
+    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{EE7E9BD7-2E97-284D-967F-980B6482DBBE}"/>
+    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{8F52C470-C988-F24E-80D8-2BB657183BDB}"/>
+    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{46B2D7A6-145C-D64A-965C-67B6F6E3EC45}"/>
+    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{B6355616-C748-2843-B2A4-23E1CD69DD85}"/>
+    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{A28932E3-6128-D94F-93FF-5ACBF7A494B9}"/>
+    <hyperlink ref="I62" r:id="rId45" xr:uid="{B7B830C0-9819-CF4F-B723-139CB3C06E36}"/>
+    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{FFE59264-E4BA-9E44-B049-3C100E12BAA2}"/>
+    <hyperlink ref="G65" r:id="rId47" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{E38C53B5-D9E5-BF46-B199-B3E05A4ECBDD}"/>
+    <hyperlink ref="G66" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{CB824271-CE19-BC43-984A-01DFAF3C5B8E}"/>
+    <hyperlink ref="G67" r:id="rId49" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{179CFA47-2DA9-6F47-BACD-C3795C2639BA}"/>
+    <hyperlink ref="G68" r:id="rId50" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{EAEA8176-0963-7B40-9B2E-6B1CD4350D39}"/>
+    <hyperlink ref="G69" r:id="rId51" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{41EC90D8-78AD-1347-B375-8A9B98A00B2F}"/>
+    <hyperlink ref="G72" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{2DCD5A92-89BD-AC41-BE57-66B810FFA4A0}"/>
+    <hyperlink ref="G73" r:id="rId53" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{B2BCC955-005F-2F46-9B3A-23D752748141}"/>
+    <hyperlink ref="G74" r:id="rId54" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{D5E0083D-BEBA-DE4D-8DDC-F8DCD6348245}"/>
+    <hyperlink ref="G78" r:id="rId55" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{071E93FF-793D-0C4D-8ACA-64C68480C477}"/>
+    <hyperlink ref="G80" r:id="rId56" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{2E60772F-7DD4-D840-B17D-D87298E8D727}"/>
+    <hyperlink ref="G81" r:id="rId57" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{E9A03AF6-835B-864C-B71C-4627011D122A}"/>
+    <hyperlink ref="G82" r:id="rId58" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{F1A3246B-6EA8-364A-9FFC-4DB1BD34757B}"/>
+    <hyperlink ref="G91" r:id="rId59" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{BACD0B47-68EA-6047-9EBB-25E94902B24A}"/>
+    <hyperlink ref="I91" r:id="rId60" xr:uid="{74EED5C1-17AE-2E4A-9F07-DC464F938DA3}"/>
+    <hyperlink ref="G92" r:id="rId61" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{6D04C2AF-9625-3442-ADF8-CD0024E1FA55}"/>
+    <hyperlink ref="G93" r:id="rId62" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{7B7A75DE-8938-2045-8EB3-81788847B8C9}"/>
+    <hyperlink ref="G96" r:id="rId63" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{E307BDF4-2C0A-F94F-97AF-C5C43BCA00CA}"/>
+    <hyperlink ref="G97" r:id="rId64" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{0C78F5DE-A083-0742-B61B-C56D7084F18D}"/>
+    <hyperlink ref="G98" r:id="rId65" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{63EA7B8F-206E-E843-A40E-20993359E6D5}"/>
+    <hyperlink ref="I98" r:id="rId66" xr:uid="{74FEA717-1429-7B46-B57E-05A7EEA92161}"/>
+    <hyperlink ref="G99" r:id="rId67" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{7CFF7B10-439A-5D41-A23B-221F96517AF4}"/>
+    <hyperlink ref="G100" r:id="rId68" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{6C1FBD82-1CBF-7641-BBD3-F135C24FB0A0}"/>
+    <hyperlink ref="G101" r:id="rId69" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{B97089C4-568E-C04A-A7DF-3CE2E4364FAC}"/>
+    <hyperlink ref="G102" r:id="rId70" display="mailto:sjaisson@chu-reims.fr" xr:uid="{82FFFC16-2B6E-EE46-B62E-3B449DBF62F4}"/>
+    <hyperlink ref="G103" r:id="rId71" display="mailto:sjaisson@chu-reims.fr" xr:uid="{03ABDE49-B71A-114B-BBB0-4385451EA80F}"/>
+    <hyperlink ref="G104" r:id="rId72" display="mailto:dmarot@chu-reims.fr" xr:uid="{914E30D8-AE96-B146-AE96-A665020529BE}"/>
+    <hyperlink ref="G105" r:id="rId73" display="mailto:lramont@chu-reims.fr" xr:uid="{4EAA1429-669C-404A-B2EA-0C34ACC3BF21}"/>
+    <hyperlink ref="G106" r:id="rId74" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{98B90DDB-72C1-084D-9498-7CD8298183A4}"/>
+    <hyperlink ref="G107" r:id="rId75" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{84031370-A25E-DA46-9109-9E603E92176E}"/>
+    <hyperlink ref="G108" r:id="rId76" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{49C350B4-6874-1649-919A-BC1C4D8764E2}"/>
+    <hyperlink ref="G109" r:id="rId77" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{B17F1D67-CE4D-F547-88E0-DADEC10457F8}"/>
+    <hyperlink ref="G110" r:id="rId78" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{4955350F-AD67-2D49-AB6D-3BCEB89B72ED}"/>
+    <hyperlink ref="G113" r:id="rId79" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{284F1AAC-C96E-4741-85C2-FE59EFD6D21A}"/>
+    <hyperlink ref="G114" r:id="rId80" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{25612B46-6B22-A74D-8FCA-F5C470BB17BE}"/>
+    <hyperlink ref="G115" r:id="rId81" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{BD192653-5DC9-0E48-85F2-420E7B710C1D}"/>
+    <hyperlink ref="G116" r:id="rId82" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{5C1F7FBB-0230-2240-BD70-9EDC6C0A085C}"/>
+    <hyperlink ref="G117" r:id="rId83" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{BF20034E-2F10-4D4F-A4C3-CB8CF25AFA9F}"/>
+    <hyperlink ref="G118" r:id="rId84" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{B41A5A99-7810-404B-BE81-E5BEB0F3010B}"/>
+    <hyperlink ref="I119" r:id="rId85" xr:uid="{6BC9BD55-8FEE-4942-A5E6-4F02914FAF04}"/>
+    <hyperlink ref="I120" r:id="rId86" xr:uid="{E244D2FF-3F85-F54A-99A7-243B07A96F1F}"/>
+    <hyperlink ref="I121" r:id="rId87" xr:uid="{6C24E5F5-2AFA-B548-B37F-B150439BC3E9}"/>
+    <hyperlink ref="I123" r:id="rId88" xr:uid="{6C9A006B-B605-104B-A1A2-D37DBDD74AC8}"/>
+    <hyperlink ref="I124" r:id="rId89" xr:uid="{1CF3150B-FE16-5941-A388-6827A20A78BA}"/>
+    <hyperlink ref="G125" r:id="rId90" display="mailto:raphael.thuillier@univ-poitiers.fr" xr:uid="{6E305BED-08D9-4D4B-8E6C-3B1379139897}"/>
+    <hyperlink ref="G130" r:id="rId91" display="http://deprunier@chu-angers.fr" xr:uid="{B6320878-3C15-DB42-8AD1-ABCF15930065}"/>
+    <hyperlink ref="I141" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
+    <hyperlink ref="I145" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
+    <hyperlink ref="I146" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB5BF8A-A210-164C-A8A8-0F419DB00E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA2292B-C3D1-9C41-B33D-3D363DC363EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="601">
   <si>
     <t>Villes</t>
   </si>
@@ -2399,9 +2399,6 @@
     <t>Ischémie Reperfusion en Transplantation</t>
   </si>
   <si>
-    <t>Recherche Fondamentale</t>
-  </si>
-  <si>
     <t>U1313 IRMETIST (Ischémie Reperfusion, Métabolisme et Inflammation Stérile en Transplantation)</t>
   </si>
   <si>
@@ -2500,9 +2497,6 @@
     <t>Angers</t>
   </si>
   <si>
-    <t>Soin - Recherche</t>
-  </si>
-  <si>
     <t>Métabolisme,  métabolomique pathologies mitochondriales et neuropathies optiques héréditaires</t>
   </si>
   <si>
@@ -2821,13 +2815,10 @@
     <t>gilles.millat@chu-lyon.fr</t>
   </si>
   <si>
-    <t>Diagnostic et suivi des patients atteints de troubles neurocognitifs comme la Maladie d’Alzheimer et les maladies apparentées par des biomarqueurs protéiques et moléculaires.</t>
-  </si>
-  <si>
-    <t>Diagnostic des neuropathies périphériques, des cardiomyopathies et troubles du rythme héréditaire et des myopathies par biologie moléculaire (panels de gènes, techniques spécifiques ciblées pour les maladies à expansions). </t>
-  </si>
-  <si>
     <t>GACHE - INMG - PGNM </t>
+  </si>
+  <si>
+    <t>Diagnostic et suivi des patients atteints de troubles neurocognitifs comme la Maladie d’Alzheimer et les maladies apparentées par des biomarqueurs protéiques et moléculaires. Diagnostic des neuropathies périphériques, des cardiomyopathies et troubles du rythme héréditaire et des myopathies par biologie moléculaire (panels de gènes, techniques spécifiques ciblées pour les maladies à expansions). </t>
   </si>
 </sst>
 </file>
@@ -3016,7 +3007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3028,15 +3019,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -5290,69 +5284,69 @@
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11" t="s">
+      <c r="B69" s="15"/>
+      <c r="C69" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="15" t="s">
         <v>341</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G69" s="13" t="s">
+      <c r="G69" s="19" t="s">
         <v>193</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I69" s="12"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
       <c r="F70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="G70" s="13"/>
+      <c r="G70" s="19"/>
       <c r="H70" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I70" s="12"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="13"/>
+      <c r="G71" s="19"/>
       <c r="H71" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I71" s="12"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -6743,7 +6737,7 @@
       <c r="I119" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="J119" s="14"/>
+      <c r="J119" s="11"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
@@ -6762,7 +6756,7 @@
       <c r="F120" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G120" s="15" t="s">
+      <c r="G120" s="12" t="s">
         <v>464</v>
       </c>
       <c r="H120" s="1" t="s">
@@ -6771,7 +6765,7 @@
       <c r="I120" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="J120" s="14"/>
+      <c r="J120" s="11"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
@@ -6799,7 +6793,7 @@
       <c r="I121" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="J121" s="14"/>
+      <c r="J121" s="11"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
@@ -6824,7 +6818,7 @@
       <c r="H122" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I122" s="14" t="s">
+      <c r="I122" s="11" t="s">
         <v>473</v>
       </c>
       <c r="J122" s="1"/>
@@ -6838,22 +6832,22 @@
         <v>475</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>476</v>
+        <v>44</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>475</v>
       </c>
       <c r="F123" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G123" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="H123" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="H123" s="16" t="s">
+      <c r="I123" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="I123" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="J123" s="1"/>
     </row>
@@ -6866,22 +6860,22 @@
         <v>13</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>476</v>
+        <v>44</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="I124" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="J124" s="1"/>
     </row>
@@ -6897,19 +6891,19 @@
         <v>45</v>
       </c>
       <c r="E125" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="G125" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="H125" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="I125" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="J125" s="1"/>
     </row>
@@ -6919,25 +6913,25 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E126" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G126" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="G126" s="9" t="s">
+      <c r="H126" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="J126" s="1"/>
     </row>
@@ -6947,19 +6941,19 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="G127" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -6967,147 +6961,147 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D128" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="G128" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="H128" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="I128" s="6" t="s">
         <v>505</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>507</v>
       </c>
       <c r="J128" s="1"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E129" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G129" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="H129" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="I129" s="6" t="s">
         <v>511</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>513</v>
       </c>
       <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="9" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E131" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G131" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="H131" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="G131" s="9" t="s">
+      <c r="I131" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E132" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G132" s="9" t="s">
+      <c r="I132" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
@@ -7117,105 +7111,105 @@
         <v>45</v>
       </c>
       <c r="E133" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E134" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G134" s="9" t="s">
+      <c r="I134" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A135" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="B135" s="15"/>
+      <c r="C135" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="F135" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="G135" s="18" t="s">
         <v>535</v>
       </c>
-      <c r="J134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A135" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="D135" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E135" s="11" t="s">
+      <c r="H135" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="F135" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="G135" s="12" t="s">
+      <c r="I135" s="15"/>
+      <c r="J135" s="15"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A136" s="15"/>
+      <c r="B136" s="15"/>
+      <c r="C136" s="15"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="18"/>
+      <c r="H136" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="H135" s="9" t="s">
+      <c r="I136" s="15"/>
+      <c r="J136" s="15"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A137" s="15"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="I135" s="11"/>
-      <c r="J135" s="11"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="12"/>
-      <c r="H136" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="I136" s="11"/>
-      <c r="J136" s="11"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="12"/>
-      <c r="H137" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="I137" s="11"/>
-      <c r="J137" s="11"/>
+      <c r="I137" s="15"/>
+      <c r="J137" s="15"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B138" s="9">
         <v>1</v>
@@ -7227,157 +7221,157 @@
         <v>45</v>
       </c>
       <c r="E138" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G138" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="H138" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="I138" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="H138" s="9" t="s">
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A139" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="B139" s="18">
+        <v>2</v>
+      </c>
+      <c r="C139" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E139" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="I138" s="6" t="s">
+      <c r="F139" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="G139" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="H139" s="18" t="s">
+        <v>548</v>
+      </c>
+      <c r="I139" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="J139" s="15"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="15"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="J138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A139" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="B139" s="12">
-        <v>2</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="G139" s="18" t="s">
-        <v>549</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="I139" s="18" t="s">
-        <v>546</v>
-      </c>
-      <c r="J139" s="11"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A140" s="11"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F140" s="11"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="12"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="11"/>
+      <c r="F140" s="15"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="16"/>
+      <c r="J140" s="15"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B141" s="9">
         <v>2</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="I141" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B142" s="9">
         <v>3</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E142" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="H142" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>557</v>
-      </c>
       <c r="I142" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B143" s="9">
         <v>3</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="I143" s="6" t="s">
         <v>559</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>561</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B144" s="9">
         <v>4</v>
@@ -7389,25 +7383,25 @@
         <v>45</v>
       </c>
       <c r="E144" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H144" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>564</v>
-      </c>
       <c r="I144" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B145" s="9">
         <v>4</v>
@@ -7419,25 +7413,25 @@
         <v>44</v>
       </c>
       <c r="E145" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="G145" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="H145" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="I145" s="5" t="s">
         <v>567</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="I145" s="5" t="s">
-        <v>569</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B146" s="9">
         <v>4</v>
@@ -7449,25 +7443,25 @@
         <v>44</v>
       </c>
       <c r="E146" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H146" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="I146" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="I146" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B147" s="9">
         <v>5</v>
@@ -7479,25 +7473,25 @@
         <v>45</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="F147" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>576</v>
-      </c>
       <c r="I147" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B148" s="9">
         <v>5</v>
@@ -7509,25 +7503,25 @@
         <v>45</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J148" s="1"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B149" s="9">
         <v>5</v>
@@ -7539,25 +7533,25 @@
         <v>44</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="G149" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="F149" s="17" t="s">
+      <c r="H149" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="I149" s="6" t="s">
         <v>581</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>583</v>
       </c>
       <c r="J149" s="1"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B150" s="9">
         <v>5</v>
@@ -7569,55 +7563,55 @@
         <v>44</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="G150" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="F150" s="1" t="s">
+      <c r="H150" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="I150" s="6" t="s">
         <v>586</v>
-      </c>
-      <c r="H150" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>588</v>
       </c>
       <c r="J150" s="1"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B151" s="9">
         <v>6</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>592</v>
-      </c>
       <c r="I151" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J151" s="2"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B152" s="9">
         <v>6</v>
@@ -7629,77 +7623,79 @@
         <v>44</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H152" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="I152" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="G152" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="H152" s="9" t="s">
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A153" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="B153" s="18">
+        <v>6</v>
+      </c>
+      <c r="C153" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="I152" s="6" t="s">
+      <c r="D153" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E153" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="J152" s="2"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A153" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="B153" s="12">
-        <v>6</v>
-      </c>
-      <c r="C153" s="11" t="s">
+      <c r="F153" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="D153" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E153" s="11" t="s">
+      <c r="G153" s="16" t="s">
         <v>598</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="H153" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="I153" s="16" t="s">
         <v>599</v>
       </c>
-      <c r="G153" s="18" t="s">
-        <v>600</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="I153" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="J153" s="19"/>
+      <c r="J153" s="17"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A154" s="11"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
-      <c r="G154" s="18"/>
-      <c r="H154" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="I154" s="18"/>
-      <c r="J154" s="19"/>
+      <c r="A154" s="15"/>
+      <c r="B154" s="18"/>
+      <c r="C154" s="15"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="15"/>
+      <c r="F154" s="15"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="20"/>
+      <c r="I154" s="16"/>
+      <c r="J154" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="F153:F154"/>
-    <mergeCell ref="G153:G154"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="J153:J154"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="D153:D154"/>
-    <mergeCell ref="E153:E154"/>
+  <mergeCells count="39">
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="D135:D137"/>
+    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="E69:E71"/>
     <mergeCell ref="F135:F137"/>
     <mergeCell ref="G135:G137"/>
     <mergeCell ref="I135:I137"/>
@@ -7716,19 +7712,16 @@
     <mergeCell ref="A135:A137"/>
     <mergeCell ref="B135:B137"/>
     <mergeCell ref="C135:C137"/>
-    <mergeCell ref="D135:D137"/>
-    <mergeCell ref="E135:E137"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="E69:E71"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="F153:F154"/>
+    <mergeCell ref="G153:G154"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="J153:J154"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D153:D154"/>
+    <mergeCell ref="E153:E154"/>
+    <mergeCell ref="H153:H154"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA2292B-C3D1-9C41-B33D-3D363DC363EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBEE5FE-429B-4D47-A079-DE010C291A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="600">
   <si>
     <t>Villes</t>
   </si>
@@ -2629,8 +2629,47 @@
     <t>https://www.chu-lyon.fr/laboratoire-biologie</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1- LBMR : </t>
+    <t>emilie.blond@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic phénotypique et/ou génotypique des patients atteints de dyslipidémies, de diabètes, d’obésités, et/ou dysmétaboliques nécessitant l’exploration de marqueurs de l’insulino-sécrétion, l’insulino-résistance et de la satiété </t>
+  </si>
+  <si>
+    <t>Nutrition, Cardiovasculaire, Diabète et Métabolisme</t>
+  </si>
+  <si>
+    <t>Laboratoire CarMeN Cardiovasculaire, Métabolisme, Diabète et Nutrition, Unités INSERM U1060, INRAE U1397, Université Lyon1 / Centre de Recherche en Nutrition Humaine Rhône Alpes (CRNH) / Centre Européen Nutrition et Santé (CENS)</t>
+  </si>
+  <si>
+    <t>Au sein de la plateforme METANUTRIBIOTA, de l’unité CarMeN et du CRNH, expertise dans l’exploration biochimique des mécanismes de l’insulino-résistance, du diabète, des dyslipidémies, de la stéatose hépatique et de l’interaction microbiote intestinal/nutrition/maladies métaboliques.</t>
+  </si>
+  <si>
+    <t>https://carmen.univ-lyon1.fr/</t>
+  </si>
+  <si>
+    <t>LBMR  : axe surrénalien, axe gonadotrope (dont les pathologies de la différenciation sexuelle et exploration des infertilités) (phénotype et génotype); axe thyréotrope, axe somatotrope, pathologies hypophysaires, Pathologies du sommeil (phénotype). </t>
+  </si>
+  <si>
+    <t>florence.roucher@chu-lyon.fr</t>
+  </si>
+  <si>
+    <t>Diagnostic des pathologies hormonales fréquentes et rares, du phénotype au génotype</t>
+  </si>
+  <si>
+    <t>Thématique : Surrénales Gonades</t>
+  </si>
+  <si>
+    <t>Unité 1208 INSERM Institut Cellules Souches Cerveau SBRI, équipe Pluripotent Stem Cell in mammals </t>
+  </si>
+  <si>
+    <t>Développement d’organoïdes testiculaires et de cellules stéroïdogènes like à partir de cellules souches pluripotentes induites de patients, afin d'étudier le développement des gonades et des glandes surrénales ainsi que les troubles de la fertilité. Modélisation des troubles du développement sexuel et de l'insuffisance surrénalienne congénitale par technologie CRISPR/Cas9. </t>
+  </si>
+  <si>
+    <t>https://sbri.fr/ </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thématique : </t>
     </r>
     <r>
       <rPr>
@@ -2640,63 +2679,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Syndrome métabolique, dyslipidémies (phénotype et génotype), insulinorésistance (phénotype et génotype) et pathologies nutritionnelles et digestives </t>
-    </r>
-  </si>
-  <si>
-    <t>2- Unité Médicale Dyslipidémies, Dysfonctions Nutritionnelles et Digestives (D2ND)</t>
-  </si>
-  <si>
-    <t>emilie.blond@chu-lyon.fr</t>
-  </si>
-  <si>
-    <t>Diagnostic phénotypique et/ou génotypique des patients atteints de dyslipidémies, de diabètes, d’obésités, et/ou dysmétaboliques nécessitant l’exploration de marqueurs de l’insulino-sécrétion, l’insulino-résistance et de la satiété </t>
-  </si>
-  <si>
-    <t>Nutrition, Cardiovasculaire, Diabète et Métabolisme</t>
-  </si>
-  <si>
-    <t>Laboratoire CarMeN Cardiovasculaire, Métabolisme, Diabète et Nutrition, Unités INSERM U1060, INRAE U1397, Université Lyon1 / Centre de Recherche en Nutrition Humaine Rhône Alpes (CRNH) / Centre Européen Nutrition et Santé (CENS)</t>
-  </si>
-  <si>
-    <t>Au sein de la plateforme METANUTRIBIOTA, de l’unité CarMeN et du CRNH, expertise dans l’exploration biochimique des mécanismes de l’insulino-résistance, du diabète, des dyslipidémies, de la stéatose hépatique et de l’interaction microbiote intestinal/nutrition/maladies métaboliques.</t>
-  </si>
-  <si>
-    <t>https://carmen.univ-lyon1.fr/</t>
-  </si>
-  <si>
-    <t>LBMR  : axe surrénalien, axe gonadotrope (dont les pathologies de la différenciation sexuelle et exploration des infertilités) (phénotype et génotype); axe thyréotrope, axe somatotrope, pathologies hypophysaires, Pathologies du sommeil (phénotype). </t>
-  </si>
-  <si>
-    <t>florence.roucher@chu-lyon.fr</t>
-  </si>
-  <si>
-    <t>Diagnostic des pathologies hormonales fréquentes et rares, du phénotype au génotype</t>
-  </si>
-  <si>
-    <t>Thématique : Surrénales Gonades</t>
-  </si>
-  <si>
-    <t>Unité 1208 INSERM Institut Cellules Souches Cerveau SBRI, équipe Pluripotent Stem Cell in mammals </t>
-  </si>
-  <si>
-    <t>Développement d’organoïdes testiculaires et de cellules stéroïdogènes like à partir de cellules souches pluripotentes induites de patients, afin d'étudier le développement des gonades et des glandes surrénales ainsi que les troubles de la fertilité. Modélisation des troubles du développement sexuel et de l'insuffisance surrénalienne congénitale par technologie CRISPR/Cas9. </t>
-  </si>
-  <si>
-    <t>https://sbri.fr/ </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Thématique : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Pathologies Cancéreuses</t>
     </r>
   </si>
@@ -2734,18 +2716,12 @@
     <t>https://www.crcl.fr/equipes-de-recherche/plasticite-tumorale-dans-le-melanome/</t>
   </si>
   <si>
-    <t>LBMR : Maladies héréditaires du métabolisme (phénotype et génotype) ; Maladies métaboliques à révélation anténatale : approche phénotypique et génotypique Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
-  </si>
-  <si>
     <t>cecile.acquaviva-bourdain@chu-lyon.fr </t>
   </si>
   <si>
     <t xml:space="preserve">Diagnostic génotypique et phénotypique des patients atteints de MHM (maladies du métabolisme intermédiaire et énergétique, maladies lysosomales, maladies peroxysomales…) en biochimie et en biologie moléculaire. </t>
   </si>
   <si>
-    <t>LBMR : Hémoglobinopathies et biochimie du globule rouge (phénotype et génotype)</t>
-  </si>
-  <si>
     <t>Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
   </si>
   <si>
@@ -2782,18 +2758,12 @@
     <t>Pathologies Neurologiques, musculaires et cardiaques</t>
   </si>
   <si>
-    <t>6 LMBR : Maladies neurodégénératives centrales (phénotype) ; Cardiomyopathies héréditaires ; Troubles du rythme cardiaque héréditaires ; Diagnostic génétique des maladies neurodégénératives à expansions (dont maladie de Huntington - MH, maladie de Steinert - DM1, dystrophie myotonique proximale - DM2 ou PROMM, maladie de Kennedy - SK) ; Diagnostic génétique des neuropathies périphériques de Charcot Marie et Tooth et apparentées ; Diagnostic génétique des myopathies</t>
-  </si>
-  <si>
     <t>isabelle.quadrio@chu-lyon.fr</t>
   </si>
   <si>
     <t>Comprendre les mécanismes de neurodégénérescence cérébrale en développant des biomarqueurs protéiques et d’imagerie des maladies neurodégénératives, du modèle animal à l’étude clinique dans une approche translationnelle. </t>
   </si>
   <si>
-    <t> Mécanismes physiopathologiques d’agrégation des protéines impliquées dans les maladies neurodégénératives</t>
-  </si>
-  <si>
     <t>Centre de Recherche en Neurosciences de Lyon (CNRL), Equipe BIORAN </t>
   </si>
   <si>
@@ -2818,7 +2788,22 @@
     <t>GACHE - INMG - PGNM </t>
   </si>
   <si>
-    <t>Diagnostic et suivi des patients atteints de troubles neurocognitifs comme la Maladie d’Alzheimer et les maladies apparentées par des biomarqueurs protéiques et moléculaires. Diagnostic des neuropathies périphériques, des cardiomyopathies et troubles du rythme héréditaire et des myopathies par biologie moléculaire (panels de gènes, techniques spécifiques ciblées pour les maladies à expansions). </t>
+    <t>1- LBMR : Syndrome métabolique, dyslipidémies (phénotype et génotype), insulinorésistance (phénotype et génotype) et pathologies nutritionnelles et digestives  2- Unité Médicale Dyslipidémies, Dysfonctions Nutritionnelles et Digestives (D2ND)</t>
+  </si>
+  <si>
+    <t>Diagnostic et suivi des patients atteints de troubles neurocognitifs comme la Maladie d’Alzheimer et les maladies apparentées par des biomarqueurs protéiques et moléculaires. Diagnostic des neuropathies périphériques, des cardiomyopathies et troubles du rythme héréditaire et des myopathies par biologie moléculaire (panels de gènes, techniques spécifiques ciblées pour les maladies à expansions).</t>
+  </si>
+  <si>
+    <t>Mécanismes physiopathologiques d’agrégation des protéines impliquées dans les maladies neurodégénératives</t>
+  </si>
+  <si>
+    <t>LBMR - Hémoglobinopathies et biochimie du globule rouge (phénotype et génotype)</t>
+  </si>
+  <si>
+    <t>LMBR - Maladies neurodégénératives centrales (phénotype) ; Cardiomyopathies héréditaires ; Troubles du rythme cardiaque héréditaires ; Diagnostic génétique des maladies neurodégénératives à expansions (dont maladie de Huntington - MH, maladie de Steinert - DM1, dystrophie myotonique proximale - DM2 ou PROMM, maladie de Kennedy - SK) ; Diagnostic génétique des neuropathies périphériques de Charcot Marie et Tooth et apparentées ; Diagnostic génétique des myopathies</t>
+  </si>
+  <si>
+    <t>LBMR - Maladies héréditaires du métabolisme (phénotype et génotype) ; Maladies métaboliques à révélation anténatale : approche phénotypique et génotypique Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
   </si>
 </sst>
 </file>
@@ -3007,7 +2992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3024,13 +3009,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3247,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1"/>
@@ -5300,14 +5280,14 @@
       <c r="F69" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G69" s="19" t="s">
+      <c r="G69" s="17" t="s">
         <v>193</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I69" s="18"/>
-      <c r="J69" s="19"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="17"/>
       <c r="K69" s="15"/>
       <c r="L69" s="15"/>
       <c r="M69" s="15"/>
@@ -5321,12 +5301,12 @@
       <c r="F70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="G70" s="19"/>
+      <c r="G70" s="17"/>
       <c r="H70" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I70" s="18"/>
-      <c r="J70" s="19"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="17"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
       <c r="M70" s="15"/>
@@ -5338,12 +5318,12 @@
       <c r="D71" s="15"/>
       <c r="E71" s="15"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="19"/>
+      <c r="G71" s="17"/>
       <c r="H71" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I71" s="18"/>
-      <c r="J71" s="19"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="17"/>
       <c r="K71" s="15"/>
       <c r="L71" s="15"/>
       <c r="M71" s="15"/>
@@ -7170,7 +7150,7 @@
       <c r="F135" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G135" s="18" t="s">
+      <c r="G135" s="16" t="s">
         <v>535</v>
       </c>
       <c r="H135" s="9" t="s">
@@ -7186,7 +7166,7 @@
       <c r="D136" s="15"/>
       <c r="E136" s="15"/>
       <c r="F136" s="15"/>
-      <c r="G136" s="18"/>
+      <c r="G136" s="16"/>
       <c r="H136" s="9" t="s">
         <v>537</v>
       </c>
@@ -7200,7 +7180,7 @@
       <c r="D137" s="15"/>
       <c r="E137" s="15"/>
       <c r="F137" s="15"/>
-      <c r="G137" s="18"/>
+      <c r="G137" s="16"/>
       <c r="H137" s="9" t="s">
         <v>538</v>
       </c>
@@ -7238,74 +7218,90 @@
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A139" s="15" t="s">
+      <c r="A139" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B139" s="18">
+      <c r="B139" s="9">
         <v>2</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C139" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D139" s="15" t="s">
+      <c r="D139" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E139" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G139" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="F139" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="G139" s="16" t="s">
+      <c r="H139" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B140" s="9">
+        <v>2</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="H139" s="18" t="s">
+      <c r="D140" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="I139" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="J139" s="15"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A140" s="15"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15"/>
-      <c r="E140" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="F140" s="15"/>
-      <c r="G140" s="16"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="16"/>
-      <c r="J140" s="15"/>
+      <c r="G140" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>539</v>
       </c>
       <c r="B141" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E141" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>551</v>
+      </c>
       <c r="F141" s="1" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>544</v>
       </c>
       <c r="J141" s="1"/>
     </row>
@@ -7320,22 +7316,22 @@
         <v>512</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="J142" s="1"/>
     </row>
@@ -7344,28 +7340,28 @@
         <v>539</v>
       </c>
       <c r="B143" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="J143" s="1"/>
     </row>
@@ -7380,22 +7376,22 @@
         <v>13</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>544</v>
+        <v>564</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>565</v>
       </c>
       <c r="J144" s="1"/>
     </row>
@@ -7413,19 +7409,19 @@
         <v>44</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J145" s="1"/>
     </row>
@@ -7434,28 +7430,28 @@
         <v>539</v>
       </c>
       <c r="B146" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E146" s="9" t="s">
-        <v>568</v>
+        <v>45</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>599</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="I146" s="5" t="s">
         <v>571</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>544</v>
       </c>
       <c r="J146" s="1"/>
     </row>
@@ -7467,22 +7463,22 @@
         <v>5</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>541</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I147" s="6" t="s">
         <v>544</v>
@@ -7497,25 +7493,25 @@
         <v>5</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="G148" s="6" t="s">
         <v>575</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>573</v>
       </c>
       <c r="H148" s="9" t="s">
         <v>576</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>544</v>
+        <v>577</v>
       </c>
       <c r="J148" s="1"/>
     </row>
@@ -7527,25 +7523,25 @@
         <v>5</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F149" s="14" t="s">
         <v>578</v>
       </c>
+      <c r="F149" s="1" t="s">
+        <v>579</v>
+      </c>
       <c r="G149" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J149" s="1"/>
     </row>
@@ -7554,19 +7550,19 @@
         <v>539</v>
       </c>
       <c r="B150" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>157</v>
+        <v>583</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="G150" s="6" t="s">
         <v>584</v>
@@ -7575,9 +7571,9 @@
         <v>585</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="J150" s="1"/>
+        <v>544</v>
+      </c>
+      <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
@@ -7587,107 +7583,64 @@
         <v>6</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="I151" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G151" s="6" t="s">
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A152" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B152" s="4">
+        <v>6</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="H151" s="9" t="s">
+      <c r="D152" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E152" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="I151" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="J151" s="2"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A152" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="B152" s="9">
-        <v>6</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="F152" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="G152" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="G152" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="H152" s="9" t="s">
+      <c r="H152" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="I152" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="I152" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="J152" s="2"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A153" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="B153" s="18">
-        <v>6</v>
-      </c>
-      <c r="C153" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E153" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="F153" s="15" t="s">
-        <v>597</v>
-      </c>
-      <c r="G153" s="16" t="s">
-        <v>598</v>
-      </c>
-      <c r="H153" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="I153" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="J153" s="17"/>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A154" s="15"/>
-      <c r="B154" s="18"/>
-      <c r="C154" s="15"/>
-      <c r="D154" s="15"/>
-      <c r="E154" s="15"/>
-      <c r="F154" s="15"/>
-      <c r="G154" s="16"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="16"/>
-      <c r="J154" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
+  <mergeCells count="20">
+    <mergeCell ref="I135:I137"/>
+    <mergeCell ref="J135:J137"/>
+    <mergeCell ref="A135:A137"/>
+    <mergeCell ref="B135:B137"/>
+    <mergeCell ref="C135:C137"/>
     <mergeCell ref="D135:D137"/>
     <mergeCell ref="E135:E137"/>
     <mergeCell ref="G69:G71"/>
@@ -7698,30 +7651,11 @@
     <mergeCell ref="E69:E71"/>
     <mergeCell ref="F135:F137"/>
     <mergeCell ref="G135:G137"/>
-    <mergeCell ref="I135:I137"/>
-    <mergeCell ref="J135:J137"/>
-    <mergeCell ref="A139:A140"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="C139:C140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="C135:C137"/>
-    <mergeCell ref="F153:F154"/>
-    <mergeCell ref="G153:G154"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="J153:J154"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="C153:C154"/>
-    <mergeCell ref="D153:D154"/>
-    <mergeCell ref="E153:E154"/>
-    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
@@ -7815,9 +7749,9 @@
     <hyperlink ref="I124" r:id="rId89" xr:uid="{1CF3150B-FE16-5941-A388-6827A20A78BA}"/>
     <hyperlink ref="G125" r:id="rId90" display="mailto:raphael.thuillier@univ-poitiers.fr" xr:uid="{6E305BED-08D9-4D4B-8E6C-3B1379139897}"/>
     <hyperlink ref="G130" r:id="rId91" display="http://deprunier@chu-angers.fr" xr:uid="{B6320878-3C15-DB42-8AD1-ABCF15930065}"/>
-    <hyperlink ref="I141" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
-    <hyperlink ref="I145" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
-    <hyperlink ref="I146" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
+    <hyperlink ref="I140" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
+    <hyperlink ref="I144" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
+    <hyperlink ref="I145" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBEE5FE-429B-4D47-A079-DE010C291A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24170553-0386-8945-925D-4A3576F374D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="580" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="598">
   <si>
     <t>Villes</t>
   </si>
@@ -2602,15 +2602,6 @@
     <t>edith.bigot@chu-nantes.fr ; maxime.carpentier-A030746@chu-nantes.fr ; pierreolivier.bertho@chu-nantes.fr</t>
   </si>
   <si>
-    <t>Exploration dans le cadre des pathologies inflammatoires (dosage des protéines : albumine, Immunoglobulines, Chaînes légères libres Kappa et Lambda, calcul des index et recherche de bandes oligoclonales d’IgG par isoélectrofocalisation.</t>
-  </si>
-  <si>
-    <t>Exploration des pathologies neurodégénératives : dosages dans le LCS des peptides amyloïdes beta 1-40, 1-42, protéines TAU totale et hyperphosphorylées, phénotypage apoE.</t>
-  </si>
-  <si>
-    <t>Brêches ostéo-méningées : sur microprélèvement (10 µL) recherche par électrophorèse et immuno-transfert de beta2 transferrine (spécifique du LCS)</t>
-  </si>
-  <si>
     <t>Lyon</t>
   </si>
   <si>
@@ -2804,6 +2795,9 @@
   </si>
   <si>
     <t>LBMR - Maladies héréditaires du métabolisme (phénotype et génotype) ; Maladies métaboliques à révélation anténatale : approche phénotypique et génotypique Diagnostic biochimique et génétique des maladies du globule rouge et en premier lieu des hémoglobinopathies. </t>
+  </si>
+  <si>
+    <t>Exploration dans le cadre des pathologies inflammatoires (dosage des protéines : albumine, Immunoglobulines, Chaînes légères libres Kappa et Lambda, calcul des index et recherche de bandes oligoclonales d’IgG par isoélectrofocalisation. Exploration des pathologies neurodégénératives : dosages dans le LCS des peptides amyloïdes beta 1-40, 1-42, protéines TAU totale et hyperphosphorylées, phénotypage apoE. Brêches ostéo-méningées : sur microprélèvement (10 µL) recherche par électrophorèse et immuno-transfert de beta2 transferrine (spécifique du LCS)</t>
   </si>
 </sst>
 </file>
@@ -3009,8 +3003,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3227,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1"/>
@@ -5280,14 +5274,14 @@
       <c r="F69" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="G69" s="16" t="s">
         <v>193</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I69" s="16"/>
-      <c r="J69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="16"/>
       <c r="K69" s="15"/>
       <c r="L69" s="15"/>
       <c r="M69" s="15"/>
@@ -5301,12 +5295,12 @@
       <c r="F70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="G70" s="17"/>
+      <c r="G70" s="16"/>
       <c r="H70" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I70" s="16"/>
-      <c r="J70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="16"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
       <c r="M70" s="15"/>
@@ -5318,12 +5312,12 @@
       <c r="D71" s="15"/>
       <c r="E71" s="15"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="17"/>
+      <c r="G71" s="16"/>
       <c r="H71" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I71" s="16"/>
-      <c r="J71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="16"/>
       <c r="K71" s="15"/>
       <c r="L71" s="15"/>
       <c r="M71" s="15"/>
@@ -7134,210 +7128,242 @@
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A135" s="15" t="s">
+      <c r="A135" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B135" s="15"/>
-      <c r="C135" s="15" t="s">
+      <c r="B135" s="1"/>
+      <c r="C135" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D135" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E135" s="15" t="s">
+      <c r="D135" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F135" s="15" t="s">
+      <c r="F135" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G135" s="16" t="s">
+      <c r="G135" s="9" t="s">
         <v>535</v>
       </c>
       <c r="H135" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="I135" s="15"/>
-      <c r="J135" s="15"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A136" s="15"/>
-      <c r="B136" s="15"/>
-      <c r="C136" s="15"/>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="15"/>
-      <c r="G136" s="16"/>
+      <c r="B136" s="9">
+        <v>1</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>539</v>
+      </c>
       <c r="H136" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="I136" s="15"/>
-      <c r="J136" s="15"/>
+        <v>540</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A137" s="15"/>
-      <c r="B137" s="15"/>
-      <c r="C137" s="15"/>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="15"/>
-      <c r="G137" s="16"/>
+      <c r="A137" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B137" s="9">
+        <v>2</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>542</v>
+      </c>
       <c r="H137" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="I137" s="15"/>
-      <c r="J137" s="15"/>
+        <v>543</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B138" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>288</v>
+        <v>544</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E138" s="9" t="s">
-        <v>540</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E138" s="1"/>
       <c r="F138" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>542</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B139" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>594</v>
+        <v>548</v>
       </c>
       <c r="F139" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="I139" s="6" t="s">
         <v>541</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>544</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B140" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E140" s="1"/>
+      <c r="E140" s="9" t="s">
+        <v>551</v>
+      </c>
       <c r="F140" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="I140" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>554</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B141" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F141" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>541</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>544</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B142" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>557</v>
+        <v>561</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>562</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B143" s="9">
         <v>4</v>
@@ -7346,88 +7372,88 @@
         <v>13</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>544</v>
+        <v>565</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>566</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B144" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>561</v>
+        <v>45</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>596</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B145" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E145" s="9" t="s">
-        <v>566</v>
+        <v>45</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>594</v>
       </c>
       <c r="F145" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G145" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="G145" s="6" t="s">
-        <v>559</v>
-      </c>
       <c r="H145" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="I145" s="5" t="s">
         <v>569</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B146" s="9">
         <v>5</v>
@@ -7436,28 +7462,28 @@
         <v>15</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>541</v>
+        <v>570</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>571</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B147" s="9">
         <v>5</v>
@@ -7466,196 +7492,127 @@
         <v>157</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>541</v>
+        <v>576</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>544</v>
+        <v>579</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B148" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>15</v>
+        <v>580</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="F148" s="14" t="s">
-        <v>574</v>
+        <v>595</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="J148" s="1"/>
+        <v>541</v>
+      </c>
+      <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B149" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>157</v>
+        <v>457</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="J149" s="1"/>
+        <v>585</v>
+      </c>
+      <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="B150" s="9">
+      <c r="A150" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B150" s="4">
         <v>6</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="H150" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="J150" s="2"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="B151" s="9">
-        <v>6</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D151" s="1" t="s">
+      <c r="C150" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="H151" s="9" t="s">
+      <c r="E150" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="I151" s="6" t="s">
+      <c r="F150" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="J151" s="2"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A152" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="B152" s="4">
-        <v>6</v>
-      </c>
-      <c r="C152" s="4" t="s">
+      <c r="G150" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="D152" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E152" s="4" t="s">
+      <c r="H150" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="I150" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="F152" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="I152" s="4" t="s">
-        <v>593</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="I135:I137"/>
-    <mergeCell ref="J135:J137"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="C135:C137"/>
-    <mergeCell ref="D135:D137"/>
-    <mergeCell ref="E135:E137"/>
+  <mergeCells count="11">
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="C69:C71"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:E71"/>
-    <mergeCell ref="F135:F137"/>
-    <mergeCell ref="G135:G137"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
@@ -7749,9 +7706,9 @@
     <hyperlink ref="I124" r:id="rId89" xr:uid="{1CF3150B-FE16-5941-A388-6827A20A78BA}"/>
     <hyperlink ref="G125" r:id="rId90" display="mailto:raphael.thuillier@univ-poitiers.fr" xr:uid="{6E305BED-08D9-4D4B-8E6C-3B1379139897}"/>
     <hyperlink ref="G130" r:id="rId91" display="http://deprunier@chu-angers.fr" xr:uid="{B6320878-3C15-DB42-8AD1-ABCF15930065}"/>
-    <hyperlink ref="I140" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
-    <hyperlink ref="I144" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
-    <hyperlink ref="I145" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
+    <hyperlink ref="I138" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
+    <hyperlink ref="I142" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
+    <hyperlink ref="I143" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24170553-0386-8945-925D-4A3576F374D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B1D07F-BC14-B54F-9DD5-A5F613593417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="595">
   <si>
     <t>Villes</t>
   </si>
@@ -2557,9 +2557,6 @@
     <t>Dépistage de la Trisomie 21 fœtale au 1er trimestre de la grossesse par les marqueurs sériques maternels et Identification des patientes à forte probabilité de pré-éclampsie dès le 1er trimestre de la grossesse (dépistage combiné à celui de la Trisomie 21) ou à partir de la 20ème semaine d’aménorrhée selon l’association de critères cliniques (mesure du ratio sFlt-1/ PlGF).</t>
   </si>
   <si>
-    <t>Dépistage, Trisomie 21, pré-éclampsie</t>
-  </si>
-  <si>
     <t>LBMR - Biochimie endocrine : axe surrénalien - Diagnostic et suivi des pathologies endocriniennes rares d’origine surrénalienne ou hypophysaire.</t>
   </si>
   <si>
@@ -2569,9 +2566,6 @@
     <t>Exploration biologiques spécialisées (stimulation ou freinage, cathétérismes veineux surrénaliens ou des sinus pétreux) des pathologies surrénaliennes réalisées en concertation avec les praticiens des Services d’Endocrinologie Adulte et Pédiatrique, de Radiologie Interventionnelle et d’Oncologie et de Chirurgie Endocrinienne du CHU de Nantes. Le Laboratoire d’Hormonologie est associé au Centre de Compétence des Maladies Endocriniennes rares de l’enfant et de l’adulte du CHU de Nantes (Dr Sabine Baron (réseau FIRENDO), Drs Delphine Drui et Maëlle Le Bras (Réseaux RENATEN et ENDOCAN-COMETE). Le laboratoire est en lien avec l’association de patients souffrant de pathologies surrénaliennes (Association SURRENALES).</t>
   </si>
   <si>
-    <t>Cushing, HAP (hyperaldostéronisme primaire), HCS (hyperplasie congénitale des surrénales), hyperandrogénie, Phéochromocytome</t>
-  </si>
-  <si>
     <t>LBMR - Biochimie des gammapathies monoclonales </t>
   </si>
   <si>
@@ -2591,9 +2585,6 @@
   </si>
   <si>
     <t>Le Laboratoire de Biologie Médicale de Référence « Génétique somatique des tumeurs solides » réalise des analyses moléculaires à visée diagnostique, pronostique et théranostique sur les tumeurs solides. Ces analyses sont effectuées à partir d’ADN et d’ARN tumoraux extraits de tissus fixés au formol et inclus en paraffine (FFPE), ou à partir de plasma (ADN tumoral circulant).Les profils moléculaires ainsi obtenus, permettent d’orienter les stratégies thérapeutiques personnalisées.</t>
-  </si>
-  <si>
-    <t>Oncogénomique, ADN tumoral circulant, marqueurs théranostiques, DNAseq, RNAseq</t>
   </si>
   <si>
     <t>Analyse protéinologique spécialisée du Liquide cérébro-spinal incluant l’exploration des pathologies inflammatoires et neurodégénératives pour le GHT, et diagnostic biologique des brèches méningées au niveau national.</t>
@@ -3003,8 +2994,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -5274,14 +5265,14 @@
       <c r="F69" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="G69" s="17" t="s">
         <v>193</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I69" s="17"/>
-      <c r="J69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="17"/>
       <c r="K69" s="15"/>
       <c r="L69" s="15"/>
       <c r="M69" s="15"/>
@@ -5295,12 +5286,12 @@
       <c r="F70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="G70" s="16"/>
+      <c r="G70" s="17"/>
       <c r="H70" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="17"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
       <c r="M70" s="15"/>
@@ -5312,12 +5303,12 @@
       <c r="D71" s="15"/>
       <c r="E71" s="15"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="16"/>
+      <c r="G71" s="17"/>
       <c r="H71" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="I71" s="17"/>
-      <c r="J71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="17"/>
       <c r="K71" s="15"/>
       <c r="L71" s="15"/>
       <c r="M71" s="15"/>
@@ -7040,9 +7031,7 @@
       <c r="H131" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>521</v>
-      </c>
+      <c r="I131" s="1"/>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -7057,20 +7046,18 @@
         <v>45</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G132" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>525</v>
-      </c>
+      <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
@@ -7085,16 +7072,16 @@
         <v>45</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7105,26 +7092,24 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>533</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -7139,23 +7124,23 @@
         <v>45</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>518</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B136" s="9">
         <v>1</v>
@@ -7167,25 +7152,25 @@
         <v>45</v>
       </c>
       <c r="E136" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="H136" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="I136" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B137" s="9">
         <v>2</v>
@@ -7197,53 +7182,53 @@
         <v>45</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F137" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="I137" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G137" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B138" s="9">
         <v>2</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B139" s="9">
         <v>3</v>
@@ -7255,25 +7240,25 @@
         <v>45</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F139" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I139" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B140" s="9">
         <v>3</v>
@@ -7285,25 +7270,25 @@
         <v>44</v>
       </c>
       <c r="E140" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="I140" s="6" t="s">
         <v>551</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>554</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B141" s="9">
         <v>4</v>
@@ -7315,25 +7300,25 @@
         <v>45</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F141" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B142" s="9">
         <v>4</v>
@@ -7345,25 +7330,25 @@
         <v>44</v>
       </c>
       <c r="E142" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="H142" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="I142" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B143" s="9">
         <v>4</v>
@@ -7375,25 +7360,25 @@
         <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="I143" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>566</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B144" s="9">
         <v>5</v>
@@ -7405,25 +7390,25 @@
         <v>45</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F144" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="I144" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B145" s="9">
         <v>5</v>
@@ -7435,25 +7420,25 @@
         <v>45</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F145" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="I145" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B146" s="9">
         <v>5</v>
@@ -7465,25 +7450,25 @@
         <v>44</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H146" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="F146" s="14" t="s">
+      <c r="I146" s="6" t="s">
         <v>571</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>574</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B147" s="9">
         <v>5</v>
@@ -7495,55 +7480,55 @@
         <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="I147" s="6" t="s">
         <v>576</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B148" s="9">
         <v>6</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="I148" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="H148" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B149" s="9">
         <v>6</v>
@@ -7555,64 +7540,64 @@
         <v>44</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G149" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="H149" s="9" t="s">
-        <v>584</v>
-      </c>
       <c r="I149" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A150" s="4" t="s">
-        <v>536</v>
+      <c r="A150" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="B150" s="4">
         <v>6</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E150" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="I150" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="I150" s="4" t="s">
-        <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="C69:C71"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:E71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B1D07F-BC14-B54F-9DD5-A5F613593417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4FC69E-1A7B-5440-9B91-5C4B01D01B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="600">
   <si>
     <t>Villes</t>
   </si>
@@ -867,9 +867,6 @@
     <t>Dijon</t>
   </si>
   <si>
-    <t> Lipides et transfert des lipides dans l'inflammation et le sepsis</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">UMR 1231 </t>
     </r>
@@ -2542,9 +2539,6 @@
     <t>Nantes</t>
   </si>
   <si>
-    <t>Grossesses pathologiques</t>
-  </si>
-  <si>
     <t>LBMR - Marqueurs sériques maternels des grossesses pathologiques : Trisomie 21 fœtale &amp; pré-éclampsie</t>
   </si>
   <si>
@@ -2789,13 +2783,34 @@
   </si>
   <si>
     <t>Exploration dans le cadre des pathologies inflammatoires (dosage des protéines : albumine, Immunoglobulines, Chaînes légères libres Kappa et Lambda, calcul des index et recherche de bandes oligoclonales d’IgG par isoélectrofocalisation. Exploration des pathologies neurodégénératives : dosages dans le LCS des peptides amyloïdes beta 1-40, 1-42, protéines TAU totale et hyperphosphorylées, phénotypage apoE. Brêches ostéo-méningées : sur microprélèvement (10 µL) recherche par électrophorèse et immuno-transfert de beta2 transferrine (spécifique du LCS)</t>
+  </si>
+  <si>
+    <t>Centre 1</t>
+  </si>
+  <si>
+    <t>Centre 2</t>
+  </si>
+  <si>
+    <t>Centre 3</t>
+  </si>
+  <si>
+    <t>Centre 4</t>
+  </si>
+  <si>
+    <t>Centre 5</t>
+  </si>
+  <si>
+    <t>Centre 6</t>
+  </si>
+  <si>
+    <t>Lipides et transfert des lipides dans l'inflammation et le sepsis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2949,6 +2964,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2993,9 +3014,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3231,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -3252,7 +3273,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3264,7 +3285,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -3273,10 +3294,10 @@
         <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>49</v>
@@ -3293,13 +3314,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>50</v>
@@ -3308,13 +3329,13 @@
         <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3326,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>117</v>
@@ -3341,13 +3362,13 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3359,7 +3380,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -3371,7 +3392,7 @@
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>54</v>
@@ -3390,7 +3411,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -3428,7 +3449,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -3608,7 +3629,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>40</v>
@@ -3689,7 +3710,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>60</v>
@@ -3712,7 +3733,7 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>45</v>
@@ -3799,13 +3820,13 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>70</v>
@@ -3834,7 +3855,7 @@
         <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>70</v>
@@ -3863,7 +3884,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>70</v>
@@ -3886,13 +3907,13 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
@@ -3921,7 +3942,7 @@
         <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -3953,7 +3974,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>81</v>
@@ -3979,7 +4000,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>82</v>
@@ -4006,7 +4027,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
@@ -4033,7 +4054,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
@@ -4054,13 +4075,13 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -4081,13 +4102,13 @@
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>87</v>
@@ -4203,7 +4224,7 @@
         <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>99</v>
@@ -4226,13 +4247,13 @@
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>99</v>
@@ -4261,7 +4282,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>99</v>
@@ -4284,13 +4305,13 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>99</v>
@@ -4316,7 +4337,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>106</v>
@@ -4457,7 +4478,7 @@
         <v>176</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>13</v>
@@ -4466,7 +4487,7 @@
         <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>135</v>
@@ -4488,7 +4509,7 @@
         <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>15</v>
@@ -4497,7 +4518,7 @@
         <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>135</v>
@@ -4519,7 +4540,7 @@
         <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>140</v>
@@ -4528,7 +4549,7 @@
         <v>45</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>141</v>
@@ -4537,7 +4558,7 @@
         <v>142</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -4550,7 +4571,7 @@
         <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -4559,7 +4580,7 @@
         <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>141</v>
@@ -4581,7 +4602,7 @@
         <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>7</v>
@@ -4590,7 +4611,7 @@
         <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>144</v>
@@ -4612,7 +4633,7 @@
         <v>176</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
@@ -4621,7 +4642,7 @@
         <v>45</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>147</v>
@@ -4643,16 +4664,16 @@
         <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>150</v>
@@ -4674,7 +4695,7 @@
         <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>15</v>
@@ -4683,7 +4704,7 @@
         <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>150</v>
@@ -4705,16 +4726,16 @@
         <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>147</v>
@@ -4736,16 +4757,16 @@
         <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
@@ -4767,7 +4788,7 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>157</v>
@@ -4776,7 +4797,7 @@
         <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>158</v>
@@ -4798,7 +4819,7 @@
         <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>13</v>
@@ -4807,7 +4828,7 @@
         <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>161</v>
@@ -4829,7 +4850,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -4838,7 +4859,7 @@
         <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>163</v>
@@ -4847,7 +4868,7 @@
         <v>159</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4860,16 +4881,16 @@
         <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>164</v>
@@ -4891,7 +4912,7 @@
         <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>157</v>
@@ -4900,7 +4921,7 @@
         <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>167</v>
@@ -4922,7 +4943,7 @@
         <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>157</v>
@@ -4931,7 +4952,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>163</v>
@@ -4953,7 +4974,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>157</v>
@@ -4962,7 +4983,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>163</v>
@@ -4984,7 +5005,7 @@
         <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>15</v>
@@ -4993,7 +5014,7 @@
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>163</v>
@@ -5015,7 +5036,7 @@
         <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>15</v>
@@ -5024,16 +5045,16 @@
         <v>44</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="H61" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -5046,7 +5067,7 @@
         <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>15</v>
@@ -5055,19 +5076,19 @@
         <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="I62" s="5" t="s">
         <v>404</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>405</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -5079,7 +5100,7 @@
         <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -5088,14 +5109,14 @@
         <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -5105,14 +5126,14 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>178</v>
@@ -5124,7 +5145,7 @@
         <v>180</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="5"/>
@@ -5134,20 +5155,20 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>181</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>182</v>
@@ -5163,7 +5184,7 @@
     </row>
     <row r="66" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
@@ -5173,16 +5194,16 @@
         <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>184</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -5192,7 +5213,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -5202,7 +5223,7 @@
         <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>185</v>
@@ -5225,13 +5246,13 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>189</v>
@@ -5249,69 +5270,69 @@
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15" t="s">
+      <c r="B69" s="16"/>
+      <c r="C69" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="15" t="s">
-        <v>341</v>
+      <c r="E69" s="16" t="s">
+        <v>340</v>
       </c>
       <c r="F69" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I69" s="17"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G69" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="H69" s="9" t="s">
+      <c r="G70" s="15"/>
+      <c r="H70" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I69" s="16"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="G70" s="17"/>
-      <c r="H70" s="9" t="s">
+      <c r="I70" s="17"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I70" s="16"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="15"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="I71" s="16"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -5319,16 +5340,16 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>194</v>
@@ -5354,16 +5375,16 @@
         <v>45</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>196</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -5383,7 +5404,7 @@
         <v>45</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>197</v>
@@ -5410,16 +5431,16 @@
         <v>44</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="5"/>
@@ -5439,16 +5460,16 @@
         <v>44</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="5"/>
@@ -5468,16 +5489,16 @@
         <v>45</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F77" s="9" t="s">
+      <c r="G77" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="H77" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -5497,16 +5518,16 @@
         <v>44</v>
       </c>
       <c r="E78" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="H78" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5520,22 +5541,22 @@
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5545,7 +5566,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
@@ -5555,16 +5576,16 @@
         <v>44</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="H80" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="5"/>
@@ -5574,26 +5595,26 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G81" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="H81" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5603,26 +5624,26 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F82" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="H82" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5632,26 +5653,26 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G83" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G83" s="10" t="s">
+      <c r="H83" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5661,7 +5682,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
@@ -5671,16 +5692,16 @@
         <v>44</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="H84" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="5"/>
@@ -5690,7 +5711,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -5700,16 +5721,16 @@
         <v>45</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -5719,26 +5740,26 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G86" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G86" s="10" t="s">
+      <c r="H86" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5748,26 +5769,26 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="H87" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5777,7 +5798,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
@@ -5787,16 +5808,16 @@
         <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G88" s="10" t="s">
+      <c r="H88" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5806,7 +5827,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
@@ -5816,16 +5837,16 @@
         <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5835,7 +5856,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -5845,16 +5866,16 @@
         <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G90" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="H90" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5864,29 +5885,29 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>425</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>426</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5895,26 +5916,26 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="G92" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="H92" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -5924,26 +5945,26 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="H93" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -5953,7 +5974,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
@@ -5963,13 +5984,13 @@
         <v>45</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -5980,7 +6001,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -5990,16 +6011,16 @@
         <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G95" s="1" t="s">
+      <c r="H95" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6009,26 +6030,26 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G96" s="5" t="s">
+      <c r="H96" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6038,7 +6059,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
@@ -6048,16 +6069,16 @@
         <v>44</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="H97" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6067,29 +6088,29 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I98" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>429</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -6098,7 +6119,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
@@ -6108,16 +6129,16 @@
         <v>45</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F99" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G99" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="H99" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6127,7 +6148,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
@@ -6137,16 +6158,16 @@
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="H100" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6156,26 +6177,26 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6185,7 +6206,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
@@ -6195,16 +6216,16 @@
         <v>44</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="H102" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6214,26 +6235,26 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6243,26 +6264,26 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G104" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6272,7 +6293,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
@@ -6282,16 +6303,16 @@
         <v>44</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F105" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G105" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="H105" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6301,26 +6322,26 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="H106" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6330,26 +6351,26 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G107" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>306</v>
-      </c>
       <c r="H107" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6359,26 +6380,26 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="G108" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="H108" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6388,7 +6409,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
@@ -6398,16 +6419,16 @@
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="H109" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6417,7 +6438,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
@@ -6427,16 +6448,16 @@
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F110" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G110" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="H110" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6446,7 +6467,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
@@ -6456,16 +6477,16 @@
         <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="H111" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6475,7 +6496,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
@@ -6485,16 +6506,16 @@
         <v>45</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6504,26 +6525,26 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G113" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G113" s="5" t="s">
+      <c r="H113" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6533,26 +6554,26 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="F114" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G114" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G114" s="5" t="s">
+      <c r="H114" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6562,7 +6583,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
@@ -6572,16 +6593,16 @@
         <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6591,26 +6612,26 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G116" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H116" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6620,26 +6641,26 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -6649,26 +6670,26 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H118" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -6678,147 +6699,147 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E119" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="G119" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="G119" s="10" t="s">
+      <c r="H119" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="I119" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>462</v>
       </c>
       <c r="J119" s="11"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G120" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="F120" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="G120" s="12" t="s">
+      <c r="H120" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="I120" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J120" s="11"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G121" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="G121" s="10" t="s">
+      <c r="H121" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="I121" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J121" s="11"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="G122" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="G122" s="10" t="s">
+      <c r="H122" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="I122" s="11" t="s">
         <v>472</v>
-      </c>
-      <c r="I122" s="11" t="s">
-        <v>473</v>
       </c>
       <c r="J122" s="1"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1" t="s">
-        <v>475</v>
+        <v>287</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="G123" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="H123" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="H123" s="13" t="s">
+      <c r="I123" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="I123" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1" t="s">
@@ -6828,25 +6849,25 @@
         <v>44</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="I124" s="5" t="s">
         <v>483</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>484</v>
       </c>
       <c r="J124" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
@@ -6856,69 +6877,69 @@
         <v>45</v>
       </c>
       <c r="E125" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="G125" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="H125" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="I125" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="J125" s="1"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="F126" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G126" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="F126" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="G126" s="9" t="s">
+      <c r="H126" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="J126" s="1"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="G127" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -6926,254 +6947,254 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E128" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="H128" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="I128" s="6" t="s">
         <v>504</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>505</v>
       </c>
       <c r="J128" s="1"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E129" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E129" s="9" t="s">
+      <c r="F129" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="G129" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="H129" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="I129" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>511</v>
       </c>
       <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E130" s="9" t="s">
+      <c r="F130" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="I130" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="9" t="s">
+      <c r="F131" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E131" s="9" t="s">
+      <c r="G131" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="H131" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E132" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E133" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G134" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E134" s="9" t="s">
+      <c r="H134" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="G134" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B136" s="9">
-        <v>1</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E136" s="9" t="s">
+      <c r="G136" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="H136" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="G136" s="6" t="s">
+      <c r="I136" s="6" t="s">
         <v>536</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>538</v>
       </c>
       <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B137" s="9">
-        <v>2</v>
+        <v>531</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>192</v>
@@ -7182,116 +7203,118 @@
         <v>45</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B138" s="9">
-        <v>2</v>
+        <v>531</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>541</v>
+        <v>192</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E138" s="1"/>
+      <c r="E138" s="1" t="s">
+        <v>539</v>
+      </c>
       <c r="F138" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="I138" s="5" t="s">
         <v>542</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="H138" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="I138" s="5" t="s">
-        <v>544</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B139" s="9">
-        <v>3</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E139" s="9" t="s">
+      <c r="G139" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="F139" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>547</v>
-      </c>
       <c r="I139" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B140" s="9">
-        <v>3</v>
+        <v>531</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>595</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E140" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="H140" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="I140" s="6" t="s">
         <v>549</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>551</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B141" s="9">
-        <v>4</v>
+        <v>531</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>596</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>13</v>
@@ -7300,28 +7323,28 @@
         <v>45</v>
       </c>
       <c r="E141" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>554</v>
-      </c>
       <c r="I141" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B142" s="9">
-        <v>4</v>
+        <v>531</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>596</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>13</v>
@@ -7330,28 +7353,28 @@
         <v>44</v>
       </c>
       <c r="E142" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="H142" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="G142" s="6" t="s">
+      <c r="I142" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>559</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B143" s="9">
-        <v>4</v>
+        <v>531</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>596</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>13</v>
@@ -7360,28 +7383,28 @@
         <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="I143" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>563</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B144" s="9">
-        <v>5</v>
+        <v>531</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>597</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>15</v>
@@ -7390,28 +7413,28 @@
         <v>45</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B145" s="9">
-        <v>5</v>
+        <v>531</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>597</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>157</v>
@@ -7420,28 +7443,28 @@
         <v>45</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G145" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="H145" s="9" t="s">
-        <v>566</v>
-      </c>
       <c r="I145" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B146" s="9">
-        <v>5</v>
+        <v>531</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>597</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>15</v>
@@ -7450,28 +7473,28 @@
         <v>44</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="G146" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="F146" s="14" t="s">
+      <c r="H146" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="I146" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>571</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B147" s="9">
-        <v>5</v>
+        <v>531</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>597</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>157</v>
@@ -7480,125 +7503,126 @@
         <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G147" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="H147" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="I147" s="6" t="s">
         <v>574</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>576</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B148" s="9">
-        <v>6</v>
-      </c>
-      <c r="C148" s="1" t="s">
+      <c r="G148" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="H148" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="H148" s="9" t="s">
-        <v>579</v>
-      </c>
       <c r="I148" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B149" s="9">
-        <v>6</v>
+        <v>531</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F149" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="I149" s="6" t="s">
         <v>580</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>582</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B150" s="4">
-        <v>6</v>
+        <v>531</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E150" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G150" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="F150" s="4" t="s">
+      <c r="H150" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I150" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="I150" s="4" t="s">
-        <v>587</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="J69:J71"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="C69:C71"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:E71"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{6558C59A-CBC3-C44B-BF9F-F7B6D9255B4D}"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4FC69E-1A7B-5440-9B91-5C4B01D01B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209B9E0E-49A5-CD42-B252-6AB040DE8882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35440" yWindow="-4900" windowWidth="32400" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="604">
   <si>
     <t>Villes</t>
   </si>
@@ -2072,9 +2072,6 @@
     <t>aurelie.bedel@u-bordeaux.fr ; julian.boutin@u-bordeaux.fr</t>
   </si>
   <si>
-    <t>Servcie de Biochimie, CHU de Bordeaux</t>
-  </si>
-  <si>
     <t>mariepierre.buisine@chu-lille.fr ; pascal.pigny@chu-lille.fr </t>
   </si>
   <si>
@@ -2804,17 +2801,62 @@
   </si>
   <si>
     <t>Lipides et transfert des lipides dans l'inflammation et le sepsis</t>
+  </si>
+  <si>
+    <t>LBMR diagnostic des maladies constitutionnelles du globule rouge  et de l'érythropoïèse : diagnostic intégratif des pathologies du globule rouge.
+CRMR Centre de référence des syndromes drépanocytaires majeurs, thalassémies et autres pathologies rares du globule rouge et de l'érythropoïèse</t>
+  </si>
+  <si>
+    <t>https://www.bricbordeaux.com/</t>
+  </si>
+  <si>
+    <t>Exploration phénotypique et génotypique des dyslipidémies</t>
+  </si>
+  <si>
+    <r>
+      <t>annie.berard@chu-bordeaux.fr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="10"/>
+        <rFont val="Calibri (Corps)"/>
+      </rPr>
+      <t xml:space="preserve"> ; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>genevieve.lacape@chu-bordeaux.fr ; louis.lebreton@chu-bordeaux.fr</t>
+    </r>
+  </si>
+  <si>
+    <t>Une expertise clinique et biologique reconnue dans l’étude phénotypique des dyslipidémies en lien étroit avec le Centre de dépistage de l’athérosclérose (CEPTA), les services d’Endocrinologie, Neuro-Vasculaire et Pédiatrie réunis dans un Centre Clinico-Biologique en Lipidologie (labellisation NFSA, 2022). La mise en place en janvier 2020, fortement soutenue par le pôle de biologie-pathologie, d’un panel NGS « HF, Sitostérolémie, HTG majeures », permet de compléter l’offre pour une prise en charge globale et adaptée du patient de la Nouvelle Aquitaine. Ce développement s’accompagne d’une forte réduction des délais de rendu des résultats ainsi que des échanges réguliers au plan national avec les collègues des laboratoires bénéficiant de la labellisation en vue de complément d’analyse génétique avec un panel plus étendu, ou de présentation en RCP en vue d’analyse très-haut débit (plateforme Auragen). 
+Un rayonnement pédagogique axé sur les apports en santé publique matérialisé par la diffusion d’informations (diagnostic - prise en charge thérapeutique - prévention) et l’animation de formations continues auprès des professionnels de santé.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2970,6 +3012,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri (Corps)"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2996,27 +3043,37 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3233,7 +3290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1"/>
@@ -3242,8 +3299,8 @@
     <col min="4" max="4" width="22.5" style="4" customWidth="1"/>
     <col min="5" max="5" width="55.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="79.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="213" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="60.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="76.6640625" style="4" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -3280,7 +3337,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3294,7 +3351,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>395</v>
@@ -3302,8 +3359,12 @@
       <c r="G2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="18" t="s">
+        <v>599</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>600</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -3329,13 +3390,13 @@
         <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3392,7 +3453,7 @@
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>54</v>
@@ -3437,28 +3498,30 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="241" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>388</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>438</v>
+        <v>45</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>601</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>395</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>603</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -3478,16 +3541,16 @@
         <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>58</v>
+        <v>437</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -3504,19 +3567,19 @@
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -3530,22 +3593,22 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -3565,16 +3628,16 @@
         <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3594,16 +3657,16 @@
         <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -3620,19 +3683,19 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>398</v>
+        <v>29</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -3652,16 +3715,16 @@
         <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>34</v>
+      <c r="G14" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -3675,22 +3738,22 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>35</v>
+      <c r="G15" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -3710,16 +3773,16 @@
         <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>439</v>
+        <v>27</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>60</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -3733,22 +3796,22 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>343</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>438</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>37</v>
+      <c r="G17" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -3758,26 +3821,26 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -3797,16 +3860,16 @@
         <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -3820,22 +3883,22 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>344</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>440</v>
+        <v>66</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -3849,22 +3912,22 @@
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>107</v>
+      <c r="G21" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -3884,16 +3947,16 @@
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>74</v>
+      <c r="G22" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3907,22 +3970,22 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>343</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -3936,13 +3999,13 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>13</v>
+        <v>343</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -3951,7 +4014,7 @@
         <v>76</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -3961,26 +4024,26 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>407</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3997,18 +4060,20 @@
         <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -4027,13 +4092,13 @@
         <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>84</v>
+      <c r="G27" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -4054,13 +4119,13 @@
         <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -4075,19 +4140,19 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -4098,27 +4163,25 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>345</v>
+        <v>449</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>346</v>
+        <v>411</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -4131,22 +4194,22 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>13</v>
+        <v>345</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -4156,26 +4219,26 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -4189,24 +4252,24 @@
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I33" s="8"/>
+        <v>94</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -4221,48 +4284,48 @@
         <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>413</v>
+        <v>96</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I34" s="1"/>
+        <v>97</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I34" s="8"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>344</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>102</v>
+      <c r="G35" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -4270,28 +4333,28 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>7</v>
+        <v>344</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -4305,22 +4368,22 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>345</v>
+        <v>7</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>99</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -4334,22 +4397,22 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>15</v>
+        <v>345</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>386</v>
+        <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>106</v>
+        <v>415</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>115</v>
+      <c r="G38" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -4359,26 +4422,26 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>44</v>
+        <v>386</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>120</v>
+        <v>99</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -4392,22 +4455,22 @@
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -4421,22 +4484,22 @@
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>124</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -4446,28 +4509,28 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G42" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>132</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -4475,30 +4538,28 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>347</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>348</v>
+        <v>130</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>136</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G43" s="6"/>
       <c r="H43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I43" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4512,22 +4573,22 @@
         <v>347</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>135</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -4543,22 +4604,22 @@
         <v>347</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>350</v>
+        <v>139</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -4574,22 +4635,22 @@
         <v>347</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>351</v>
+        <v>441</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>141</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>143</v>
+        <v>350</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4602,25 +4663,25 @@
         <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>391</v>
+        <v>347</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4639,19 +4700,19 @@
         <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>417</v>
+        <v>352</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -4667,22 +4728,22 @@
         <v>391</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>353</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>354</v>
+        <v>416</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -4698,13 +4759,13 @@
         <v>391</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>15</v>
+        <v>353</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>150</v>
@@ -4713,7 +4774,7 @@
         <v>151</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -4729,22 +4790,22 @@
         <v>391</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4760,22 +4821,22 @@
         <v>391</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>155</v>
+      <c r="G52" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4788,25 +4849,25 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>157</v>
+        <v>449</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4822,22 +4883,22 @@
         <v>392</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>420</v>
+        <v>356</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>159</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4856,19 +4917,19 @@
         <v>13</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>159</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>444</v>
+        <v>162</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4881,25 +4942,25 @@
         <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>345</v>
+        <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>166</v>
+        <v>443</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -4915,22 +4976,22 @@
         <v>393</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>157</v>
+        <v>345</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -4949,19 +5010,19 @@
         <v>157</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4983,16 +5044,16 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>172</v>
+      <c r="G59" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -5008,22 +5069,22 @@
         <v>393</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -5036,25 +5097,25 @@
         <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>362</v>
+        <v>163</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>363</v>
+        <v>174</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>364</v>
+        <v>175</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -5073,23 +5134,21 @@
         <v>15</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>404</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -5109,16 +5168,20 @@
         <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>420</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>365</v>
+      </c>
       <c r="G63" s="5" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="I63" s="1"/>
+        <v>366</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>403</v>
+      </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -5126,94 +5189,94 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>176</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="C64" s="1" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>386</v>
+        <v>45</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="5"/>
+        <v>421</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>386</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I65" s="1"/>
+        <v>179</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="I65" s="9"/>
       <c r="J65" s="5"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>45</v>
+        <v>386</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>371</v>
+        <v>181</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>372</v>
+        <v>183</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
+      <c r="J66" s="5"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -5226,13 +5289,13 @@
         <v>340</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>185</v>
+        <v>371</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>187</v>
+        <v>372</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -5242,126 +5305,126 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>188</v>
+        <v>452</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>373</v>
+        <v>7</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>374</v>
+        <v>45</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>189</v>
+      <c r="F68" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="5"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16" t="s">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D70" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="E70" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F70" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G69" s="15" t="s">
+      <c r="G70" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="H70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="I69" s="17"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="16"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="9" t="s">
+      <c r="I70" s="16"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G70" s="15"/>
-      <c r="H70" s="9" t="s">
+      <c r="G71" s="17"/>
+      <c r="H71" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="16"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="9" t="s">
+      <c r="I71" s="16"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I71" s="17"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
@@ -5369,7 +5432,7 @@
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>192</v>
+        <v>373</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>45</v>
@@ -5378,15 +5441,15 @@
         <v>340</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="I73" s="1"/>
+        <v>194</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="I73" s="9"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -5398,7 +5461,7 @@
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>45</v>
@@ -5407,12 +5470,14 @@
         <v>340</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>197</v>
+        <v>381</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H74" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -5421,29 +5486,27 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="5"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -5459,17 +5522,17 @@
       <c r="D76" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>203</v>
+      <c r="E76" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>200</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="5"/>
@@ -5486,22 +5549,22 @@
         <v>15</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>382</v>
+        <v>205</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="J77" s="5"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -5515,19 +5578,19 @@
         <v>15</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>211</v>
+        <v>45</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>212</v>
+        <v>382</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5541,22 +5604,22 @@
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
-        <v>213</v>
+        <v>15</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>445</v>
+        <v>44</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5566,29 +5629,29 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>218</v>
+        <v>444</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I80" s="1"/>
-      <c r="J80" s="5"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -5599,25 +5662,25 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>386</v>
+        <v>44</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>446</v>
+        <v>218</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="J81" s="5"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -5628,22 +5691,22 @@
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>386</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5657,22 +5720,22 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>228</v>
+        <v>449</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>386</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5682,84 +5745,84 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>454</v>
+        <v>217</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
-        <v>7</v>
+        <v>228</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>44</v>
+        <v>386</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>231</v>
+        <v>447</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I84" s="1"/>
-      <c r="J84" s="5"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="J85" s="5"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>228</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5769,26 +5832,26 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5798,26 +5861,26 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
-        <v>15</v>
+        <v>242</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5827,26 +5890,26 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>192</v>
+        <v>15</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>423</v>
+        <v>246</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5856,26 +5919,26 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>251</v>
+        <v>422</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -5885,30 +5948,28 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>343</v>
+        <v>157</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>424</v>
+        <v>251</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>255</v>
+        <v>236</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>425</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -5920,24 +5981,26 @@
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>257</v>
+        <v>423</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I92" s="1"/>
+        <v>256</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>424</v>
+      </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -5949,22 +6012,22 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>343</v>
+        <v>449</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -5978,21 +6041,23 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>426</v>
+        <v>261</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="H94" s="1"/>
+        <v>262</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -6011,17 +6076,15 @@
         <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>267</v>
+        <v>425</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>265</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -6034,22 +6097,22 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>343</v>
+        <v>15</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>271</v>
+      <c r="G96" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6059,26 +6122,26 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>7</v>
+        <v>343</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6092,26 +6155,24 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>452</v>
+        <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>427</v>
+        <v>274</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>428</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -6123,24 +6184,26 @@
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I99" s="1"/>
+        <v>280</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>427</v>
+      </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -6152,22 +6215,22 @@
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6181,22 +6244,22 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>287</v>
+        <v>15</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>284</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6206,26 +6269,26 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>122</v>
+        <v>287</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>290</v>
+        <v>429</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6239,22 +6302,22 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>343</v>
+        <v>122</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>431</v>
+        <v>290</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>292</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6274,16 +6337,16 @@
         <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>294</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6297,22 +6360,22 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>13</v>
+        <v>343</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6322,26 +6385,26 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>302</v>
+        <v>13</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>303</v>
+        <v>432</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6355,13 +6418,13 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>434</v>
+        <v>303</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>304</v>
@@ -6370,7 +6433,7 @@
         <v>305</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6384,22 +6447,22 @@
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>308</v>
+        <v>433</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6413,22 +6476,22 @@
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
-        <v>13</v>
+        <v>344</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6448,16 +6511,16 @@
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>449</v>
+        <v>312</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6471,22 +6534,22 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>319</v>
+        <v>448</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6500,22 +6563,22 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>435</v>
+        <v>319</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6529,22 +6592,22 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>326</v>
+        <v>434</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>327</v>
+      <c r="G113" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6558,22 +6621,22 @@
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>329</v>
+        <v>449</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>323</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6587,22 +6650,22 @@
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>436</v>
+        <v>330</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>323</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6616,22 +6679,22 @@
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>323</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6645,13 +6708,13 @@
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>336</v>
+        <v>436</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>323</v>
@@ -6660,7 +6723,7 @@
         <v>334</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -6674,13 +6737,13 @@
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>323</v>
@@ -6689,7 +6752,7 @@
         <v>334</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -6699,682 +6762,681 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>455</v>
+        <v>301</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>457</v>
+        <v>338</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>459</v>
+        <v>323</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="J119" s="11"/>
+        <v>339</v>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F120" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G120" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="G120" s="12" t="s">
-        <v>463</v>
-      </c>
       <c r="H120" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J120" s="11"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>466</v>
+        <v>457</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>462</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J121" s="11"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I122" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="J122" s="1"/>
+        <v>466</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="J122" s="11"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1" t="s">
-        <v>287</v>
+        <v>455</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="H123" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="I123" s="5" t="s">
-        <v>478</v>
+        <v>468</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>471</v>
       </c>
       <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1" t="s">
-        <v>13</v>
+        <v>287</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>476</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="J124" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E125" s="9" t="s">
-        <v>484</v>
+        <v>44</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>486</v>
+        <v>479</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="J125" s="1"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
-        <v>489</v>
+        <v>15</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>490</v>
+      <c r="E126" s="9" t="s">
+        <v>483</v>
       </c>
       <c r="F126" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G126" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="G126" s="9" t="s">
-        <v>491</v>
-      </c>
       <c r="H126" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="J126" s="1"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>495</v>
+        <v>45</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
+        <v>484</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>492</v>
+      </c>
       <c r="J127" s="1"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
-        <v>15</v>
+        <v>493</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>386</v>
+        <v>494</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>504</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
       <c r="J128" s="1"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
-        <v>505</v>
+        <v>15</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>506</v>
+        <v>386</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="F130" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="G130" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>502</v>
-      </c>
       <c r="H130" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="s">
-        <v>344</v>
+        <v>510</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>517</v>
+        <v>506</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="I131" s="1"/>
+        <v>512</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>509</v>
+      </c>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>511</v>
+        <v>344</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F132" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="G132" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="G132" s="9" t="s">
-        <v>520</v>
-      </c>
       <c r="H132" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>228</v>
+        <v>510</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>529</v>
+      <c r="E135" s="9" t="s">
+        <v>525</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>592</v>
+        <v>526</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>527</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="B136" s="9" t="s">
-        <v>593</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>287</v>
+        <v>455</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E136" s="9" t="s">
-        <v>532</v>
+      <c r="E136" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>534</v>
+        <v>515</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>529</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>536</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="I136" s="1"/>
       <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E137" s="9" t="s">
-        <v>586</v>
-      </c>
       <c r="F137" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G137" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="G137" s="6" t="s">
-        <v>537</v>
-      </c>
       <c r="H137" s="9" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>192</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>539</v>
+        <v>45</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>585</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="H138" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="H138" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="I138" s="5" t="s">
-        <v>542</v>
+      <c r="I138" s="6" t="s">
+        <v>535</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>511</v>
+        <v>192</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>543</v>
+        <v>44</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>541</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="H140" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="H140" s="9" t="s">
-        <v>548</v>
-      </c>
       <c r="I140" s="6" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>13</v>
+        <v>510</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>557</v>
+        <v>551</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>535</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>13</v>
@@ -7383,246 +7445,276 @@
         <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>591</v>
+        <v>44</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>557</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>536</v>
+        <v>559</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>560</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G145" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="H145" s="9" t="s">
-        <v>564</v>
-      </c>
       <c r="I145" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="F146" s="14" t="s">
-        <v>566</v>
+        <v>588</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>571</v>
+        <v>564</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>565</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>575</v>
+        <v>157</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="J148" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="J148" s="1"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>456</v>
+        <v>574</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="G149" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="H149" s="9" t="s">
-        <v>579</v>
-      </c>
       <c r="I149" s="6" t="s">
-        <v>580</v>
+        <v>535</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="C150" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="D150" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E150" s="4" t="s">
+      <c r="F151" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="F150" s="4" t="s">
+      <c r="G151" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="H151" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I151" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="I150" s="4" t="s">
-        <v>585</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="E69:E71"/>
+    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="D70:D72"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="K70:K72"/>
+    <mergeCell ref="L70:L72"/>
+    <mergeCell ref="M70:M72"/>
+    <mergeCell ref="I70:I72"/>
+    <mergeCell ref="J70:J72"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{6558C59A-CBC3-C44B-BF9F-F7B6D9255B4D}"/>
@@ -7630,94 +7722,95 @@
     <hyperlink ref="I4" r:id="rId4" xr:uid="{BAAAF0CB-3D5A-5949-A37D-A2C50B731AF0}"/>
     <hyperlink ref="G5" r:id="rId5" display="mailto:aurelie.bedel@u-bordeaux.fr" xr:uid="{02C0CB78-D29E-3647-B6CB-37D7CECADEFF}"/>
     <hyperlink ref="G6" r:id="rId6" display="mailto:marie-lise.bats@u-bordeaux.fr" xr:uid="{B179A81E-13D4-BA4C-AA82-773B4AF2D1E7}"/>
-    <hyperlink ref="G7" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{19818837-D83A-EF46-9A87-56DA857E21BF}"/>
-    <hyperlink ref="G8" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{404568B7-5E84-374C-86CF-5AD4367A7135}"/>
-    <hyperlink ref="G9" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{56D59BBB-465E-5641-A9F7-F2E5A28229DE}"/>
-    <hyperlink ref="G10" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{4E0E266F-A36A-534A-B732-B257A8710410}"/>
-    <hyperlink ref="G11" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{238F2984-E507-AD4C-9ECF-593475C4AD53}"/>
-    <hyperlink ref="G12" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{59075E53-0EBC-4847-9B63-F640FE924229}"/>
-    <hyperlink ref="G14" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{FD096503-D7B9-264C-BCDB-6BD7CB031C27}"/>
-    <hyperlink ref="G17" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{6018113E-52E5-C546-A726-3F07B4FE62D1}"/>
-    <hyperlink ref="G18" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{11482541-6756-4F49-BF84-994EA57212DF}"/>
-    <hyperlink ref="G20" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{DAEFBA44-5260-BA46-A86D-12F5080D70ED}"/>
-    <hyperlink ref="G22" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{85EE1029-98D3-FD47-9068-97CB0579190C}"/>
-    <hyperlink ref="G23" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{97E273A2-52B9-3D40-8872-1FDA66D1E846}"/>
-    <hyperlink ref="G24" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{9ACC63ED-843A-1045-B9B4-12C07C6CEEF8}"/>
-    <hyperlink ref="G27" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{E44DE2B2-25F7-B24B-A4C8-DB3BCCB7115A}"/>
-    <hyperlink ref="G28" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{C52AC72E-5EC3-8F41-98E3-28B2046ECD73}"/>
-    <hyperlink ref="G29" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{C417B978-A9E9-5447-B082-5172C07882E5}"/>
-    <hyperlink ref="G30" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{01A97F3F-1FE0-EC4D-99BE-5C9365E3A43D}"/>
-    <hyperlink ref="G31" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{5A0CDA27-8A97-3B48-B26C-414861879147}"/>
-    <hyperlink ref="G35" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{1F8902C9-7758-2940-B6B9-A168EDA21EAF}"/>
-    <hyperlink ref="G36" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{929EE593-D0FD-D445-B1BA-A3F8FDE6676B}"/>
-    <hyperlink ref="G37" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{F8EAC02E-BC4B-1743-837D-130A329FD052}"/>
-    <hyperlink ref="G39" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{234156F7-C14A-5241-8C74-AC721D0B56D3}"/>
-    <hyperlink ref="G40" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{4104F0D0-6CA0-7745-9468-257A4D0EB98A}"/>
-    <hyperlink ref="G41" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{B3F0F384-6218-3C46-94BE-75DF28DEDE7D}"/>
-    <hyperlink ref="I42" r:id="rId31" xr:uid="{0003CCF9-EA24-0144-80EF-A2FF95FFB6BB}"/>
-    <hyperlink ref="G43" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{8C451BC4-2DFB-5349-809D-05DE4C13DC67}"/>
-    <hyperlink ref="G44" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{455F44C0-7170-FB4F-8C6C-AB8C917AA32A}"/>
-    <hyperlink ref="G45" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{93ECACD7-0694-B648-AFEC-19945C5C57B3}"/>
-    <hyperlink ref="G46" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{E3A16A9D-DB36-2242-8C7D-12538308719E}"/>
-    <hyperlink ref="G49" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{04B47570-CEC1-044B-AC1A-8CBC673D5394}"/>
-    <hyperlink ref="G50" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{E10E3A24-FD55-3742-8FB8-E26FA664F94B}"/>
-    <hyperlink ref="G52" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{A8019C87-9474-4640-BCD9-2055202E563E}"/>
-    <hyperlink ref="G56" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{0F757E56-F0FF-2F42-BF04-27A891E0C555}"/>
-    <hyperlink ref="G57" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{EE7E9BD7-2E97-284D-967F-980B6482DBBE}"/>
-    <hyperlink ref="G59" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{8F52C470-C988-F24E-80D8-2BB657183BDB}"/>
-    <hyperlink ref="G60" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{46B2D7A6-145C-D64A-965C-67B6F6E3EC45}"/>
-    <hyperlink ref="G61" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{B6355616-C748-2843-B2A4-23E1CD69DD85}"/>
-    <hyperlink ref="G62" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{A28932E3-6128-D94F-93FF-5ACBF7A494B9}"/>
-    <hyperlink ref="I62" r:id="rId45" xr:uid="{B7B830C0-9819-CF4F-B723-139CB3C06E36}"/>
-    <hyperlink ref="G63" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{FFE59264-E4BA-9E44-B049-3C100E12BAA2}"/>
-    <hyperlink ref="G65" r:id="rId47" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{E38C53B5-D9E5-BF46-B199-B3E05A4ECBDD}"/>
-    <hyperlink ref="G66" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{CB824271-CE19-BC43-984A-01DFAF3C5B8E}"/>
-    <hyperlink ref="G67" r:id="rId49" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{179CFA47-2DA9-6F47-BACD-C3795C2639BA}"/>
-    <hyperlink ref="G68" r:id="rId50" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{EAEA8176-0963-7B40-9B2E-6B1CD4350D39}"/>
-    <hyperlink ref="G69" r:id="rId51" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{41EC90D8-78AD-1347-B375-8A9B98A00B2F}"/>
-    <hyperlink ref="G72" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{2DCD5A92-89BD-AC41-BE57-66B810FFA4A0}"/>
-    <hyperlink ref="G73" r:id="rId53" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{B2BCC955-005F-2F46-9B3A-23D752748141}"/>
-    <hyperlink ref="G74" r:id="rId54" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{D5E0083D-BEBA-DE4D-8DDC-F8DCD6348245}"/>
-    <hyperlink ref="G78" r:id="rId55" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{071E93FF-793D-0C4D-8ACA-64C68480C477}"/>
-    <hyperlink ref="G80" r:id="rId56" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{2E60772F-7DD4-D840-B17D-D87298E8D727}"/>
-    <hyperlink ref="G81" r:id="rId57" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{E9A03AF6-835B-864C-B71C-4627011D122A}"/>
-    <hyperlink ref="G82" r:id="rId58" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{F1A3246B-6EA8-364A-9FFC-4DB1BD34757B}"/>
-    <hyperlink ref="G91" r:id="rId59" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{BACD0B47-68EA-6047-9EBB-25E94902B24A}"/>
-    <hyperlink ref="I91" r:id="rId60" xr:uid="{74EED5C1-17AE-2E4A-9F07-DC464F938DA3}"/>
-    <hyperlink ref="G92" r:id="rId61" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{6D04C2AF-9625-3442-ADF8-CD0024E1FA55}"/>
-    <hyperlink ref="G93" r:id="rId62" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{7B7A75DE-8938-2045-8EB3-81788847B8C9}"/>
-    <hyperlink ref="G96" r:id="rId63" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{E307BDF4-2C0A-F94F-97AF-C5C43BCA00CA}"/>
-    <hyperlink ref="G97" r:id="rId64" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{0C78F5DE-A083-0742-B61B-C56D7084F18D}"/>
-    <hyperlink ref="G98" r:id="rId65" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{63EA7B8F-206E-E843-A40E-20993359E6D5}"/>
-    <hyperlink ref="I98" r:id="rId66" xr:uid="{74FEA717-1429-7B46-B57E-05A7EEA92161}"/>
-    <hyperlink ref="G99" r:id="rId67" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{7CFF7B10-439A-5D41-A23B-221F96517AF4}"/>
-    <hyperlink ref="G100" r:id="rId68" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{6C1FBD82-1CBF-7641-BBD3-F135C24FB0A0}"/>
-    <hyperlink ref="G101" r:id="rId69" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{B97089C4-568E-C04A-A7DF-3CE2E4364FAC}"/>
-    <hyperlink ref="G102" r:id="rId70" display="mailto:sjaisson@chu-reims.fr" xr:uid="{82FFFC16-2B6E-EE46-B62E-3B449DBF62F4}"/>
-    <hyperlink ref="G103" r:id="rId71" display="mailto:sjaisson@chu-reims.fr" xr:uid="{03ABDE49-B71A-114B-BBB0-4385451EA80F}"/>
-    <hyperlink ref="G104" r:id="rId72" display="mailto:dmarot@chu-reims.fr" xr:uid="{914E30D8-AE96-B146-AE96-A665020529BE}"/>
-    <hyperlink ref="G105" r:id="rId73" display="mailto:lramont@chu-reims.fr" xr:uid="{4EAA1429-669C-404A-B2EA-0C34ACC3BF21}"/>
-    <hyperlink ref="G106" r:id="rId74" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{98B90DDB-72C1-084D-9498-7CD8298183A4}"/>
-    <hyperlink ref="G107" r:id="rId75" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{84031370-A25E-DA46-9109-9E603E92176E}"/>
-    <hyperlink ref="G108" r:id="rId76" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{49C350B4-6874-1649-919A-BC1C4D8764E2}"/>
-    <hyperlink ref="G109" r:id="rId77" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{B17F1D67-CE4D-F547-88E0-DADEC10457F8}"/>
-    <hyperlink ref="G110" r:id="rId78" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{4955350F-AD67-2D49-AB6D-3BCEB89B72ED}"/>
-    <hyperlink ref="G113" r:id="rId79" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{284F1AAC-C96E-4741-85C2-FE59EFD6D21A}"/>
-    <hyperlink ref="G114" r:id="rId80" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{25612B46-6B22-A74D-8FCA-F5C470BB17BE}"/>
-    <hyperlink ref="G115" r:id="rId81" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{BD192653-5DC9-0E48-85F2-420E7B710C1D}"/>
-    <hyperlink ref="G116" r:id="rId82" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{5C1F7FBB-0230-2240-BD70-9EDC6C0A085C}"/>
-    <hyperlink ref="G117" r:id="rId83" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{BF20034E-2F10-4D4F-A4C3-CB8CF25AFA9F}"/>
-    <hyperlink ref="G118" r:id="rId84" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{B41A5A99-7810-404B-BE81-E5BEB0F3010B}"/>
-    <hyperlink ref="I119" r:id="rId85" xr:uid="{6BC9BD55-8FEE-4942-A5E6-4F02914FAF04}"/>
-    <hyperlink ref="I120" r:id="rId86" xr:uid="{E244D2FF-3F85-F54A-99A7-243B07A96F1F}"/>
-    <hyperlink ref="I121" r:id="rId87" xr:uid="{6C24E5F5-2AFA-B548-B37F-B150439BC3E9}"/>
-    <hyperlink ref="I123" r:id="rId88" xr:uid="{6C9A006B-B605-104B-A1A2-D37DBDD74AC8}"/>
-    <hyperlink ref="I124" r:id="rId89" xr:uid="{1CF3150B-FE16-5941-A388-6827A20A78BA}"/>
-    <hyperlink ref="G125" r:id="rId90" display="mailto:raphael.thuillier@univ-poitiers.fr" xr:uid="{6E305BED-08D9-4D4B-8E6C-3B1379139897}"/>
-    <hyperlink ref="G130" r:id="rId91" display="http://deprunier@chu-angers.fr" xr:uid="{B6320878-3C15-DB42-8AD1-ABCF15930065}"/>
-    <hyperlink ref="I138" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
-    <hyperlink ref="I142" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
-    <hyperlink ref="I143" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
+    <hyperlink ref="G8" r:id="rId7" display="mailto:claire-marie.dhaenens@inserm.fr" xr:uid="{19818837-D83A-EF46-9A87-56DA857E21BF}"/>
+    <hyperlink ref="G9" r:id="rId8" display="mailto:vincent.huin@inserm.fr" xr:uid="{404568B7-5E84-374C-86CF-5AD4367A7135}"/>
+    <hyperlink ref="G10" r:id="rId9" display="mailto:susanna.schraen@chu-lille.fr" xr:uid="{56D59BBB-465E-5641-A9F7-F2E5A28229DE}"/>
+    <hyperlink ref="G11" r:id="rId10" display="mailto:julie.leclerc@inserm.fr" xr:uid="{4E0E266F-A36A-534A-B732-B257A8710410}"/>
+    <hyperlink ref="G12" r:id="rId11" display="mailto:nicolas.pottier@univ-lille.fr" xr:uid="{238F2984-E507-AD4C-9ECF-593475C4AD53}"/>
+    <hyperlink ref="G13" r:id="rId12" display="mailto:lucie.coppin@inserm.fr" xr:uid="{59075E53-0EBC-4847-9B63-F640FE924229}"/>
+    <hyperlink ref="G15" r:id="rId13" display="mailto:fabienne.escande@chu-lille.fr" xr:uid="{FD096503-D7B9-264C-BCDB-6BD7CB031C27}"/>
+    <hyperlink ref="G18" r:id="rId14" display="mailto:pascal.pigny@chu-lille.fr" xr:uid="{6018113E-52E5-C546-A726-3F07B4FE62D1}"/>
+    <hyperlink ref="G19" r:id="rId15" tooltip="mailto:jerome.ausseil@inserm.fr" display="mailto:jerome.ausseil@inserm.fr" xr:uid="{11482541-6756-4F49-BF84-994EA57212DF}"/>
+    <hyperlink ref="G21" r:id="rId16" display="mailto:hamdi.s@chu-toulouse.fr" xr:uid="{DAEFBA44-5260-BA46-A86D-12F5080D70ED}"/>
+    <hyperlink ref="G23" r:id="rId17" tooltip="mailto:gennero.i@chu-toulouse.fr" display="mailto:gennero.i@chu-toulouse.fr" xr:uid="{85EE1029-98D3-FD47-9068-97CB0579190C}"/>
+    <hyperlink ref="G24" r:id="rId18" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{97E273A2-52B9-3D40-8872-1FDA66D1E846}"/>
+    <hyperlink ref="G25" r:id="rId19" tooltip="mailto:savagner.f@chu-toulouse.fr" display="mailto:savagner.f@chu-toulouse.fr" xr:uid="{9ACC63ED-843A-1045-B9B4-12C07C6CEEF8}"/>
+    <hyperlink ref="G28" r:id="rId20" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{E44DE2B2-25F7-B24B-A4C8-DB3BCCB7115A}"/>
+    <hyperlink ref="G29" r:id="rId21" display="mailto:c.malaplate@chru-nancy.fr" xr:uid="{C52AC72E-5EC3-8F41-98E3-28B2046ECD73}"/>
+    <hyperlink ref="G30" r:id="rId22" display="mailto:abderrahim.oussalah@univ-lorraine.fr" xr:uid="{C417B978-A9E9-5447-B082-5172C07882E5}"/>
+    <hyperlink ref="G31" r:id="rId23" display="mailto:said.kamel@u-picardie.fr" xr:uid="{01A97F3F-1FE0-EC4D-99BE-5C9365E3A43D}"/>
+    <hyperlink ref="G32" r:id="rId24" tooltip="mailto:Galmiche.Antoine@chu-amiens.fr" display="mailto:Galmiche.Antoine@chu-amiens.fr" xr:uid="{5A0CDA27-8A97-3B48-B26C-414861879147}"/>
+    <hyperlink ref="G36" r:id="rId25" tooltip="mailto:piver_e@med.univ-tours.fr" display="mailto:piver_e@med.univ-tours.fr" xr:uid="{1F8902C9-7758-2940-B6B9-A168EDA21EAF}"/>
+    <hyperlink ref="G37" r:id="rId26" tooltip="mailto:patrick.vourch@univ-tours.fr" display="mailto:patrick.vourch@univ-tours.fr" xr:uid="{929EE593-D0FD-D445-B1BA-A3F8FDE6676B}"/>
+    <hyperlink ref="G38" r:id="rId27" tooltip="mailto:charlotte.veyratdurebex@univ-tours.fr" display="mailto:charlotte.veyratdurebex@univ-tours.fr" xr:uid="{F8EAC02E-BC4B-1743-837D-130A329FD052}"/>
+    <hyperlink ref="G40" r:id="rId28" tooltip="mailto:art-arnm@inserm.fr" display="mailto:art-arnm@inserm.fr" xr:uid="{234156F7-C14A-5241-8C74-AC721D0B56D3}"/>
+    <hyperlink ref="G41" r:id="rId29" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{4104F0D0-6CA0-7745-9468-257A4D0EB98A}"/>
+    <hyperlink ref="G42" r:id="rId30" display="mailto:thibaut.eguether@univ-orleans.fr" xr:uid="{B3F0F384-6218-3C46-94BE-75DF28DEDE7D}"/>
+    <hyperlink ref="I43" r:id="rId31" xr:uid="{0003CCF9-EA24-0144-80EF-A2FF95FFB6BB}"/>
+    <hyperlink ref="G44" r:id="rId32" display="mailto:helene.blons@aphp.fr" xr:uid="{8C451BC4-2DFB-5349-809D-05DE4C13DC67}"/>
+    <hyperlink ref="G45" r:id="rId33" display="mailto:nicolas.pallet@aphp.fr" xr:uid="{455F44C0-7170-FB4F-8C6C-AB8C917AA32A}"/>
+    <hyperlink ref="G46" r:id="rId34" display="mailto:marie-anne.loriot@aphp.fr" xr:uid="{93ECACD7-0694-B648-AFEC-19945C5C57B3}"/>
+    <hyperlink ref="G47" r:id="rId35" display="mailto:helene.blons@aphp.fr" xr:uid="{E3A16A9D-DB36-2242-8C7D-12538308719E}"/>
+    <hyperlink ref="G50" r:id="rId36" display="mailto:sophie.valleix@aphp.fr" xr:uid="{04B47570-CEC1-044B-AC1A-8CBC673D5394}"/>
+    <hyperlink ref="G51" r:id="rId37" display="mailto:sophie.valleix@aphp.fr" xr:uid="{E10E3A24-FD55-3742-8FB8-E26FA664F94B}"/>
+    <hyperlink ref="G53" r:id="rId38" display="mailto:laurence.cuisset@aphp.fr" xr:uid="{A8019C87-9474-4640-BCD9-2055202E563E}"/>
+    <hyperlink ref="G57" r:id="rId39" display="mailto:bijan.ghaleh@inserm.fr" xr:uid="{0F757E56-F0FF-2F42-BF04-27A891E0C555}"/>
+    <hyperlink ref="G58" r:id="rId40" display="mailto:commandes-equipes.imrb@inserm.fr" xr:uid="{EE7E9BD7-2E97-284D-967F-980B6482DBBE}"/>
+    <hyperlink ref="G60" r:id="rId41" display="mailto:c-ref-globulerouge.hmn@aphp.fr" xr:uid="{8F52C470-C988-F24E-80D8-2BB657183BDB}"/>
+    <hyperlink ref="G61" r:id="rId42" display="mailto:soraya.fellahi@aphp.fr;" xr:uid="{46B2D7A6-145C-D64A-965C-67B6F6E3EC45}"/>
+    <hyperlink ref="G62" r:id="rId43" display="mailto:mariano.ostuni@inserm.fr" xr:uid="{B6355616-C748-2843-B2A4-23E1CD69DD85}"/>
+    <hyperlink ref="G63" r:id="rId44" display="mailto:arnaud.bruneel@aphp.fr" xr:uid="{A28932E3-6128-D94F-93FF-5ACBF7A494B9}"/>
+    <hyperlink ref="I63" r:id="rId45" xr:uid="{B7B830C0-9819-CF4F-B723-139CB3C06E36}"/>
+    <hyperlink ref="G64" r:id="rId46" display="mailto:katell.peoch@aphp.fr" xr:uid="{FFE59264-E4BA-9E44-B049-3C100E12BAA2}"/>
+    <hyperlink ref="G66" r:id="rId47" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{E38C53B5-D9E5-BF46-B199-B3E05A4ECBDD}"/>
+    <hyperlink ref="G67" r:id="rId48" tooltip="mailto:vsapin@chu-clermontferrand.fr" display="mailto:vsapin@chu-clermontferrand.fr" xr:uid="{CB824271-CE19-BC43-984A-01DFAF3C5B8E}"/>
+    <hyperlink ref="G68" r:id="rId49" display="mailto:isabelle.creveaux@uca.fr" xr:uid="{179CFA47-2DA9-6F47-BACD-C3795C2639BA}"/>
+    <hyperlink ref="G69" r:id="rId50" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{EAEA8176-0963-7B40-9B2E-6B1CD4350D39}"/>
+    <hyperlink ref="G70" r:id="rId51" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{41EC90D8-78AD-1347-B375-8A9B98A00B2F}"/>
+    <hyperlink ref="G73" r:id="rId52" tooltip="mailto:allouche-s@chu-caen.fr" display="mailto:allouche-s@chu-caen.fr" xr:uid="{2DCD5A92-89BD-AC41-BE57-66B810FFA4A0}"/>
+    <hyperlink ref="G74" r:id="rId53" tooltip="mailto:coulbault-l@chu-caen.fr" display="mailto:coulbault-l@chu-caen.fr" xr:uid="{B2BCC955-005F-2F46-9B3A-23D752748141}"/>
+    <hyperlink ref="G75" r:id="rId54" tooltip="mailto:nowoczyn-m@chu-caen.fr" display="mailto:nowoczyn-m@chu-caen.fr" xr:uid="{D5E0083D-BEBA-DE4D-8DDC-F8DCD6348245}"/>
+    <hyperlink ref="G79" r:id="rId55" display="mailto:segolene.gambert@chu-dijon.fr" xr:uid="{071E93FF-793D-0C4D-8ACA-64C68480C477}"/>
+    <hyperlink ref="G81" r:id="rId56" tooltip="mailto:alegouellec@chu-grenoble.fr" display="mailto:alegouellec@chu-grenoble.fr" xr:uid="{2E60772F-7DD4-D840-B17D-D87298E8D727}"/>
+    <hyperlink ref="G82" r:id="rId57" tooltip="mailto:jfaure1@chu-grenoble.fr" display="mailto:jfaure1@chu-grenoble.fr" xr:uid="{E9A03AF6-835B-864C-B71C-4627011D122A}"/>
+    <hyperlink ref="G83" r:id="rId58" tooltip="mailto:jrendu@chu-grenoble.fr" display="mailto:jrendu@chu-grenoble.fr" xr:uid="{F1A3246B-6EA8-364A-9FFC-4DB1BD34757B}"/>
+    <hyperlink ref="G92" r:id="rId59" display="mailto:anne.barlier@univ-amu.fr" xr:uid="{BACD0B47-68EA-6047-9EBB-25E94902B24A}"/>
+    <hyperlink ref="I92" r:id="rId60" xr:uid="{74EED5C1-17AE-2E4A-9F07-DC464F938DA3}"/>
+    <hyperlink ref="G93" r:id="rId61" display="mailto:anne.barlier@ap-hm.fr" xr:uid="{6D04C2AF-9625-3442-ADF8-CD0024E1FA55}"/>
+    <hyperlink ref="G94" r:id="rId62" display="mailto:regis.guieu@univ-amu.fr" xr:uid="{7B7A75DE-8938-2045-8EB3-81788847B8C9}"/>
+    <hyperlink ref="G97" r:id="rId63" display="mailto:julien.fromonot@ap-hm.fr" xr:uid="{E307BDF4-2C0A-F94F-97AF-C5C43BCA00CA}"/>
+    <hyperlink ref="G98" r:id="rId64" display="mailto:sylvain.lehmann@umontpellier.fr" xr:uid="{0C78F5DE-A083-0742-B61B-C56D7084F18D}"/>
+    <hyperlink ref="G99" r:id="rId65" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{63EA7B8F-206E-E843-A40E-20993359E6D5}"/>
+    <hyperlink ref="I99" r:id="rId66" xr:uid="{74FEA717-1429-7B46-B57E-05A7EEA92161}"/>
+    <hyperlink ref="G100" r:id="rId67" display="mailto:s-lehmann@chu-montpellier.fr" xr:uid="{7CFF7B10-439A-5D41-A23B-221F96517AF4}"/>
+    <hyperlink ref="G101" r:id="rId68" display="mailto:s-badiou@chu-montpellier.fr" xr:uid="{6C1FBD82-1CBF-7641-BBD3-F135C24FB0A0}"/>
+    <hyperlink ref="G102" r:id="rId69" display="mailto:jp-cristol@chu-montpellier.fr" xr:uid="{B97089C4-568E-C04A-A7DF-3CE2E4364FAC}"/>
+    <hyperlink ref="G103" r:id="rId70" display="mailto:sjaisson@chu-reims.fr" xr:uid="{82FFFC16-2B6E-EE46-B62E-3B449DBF62F4}"/>
+    <hyperlink ref="G104" r:id="rId71" display="mailto:sjaisson@chu-reims.fr" xr:uid="{03ABDE49-B71A-114B-BBB0-4385451EA80F}"/>
+    <hyperlink ref="G105" r:id="rId72" display="mailto:dmarot@chu-reims.fr" xr:uid="{914E30D8-AE96-B146-AE96-A665020529BE}"/>
+    <hyperlink ref="G106" r:id="rId73" display="mailto:lramont@chu-reims.fr" xr:uid="{4EAA1429-669C-404A-B2EA-0C34ACC3BF21}"/>
+    <hyperlink ref="G107" r:id="rId74" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{98B90DDB-72C1-084D-9498-7CD8298183A4}"/>
+    <hyperlink ref="G108" r:id="rId75" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{84031370-A25E-DA46-9109-9E603E92176E}"/>
+    <hyperlink ref="G109" r:id="rId76" display="mailto:Caroline.moreau@univ-rennes.fr" xr:uid="{49C350B4-6874-1649-919A-BC1C4D8764E2}"/>
+    <hyperlink ref="G110" r:id="rId77" display="mailto:jean.mosser@univ-rennes.fr" xr:uid="{B17F1D67-CE4D-F547-88E0-DADEC10457F8}"/>
+    <hyperlink ref="G111" r:id="rId78" display="mailto:marie-dominique-galibert-anne@univ-rennes.fr" xr:uid="{4955350F-AD67-2D49-AB6D-3BCEB89B72ED}"/>
+    <hyperlink ref="G114" r:id="rId79" display="mailto:houda.hamdi@chu-rennes.fr" xr:uid="{284F1AAC-C96E-4741-85C2-FE59EFD6D21A}"/>
+    <hyperlink ref="G115" r:id="rId80" display="mailto:marie.de.tayrac@chu-rennes.fr" xr:uid="{25612B46-6B22-A74D-8FCA-F5C470BB17BE}"/>
+    <hyperlink ref="G116" r:id="rId81" display="mailto:Claude.bendavid@univ-rennes.fr" xr:uid="{BD192653-5DC9-0E48-85F2-420E7B710C1D}"/>
+    <hyperlink ref="G117" r:id="rId82" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{5C1F7FBB-0230-2240-BD70-9EDC6C0A085C}"/>
+    <hyperlink ref="G118" r:id="rId83" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{BF20034E-2F10-4D4F-A4C3-CB8CF25AFA9F}"/>
+    <hyperlink ref="G119" r:id="rId84" display="mailto:christele.dubourg@chu-rennes.fr" xr:uid="{B41A5A99-7810-404B-BE81-E5BEB0F3010B}"/>
+    <hyperlink ref="I120" r:id="rId85" xr:uid="{6BC9BD55-8FEE-4942-A5E6-4F02914FAF04}"/>
+    <hyperlink ref="I121" r:id="rId86" xr:uid="{E244D2FF-3F85-F54A-99A7-243B07A96F1F}"/>
+    <hyperlink ref="I122" r:id="rId87" xr:uid="{6C24E5F5-2AFA-B548-B37F-B150439BC3E9}"/>
+    <hyperlink ref="I124" r:id="rId88" xr:uid="{6C9A006B-B605-104B-A1A2-D37DBDD74AC8}"/>
+    <hyperlink ref="I125" r:id="rId89" xr:uid="{1CF3150B-FE16-5941-A388-6827A20A78BA}"/>
+    <hyperlink ref="G126" r:id="rId90" display="mailto:raphael.thuillier@univ-poitiers.fr" xr:uid="{6E305BED-08D9-4D4B-8E6C-3B1379139897}"/>
+    <hyperlink ref="G131" r:id="rId91" display="http://deprunier@chu-angers.fr" xr:uid="{B6320878-3C15-DB42-8AD1-ABCF15930065}"/>
+    <hyperlink ref="I139" r:id="rId92" xr:uid="{FF6B806A-8EC8-9342-BC3A-B5FAB6A6E149}"/>
+    <hyperlink ref="I143" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
+    <hyperlink ref="I144" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
+    <hyperlink ref="I2" r:id="rId95" xr:uid="{ACE3431A-695C-1944-A1A8-1AE467A8F901}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209B9E0E-49A5-CD42-B252-6AB040DE8882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1C4534-F8CF-E345-AB9F-E74B89108426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35440" yWindow="-4900" windowWidth="32400" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="610">
   <si>
     <t>Villes</t>
   </si>
@@ -2839,6 +2839,24 @@
   <si>
     <t>Une expertise clinique et biologique reconnue dans l’étude phénotypique des dyslipidémies en lien étroit avec le Centre de dépistage de l’athérosclérose (CEPTA), les services d’Endocrinologie, Neuro-Vasculaire et Pédiatrie réunis dans un Centre Clinico-Biologique en Lipidologie (labellisation NFSA, 2022). La mise en place en janvier 2020, fortement soutenue par le pôle de biologie-pathologie, d’un panel NGS « HF, Sitostérolémie, HTG majeures », permet de compléter l’offre pour une prise en charge globale et adaptée du patient de la Nouvelle Aquitaine. Ce développement s’accompagne d’une forte réduction des délais de rendu des résultats ainsi que des échanges réguliers au plan national avec les collègues des laboratoires bénéficiant de la labellisation en vue de complément d’analyse génétique avec un panel plus étendu, ou de présentation en RCP en vue d’analyse très-haut débit (plateforme Auragen). 
 Un rayonnement pédagogique axé sur les apports en santé publique matérialisé par la diffusion d’informations (diagnostic - prise en charge thérapeutique - prévention) et l’animation de formations continues auprès des professionnels de santé.</t>
+  </si>
+  <si>
+    <t>https://www.chu-bordeaux.fr/Les-services/Service-de-biochimie/</t>
+  </si>
+  <si>
+    <t>https://ctm.ube.fr/</t>
+  </si>
+  <si>
+    <t>https://www.gemeli-uga.fr/</t>
+  </si>
+  <si>
+    <t>https://www.univ-st-etienne.fr/fr/synatac.html</t>
+  </si>
+  <si>
+    <t>https://www.igred.fr/equipe/approche-translationnelle-des-lesions-epitheliales-et-de-leur-reparation-2/</t>
+  </si>
+  <si>
+    <t>https://www.chu-clermontferrand.fr/liste-services/direction-de-la-recherche-clinique-et-de-linnovation-drci</t>
   </si>
 </sst>
 </file>
@@ -3061,9 +3079,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3074,6 +3089,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3300,7 +3318,7 @@
     <col min="5" max="5" width="55.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="79.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="60.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="76.6640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="144.5" style="4" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -3337,7 +3355,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3359,7 +3377,7 @@
       <c r="G2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="15" t="s">
         <v>599</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -3461,7 +3479,9 @@
       <c r="H5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -3498,7 +3518,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" ht="241" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -3511,19 +3531,21 @@
       <c r="D7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>601</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="18" t="s">
         <v>603</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -5239,7 +5261,7 @@
       <c r="H65" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="I65" s="9"/>
+      <c r="I65" s="1"/>
       <c r="J65" s="5"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -5268,13 +5290,15 @@
       <c r="H66" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="5" t="s">
+        <v>608</v>
+      </c>
       <c r="J66" s="5"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>452</v>
       </c>
@@ -5297,7 +5321,9 @@
       <c r="H67" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I67" s="1"/>
+      <c r="I67" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -5362,69 +5388,89 @@
       <c r="M69" s="1"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15" t="s">
+      <c r="B70" s="20"/>
+      <c r="C70" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="20" t="s">
         <v>340</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G70" s="17" t="s">
+      <c r="G70" s="19" t="s">
         <v>193</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="I70" s="16"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="20"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="15"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
+      <c r="A71" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>340</v>
+      </c>
       <c r="F71" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G71" s="17"/>
+      <c r="G71" s="19" t="s">
+        <v>193</v>
+      </c>
       <c r="H71" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="I71" s="16"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="20"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A72" s="15"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
+      <c r="A72" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>340</v>
+      </c>
       <c r="F72" s="9"/>
-      <c r="G72" s="17"/>
+      <c r="G72" s="19" t="s">
+        <v>193</v>
+      </c>
       <c r="H72" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="I72" s="16"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="15"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="20"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
@@ -5505,7 +5551,7 @@
         <v>198</v>
       </c>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="I75" s="6"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -5534,7 +5580,9 @@
       <c r="H76" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I76" s="1"/>
+      <c r="I76" s="5" t="s">
+        <v>605</v>
+      </c>
       <c r="J76" s="5"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -5650,7 +5698,9 @@
       <c r="H80" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I80" s="1"/>
+      <c r="I80" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -5766,7 +5816,9 @@
       <c r="H84" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I84" s="1"/>
+      <c r="I84" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -7701,19 +7753,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="G70:G72"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="D70:D72"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="K70:K72"/>
-    <mergeCell ref="L70:L72"/>
-    <mergeCell ref="M70:M72"/>
-    <mergeCell ref="I70:I72"/>
-    <mergeCell ref="J70:J72"/>
-  </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
@@ -7811,6 +7850,13 @@
     <hyperlink ref="I143" r:id="rId93" xr:uid="{76EC3D46-A11A-4E40-8EBE-BE51D6E70F8A}"/>
     <hyperlink ref="I144" r:id="rId94" xr:uid="{C3D17D62-9AA0-F340-BC6F-E914D2714F6B}"/>
     <hyperlink ref="I2" r:id="rId95" xr:uid="{ACE3431A-695C-1944-A1A8-1AE467A8F901}"/>
+    <hyperlink ref="I76" r:id="rId96" xr:uid="{54B0FCEC-DCAC-D041-8A30-A95C59C5770B}"/>
+    <hyperlink ref="I80" r:id="rId97" xr:uid="{97A48BA7-EE92-6848-9D6E-9B40A7B46687}"/>
+    <hyperlink ref="I84" r:id="rId98" xr:uid="{E827B391-3A73-8942-810B-6726BB702414}"/>
+    <hyperlink ref="I66" r:id="rId99" xr:uid="{BDE42E8F-6435-614E-9205-D14EC7BD29B3}"/>
+    <hyperlink ref="I67" r:id="rId100" xr:uid="{44FB7309-50A0-364E-9855-7E0C190D88BE}"/>
+    <hyperlink ref="G71" r:id="rId101" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{54E1D358-4312-A740-9D72-59EE8DB0B001}"/>
+    <hyperlink ref="G72" r:id="rId102" tooltip="mailto:coulbault-l@unicaen.fr" display="mailto:coulbault-l@unicaen.fr" xr:uid="{E412BE40-E4E0-CD41-BA90-595DBBB977A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1C4534-F8CF-E345-AB9F-E74B89108426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F8A247-3EFC-A046-8CC0-346F92FBA45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="611">
   <si>
     <t>Villes</t>
   </si>
@@ -852,9 +852,6 @@
     <t>allouche-s@chu-caen.fr</t>
   </si>
   <si>
-    <t>Diagnostic biochimique des maladies mitochondriales : mesure de l’activité enzymatique des complexes de la chaîne respiratoire mitochondriale par spectrophotométrie sur homogénats musculaires et fibroblastes ; mesure de la respiration sur fibroblastes perméabilisés par oxygraphie. Diagnostic génétique : séquençage NGS de l’ADN mitochondrial ; analyse des 1136 gènes nucléaires à fonction mitochondriale par WES.Diagnostic des déficits en CoQ10 : dosage du CoQ10 par HPLC-MS/MS sur plasma, muscle, fibroblaste</t>
-  </si>
-  <si>
     <t>coulbault-l@chu-caen.fr</t>
   </si>
   <si>
@@ -2857,6 +2854,12 @@
   </si>
   <si>
     <t>https://www.chu-clermontferrand.fr/liste-services/direction-de-la-recherche-clinique-et-de-linnovation-drci</t>
+  </si>
+  <si>
+    <t>Mesure de l’activité enzymatique des complexes de la chaîne respiratoire mitochondriale par spectrophotométrie sur homogénats musculaires et fibroblastes ; mesure de la respiration sur fibroblastes perméabilisés par oxygraphie. Diagnostic génétique : séquençage NGS de l’ADN mitochondrial ; analyse des 1136 gènes nucléaires à fonction mitochondriale par WES.Diagnostic des déficits en CoQ10 : dosage du CoQ10 par HPLC-MS/MS sur plasma, muscle, fibroblaste</t>
+  </si>
+  <si>
+    <t>Diagnostic biochimique des maladies mitochondriales</t>
   </si>
 </sst>
 </file>
@@ -3063,7 +3066,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3089,9 +3092,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3318,7 +3324,7 @@
     <col min="5" max="5" width="55.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="79.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="60.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="144.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="255.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -3327,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -3348,7 +3354,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3360,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
@@ -3369,19 +3375,19 @@
         <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3393,13 +3399,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>50</v>
@@ -3408,13 +3414,13 @@
         <v>51</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3426,7 +3432,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>117</v>
@@ -3441,13 +3447,13 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -3459,7 +3465,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -3471,7 +3477,7 @@
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>54</v>
@@ -3480,7 +3486,7 @@
         <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -3492,7 +3498,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -3523,7 +3529,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
@@ -3532,19 +3538,19 @@
         <v>45</v>
       </c>
       <c r="E7" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -3563,7 +3569,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
@@ -3743,7 +3749,7 @@
         <v>60</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>40</v>
@@ -3824,7 +3830,7 @@
         <v>45</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>60</v>
@@ -3847,7 +3853,7 @@
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>45</v>
@@ -3934,13 +3940,13 @@
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>70</v>
@@ -3969,7 +3975,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>70</v>
@@ -3998,7 +4004,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
@@ -4021,13 +4027,13 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -4056,7 +4062,7 @@
         <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>70</v>
@@ -4088,7 +4094,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>81</v>
@@ -4114,7 +4120,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>82</v>
@@ -4141,7 +4147,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>82</v>
@@ -4168,7 +4174,7 @@
         <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>82</v>
@@ -4189,13 +4195,13 @@
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>82</v>
@@ -4216,13 +4222,13 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>87</v>
@@ -4338,7 +4344,7 @@
         <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>99</v>
@@ -4361,13 +4367,13 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>99</v>
@@ -4396,7 +4402,7 @@
         <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>99</v>
@@ -4419,13 +4425,13 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>99</v>
@@ -4451,7 +4457,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>106</v>
@@ -4592,7 +4598,7 @@
         <v>176</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>13</v>
@@ -4601,7 +4607,7 @@
         <v>44</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>135</v>
@@ -4623,7 +4629,7 @@
         <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>15</v>
@@ -4632,7 +4638,7 @@
         <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>135</v>
@@ -4654,7 +4660,7 @@
         <v>176</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>140</v>
@@ -4663,7 +4669,7 @@
         <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>141</v>
@@ -4672,7 +4678,7 @@
         <v>142</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4685,7 +4691,7 @@
         <v>176</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>13</v>
@@ -4694,7 +4700,7 @@
         <v>45</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>141</v>
@@ -4716,7 +4722,7 @@
         <v>176</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
@@ -4725,7 +4731,7 @@
         <v>44</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>144</v>
@@ -4747,7 +4753,7 @@
         <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>7</v>
@@ -4756,7 +4762,7 @@
         <v>45</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>147</v>
@@ -4778,16 +4784,16 @@
         <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>150</v>
@@ -4809,7 +4815,7 @@
         <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>15</v>
@@ -4818,7 +4824,7 @@
         <v>44</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>150</v>
@@ -4840,16 +4846,16 @@
         <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
@@ -4871,16 +4877,16 @@
         <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>147</v>
@@ -4902,7 +4908,7 @@
         <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>157</v>
@@ -4911,7 +4917,7 @@
         <v>44</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>158</v>
@@ -4933,7 +4939,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>13</v>
@@ -4942,7 +4948,7 @@
         <v>44</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>161</v>
@@ -4964,7 +4970,7 @@
         <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>13</v>
@@ -4973,7 +4979,7 @@
         <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>163</v>
@@ -4982,7 +4988,7 @@
         <v>159</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -4995,16 +5001,16 @@
         <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>164</v>
@@ -5026,7 +5032,7 @@
         <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>157</v>
@@ -5035,7 +5041,7 @@
         <v>44</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>167</v>
@@ -5057,7 +5063,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>157</v>
@@ -5066,7 +5072,7 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>163</v>
@@ -5088,7 +5094,7 @@
         <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>157</v>
@@ -5097,7 +5103,7 @@
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>163</v>
@@ -5119,7 +5125,7 @@
         <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>15</v>
@@ -5128,7 +5134,7 @@
         <v>45</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>163</v>
@@ -5150,7 +5156,7 @@
         <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>15</v>
@@ -5159,16 +5165,16 @@
         <v>44</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="H62" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -5181,7 +5187,7 @@
         <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -5190,19 +5196,19 @@
         <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="I63" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>403</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -5214,7 +5220,7 @@
         <v>176</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>15</v>
@@ -5223,14 +5229,14 @@
         <v>45</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -5240,14 +5246,14 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>178</v>
@@ -5259,7 +5265,7 @@
         <v>180</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="5"/>
@@ -5269,20 +5275,20 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>181</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>182</v>
@@ -5291,7 +5297,7 @@
         <v>183</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="1"/>
@@ -5300,7 +5306,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -5310,19 +5316,19 @@
         <v>45</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>184</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -5331,7 +5337,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
@@ -5341,7 +5347,7 @@
         <v>45</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>185</v>
@@ -5358,208 +5364,202 @@
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1" t="s">
+      <c r="B69" s="19"/>
+      <c r="C69" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D69" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H69" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="I69" s="19"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+    </row>
+    <row r="70" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="F70" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I69" s="1"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" s="20" t="s">
+      <c r="G70" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="23"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+    </row>
+    <row r="71" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20" t="s">
+      <c r="B71" s="19"/>
+      <c r="C71" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D71" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="F70" s="9" t="s">
+      <c r="E71" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="F71" s="22" t="s">
         <v>375</v>
       </c>
-      <c r="G70" s="19" t="s">
+      <c r="G71" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="H70" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="I70" s="21"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="20"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="20"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+    </row>
+    <row r="72" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20" t="s">
+      <c r="B72" s="19"/>
+      <c r="C72" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="20" t="s">
+      <c r="D72" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="G71" s="19" t="s">
+      <c r="E72" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="F72" s="22"/>
+      <c r="G72" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="H71" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="I71" s="21"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="23"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+    </row>
+    <row r="73" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20" t="s">
+      <c r="B73" s="19"/>
+      <c r="C73" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>610</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H73" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I73" s="22"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="19"/>
+      <c r="M73" s="19"/>
+    </row>
+    <row r="74" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D72" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="I72" s="21"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="20"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="20"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+      <c r="D74" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F74" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H74" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19"/>
+    </row>
+    <row r="75" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="G74" s="5" t="s">
+      <c r="B75" s="19"/>
+      <c r="C75" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F75" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F75" s="9" t="s">
+      <c r="G75" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+      <c r="M75" s="19"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
@@ -5569,19 +5569,19 @@
         <v>44</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="I76" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="1"/>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
@@ -5600,16 +5600,16 @@
         <v>44</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="5"/>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
@@ -5629,16 +5629,16 @@
         <v>45</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F78" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="G78" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="H78" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
@@ -5658,16 +5658,16 @@
         <v>44</v>
       </c>
       <c r="E79" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="H79" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5677,29 +5677,29 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="I80" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
@@ -5718,16 +5718,16 @@
         <v>44</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="H81" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="5"/>
@@ -5737,26 +5737,26 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F82" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="H82" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5766,26 +5766,26 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F83" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G83" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="H83" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5795,29 +5795,29 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G84" s="10" t="s">
+      <c r="H84" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="I84" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -5826,7 +5826,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -5836,16 +5836,16 @@
         <v>44</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="5"/>
@@ -5855,7 +5855,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
@@ -5865,16 +5865,16 @@
         <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="H86" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -5884,26 +5884,26 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="H87" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5913,26 +5913,26 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G88" s="10" t="s">
+      <c r="H88" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
@@ -5952,16 +5952,16 @@
         <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G89" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G89" s="10" t="s">
+      <c r="H89" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -5981,16 +5981,16 @@
         <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G90" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -6000,7 +6000,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
@@ -6010,16 +6010,16 @@
         <v>45</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>252</v>
-      </c>
       <c r="H91" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -6029,29 +6029,29 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I92" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -6060,26 +6060,26 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="H93" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6089,26 +6089,26 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="G94" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="H94" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -6128,13 +6128,13 @@
         <v>45</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
@@ -6155,16 +6155,16 @@
         <v>45</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G96" s="1" t="s">
+      <c r="H96" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6174,26 +6174,26 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G97" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="G97" s="5" t="s">
+      <c r="H97" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6203,7 +6203,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
@@ -6213,16 +6213,16 @@
         <v>44</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="G98" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="H98" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -6232,29 +6232,29 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I99" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
@@ -6273,16 +6273,16 @@
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="H100" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
@@ -6302,16 +6302,16 @@
         <v>45</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G101" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="H101" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6321,26 +6321,26 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H102" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6350,7 +6350,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
@@ -6360,16 +6360,16 @@
         <v>44</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="G103" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="H103" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6379,26 +6379,26 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F104" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6408,26 +6408,26 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G105" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
@@ -6447,16 +6447,16 @@
         <v>44</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G106" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="H106" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6466,26 +6466,26 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="G107" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="H107" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6495,26 +6495,26 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F108" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G108" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>305</v>
-      </c>
       <c r="H108" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6524,26 +6524,26 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="H109" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
@@ -6563,16 +6563,16 @@
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="G110" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="H110" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
@@ -6592,16 +6592,16 @@
         <v>44</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F111" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G111" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="H111" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6611,7 +6611,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
@@ -6621,16 +6621,16 @@
         <v>44</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="G112" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
@@ -6650,16 +6650,16 @@
         <v>45</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F113" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="H113" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6669,26 +6669,26 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G114" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G114" s="5" t="s">
+      <c r="H114" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -6698,26 +6698,26 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="F115" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G115" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G115" s="5" t="s">
+      <c r="H115" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
@@ -6737,16 +6737,16 @@
         <v>45</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6756,26 +6756,26 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G117" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H117" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -6785,26 +6785,26 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H118" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -6814,26 +6814,26 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E119" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H119" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
@@ -6843,147 +6843,147 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G120" s="10" t="s">
+      <c r="H120" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="I120" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="I120" s="5" t="s">
-        <v>460</v>
       </c>
       <c r="J120" s="11"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G121" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G121" s="12" t="s">
+      <c r="H121" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="I121" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J121" s="11"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G122" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G122" s="10" t="s">
+      <c r="H122" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="I122" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J122" s="11"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="G123" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="G123" s="10" t="s">
+      <c r="H123" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="I123" s="11" t="s">
         <v>470</v>
-      </c>
-      <c r="I123" s="11" t="s">
-        <v>471</v>
       </c>
       <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="G124" s="6" t="s">
+      <c r="H124" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="H124" s="13" t="s">
+      <c r="I124" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="J124" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
@@ -6993,25 +6993,25 @@
         <v>44</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="G125" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="I125" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="I125" s="5" t="s">
-        <v>482</v>
       </c>
       <c r="J125" s="1"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
@@ -7021,69 +7021,69 @@
         <v>45</v>
       </c>
       <c r="E126" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="G126" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="H126" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="J126" s="1"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G127" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G127" s="9" t="s">
+      <c r="H127" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="J127" s="1"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -7091,254 +7091,254 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="G129" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="H129" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="I129" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>503</v>
       </c>
       <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E130" s="9" t="s">
+      <c r="F130" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="G130" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="H130" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="I130" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>509</v>
       </c>
       <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E131" s="9" t="s">
+      <c r="F131" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="I131" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E132" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="G132" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="H132" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E133" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G133" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G133" s="9" t="s">
+      <c r="H133" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E134" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G134" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G134" s="9" t="s">
+      <c r="H134" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E135" s="9" t="s">
+      <c r="F135" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G135" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G135" s="9" t="s">
+      <c r="H135" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G136" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="G136" s="9" t="s">
-        <v>529</v>
-      </c>
       <c r="H136" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E137" s="9" t="s">
+      <c r="F137" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="G137" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="H137" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="H137" s="9" t="s">
+      <c r="I137" s="6" t="s">
         <v>534</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>535</v>
       </c>
       <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>192</v>
@@ -7347,28 +7347,28 @@
         <v>45</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="H138" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="H138" s="9" t="s">
-        <v>537</v>
-      </c>
       <c r="I138" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>192</v>
@@ -7377,88 +7377,88 @@
         <v>44</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="G139" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="H139" s="9" t="s">
+      <c r="I139" s="5" t="s">
         <v>540</v>
-      </c>
-      <c r="I139" s="5" t="s">
-        <v>541</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E140" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G140" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="G140" s="6" t="s">
+      <c r="H140" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="H140" s="9" t="s">
-        <v>544</v>
-      </c>
       <c r="I140" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E141" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="G141" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="H141" s="9" t="s">
+      <c r="I141" s="6" t="s">
         <v>547</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>548</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>13</v>
@@ -7467,28 +7467,28 @@
         <v>45</v>
       </c>
       <c r="E142" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="G142" s="6" t="s">
+      <c r="H142" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="H142" s="9" t="s">
-        <v>551</v>
-      </c>
       <c r="I142" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>13</v>
@@ -7497,28 +7497,28 @@
         <v>44</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="G143" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="H143" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="H143" s="9" t="s">
+      <c r="I143" s="5" t="s">
         <v>555</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>556</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>13</v>
@@ -7527,28 +7527,28 @@
         <v>44</v>
       </c>
       <c r="E144" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="G144" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="H144" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="G144" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="H144" s="9" t="s">
+      <c r="I144" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>15</v>
@@ -7557,28 +7557,28 @@
         <v>45</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G145" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="H145" s="9" t="s">
-        <v>562</v>
-      </c>
       <c r="I145" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>157</v>
@@ -7587,28 +7587,28 @@
         <v>45</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>15</v>
@@ -7617,28 +7617,28 @@
         <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="F147" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="F147" s="14" t="s">
+      <c r="G147" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="H147" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="H147" s="9" t="s">
+      <c r="I147" s="6" t="s">
         <v>567</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>568</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>157</v>
@@ -7647,109 +7647,109 @@
         <v>44</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="G148" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="H148" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="H148" s="9" t="s">
+      <c r="I148" s="6" t="s">
         <v>572</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>573</v>
       </c>
       <c r="J148" s="1"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G149" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="G149" s="6" t="s">
+      <c r="H149" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="H149" s="9" t="s">
-        <v>576</v>
-      </c>
       <c r="I149" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="H150" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="G150" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="H150" s="9" t="s">
+      <c r="I150" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E151" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F151" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="G151" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="H151" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="I151" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="I151" s="4" t="s">
-        <v>584</v>
       </c>
     </row>
   </sheetData>

--- a/expertises.xlsx
+++ b/expertises.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guyon_joris/Documents/Science/Attractivité/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F8A247-3EFC-A046-8CC0-346F92FBA45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E35186-6E8A-3340-9217-54D3CD9299E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2040" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -2237,9 +2240,6 @@
     <t>Clermont-Ferrand</t>
   </si>
   <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
     <t>Limoges</t>
   </si>
   <si>
@@ -2860,13 +2860,16 @@
   </si>
   <si>
     <t>Diagnostic biochimique des maladies mitochondriales</t>
+  </si>
+  <si>
+    <t>Saint-Etienne</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2898,14 +2901,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3038,8 +3033,23 @@
       <color theme="10"/>
       <name val="Calibri (Corps)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3048,7 +3058,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor theme="8" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -3066,22 +3082,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3092,12 +3107,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3317,49 +3331,49 @@
   <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="55.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="79.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="255.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="38" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="55.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="60.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="255.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3383,11 +3397,11 @@
       <c r="G2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>598</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>599</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -3413,13 +3427,13 @@
       <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>398</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>397</v>
       </c>
       <c r="J3" s="1"/>
@@ -3446,13 +3460,13 @@
       <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>395</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>341</v>
       </c>
       <c r="J4" s="1"/>
@@ -3479,14 +3493,14 @@
       <c r="F5" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -3512,7 +3526,7 @@
       <c r="F6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -3524,7 +3538,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -3537,20 +3551,20 @@
       <c r="D7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>600</v>
+      <c r="E7" s="15" t="s">
+        <v>599</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -3574,7 +3588,7 @@
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -3603,7 +3617,7 @@
       <c r="F9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -3632,7 +3646,7 @@
       <c r="F10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -3661,7 +3675,7 @@
       <c r="F11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -3690,7 +3704,7 @@
       <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -3719,7 +3733,7 @@
       <c r="F13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -3777,7 +3791,7 @@
       <c r="F15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -3864,7 +3878,7 @@
       <c r="F18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -3893,7 +3907,7 @@
       <c r="F19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>64</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -3951,7 +3965,7 @@
       <c r="F21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -3980,7 +3994,7 @@
       <c r="F22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -4009,7 +4023,7 @@
       <c r="F23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
@@ -4038,7 +4052,7 @@
       <c r="F24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>76</v>
       </c>
       <c r="H24" s="1" t="s">
@@ -4067,7 +4081,7 @@
       <c r="F25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
@@ -4096,7 +4110,7 @@
       <c r="F26" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>81</v>
       </c>
       <c r="H26" s="1" t="s">
@@ -4125,7 +4139,7 @@
       <c r="F27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>83</v>
       </c>
       <c r="H27" s="1"/>
@@ -4152,7 +4166,7 @@
       <c r="F28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>84</v>
       </c>
       <c r="H28" s="1"/>
@@ -4179,7 +4193,7 @@
       <c r="F29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>85</v>
       </c>
       <c r="H29" s="1"/>
@@ -4206,7 +4220,7 @@
       <c r="F30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>84</v>
       </c>
       <c r="H30" s="1"/>
@@ -4233,7 +4247,7 @@
       <c r="F31" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>88</v>
       </c>
       <c r="H31" s="1" t="s">
@@ -4262,7 +4276,7 @@
       <c r="F32" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H32" s="1" t="s">
@@ -4291,7 +4305,7 @@
       <c r="F33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>111</v>
       </c>
       <c r="H33" s="1" t="s">
@@ -4320,13 +4334,13 @@
       <c r="F34" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I34" s="8"/>
+      <c r="I34" s="7"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -4349,7 +4363,7 @@
       <c r="F35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>100</v>
       </c>
       <c r="H35" s="1" t="s">
@@ -4378,7 +4392,7 @@
       <c r="F36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H36" s="1" t="s">
@@ -4407,7 +4421,7 @@
       <c r="F37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>103</v>
       </c>
       <c r="H37" s="1" t="s">
@@ -4436,7 +4450,7 @@
       <c r="F38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>104</v>
       </c>
       <c r="H38" s="1" t="s">
@@ -4465,7 +4479,7 @@
       <c r="F39" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="5" t="s">
         <v>115</v>
       </c>
       <c r="H39" s="1" t="s">
@@ -4494,7 +4508,7 @@
       <c r="F40" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>120</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -4523,7 +4537,7 @@
       <c r="F41" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>124</v>
       </c>
       <c r="H41" s="1" t="s">
@@ -4552,7 +4566,7 @@
       <c r="F42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>124</v>
       </c>
       <c r="H42" s="1" t="s">
@@ -4581,11 +4595,11 @@
       <c r="F43" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G43" s="6"/>
+      <c r="G43" s="5"/>
       <c r="H43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="4" t="s">
         <v>132</v>
       </c>
       <c r="J43" s="1"/>
@@ -4612,7 +4626,7 @@
       <c r="F44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>136</v>
       </c>
       <c r="H44" s="1" t="s">
@@ -4643,7 +4657,7 @@
       <c r="F45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="4" t="s">
         <v>138</v>
       </c>
       <c r="H45" s="1" t="s">
@@ -4674,7 +4688,7 @@
       <c r="F46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>142</v>
       </c>
       <c r="H46" s="1" t="s">
@@ -4705,7 +4719,7 @@
       <c r="F47" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>136</v>
       </c>
       <c r="H47" s="1" t="s">
@@ -4798,7 +4812,7 @@
       <c r="F50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H50" s="1" t="s">
@@ -4829,7 +4843,7 @@
       <c r="F51" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H51" s="1" t="s">
@@ -4891,7 +4905,7 @@
       <c r="F53" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="4" t="s">
         <v>155</v>
       </c>
       <c r="H53" s="1" t="s">
@@ -5015,7 +5029,7 @@
       <c r="F57" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="4" t="s">
         <v>165</v>
       </c>
       <c r="H57" s="1" t="s">
@@ -5046,7 +5060,7 @@
       <c r="F58" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>168</v>
       </c>
       <c r="H58" s="1" t="s">
@@ -5108,7 +5122,7 @@
       <c r="F60" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="4" t="s">
         <v>172</v>
       </c>
       <c r="H60" s="1" t="s">
@@ -5139,7 +5153,7 @@
       <c r="F61" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="4" t="s">
         <v>174</v>
       </c>
       <c r="H61" s="1" t="s">
@@ -5170,7 +5184,7 @@
       <c r="F62" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>362</v>
       </c>
       <c r="H62" s="1" t="s">
@@ -5201,13 +5215,13 @@
       <c r="F63" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="4" t="s">
         <v>401</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I63" s="4" t="s">
         <v>402</v>
       </c>
       <c r="J63" s="1"/>
@@ -5232,7 +5246,7 @@
         <v>420</v>
       </c>
       <c r="F64" s="1"/>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="4" t="s">
         <v>366</v>
       </c>
       <c r="H64" s="1" t="s">
@@ -5261,14 +5275,14 @@
       <c r="F65" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="8" t="s">
         <v>368</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="5"/>
+      <c r="J65" s="4"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -5290,16 +5304,16 @@
       <c r="F66" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="4" t="s">
         <v>182</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="J66" s="5"/>
+      <c r="I66" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="J66" s="4"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -5318,17 +5332,17 @@
       <c r="E67" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="4" t="s">
         <v>184</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>608</v>
+      <c r="I67" s="4" t="s">
+        <v>607</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -5349,10 +5363,10 @@
       <c r="E68" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="F68" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="4" t="s">
         <v>186</v>
       </c>
       <c r="H68" s="1" t="s">
@@ -5364,198 +5378,198 @@
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="19" t="s">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19" t="s">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E69" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F69" s="19" t="s">
+      <c r="F69" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="G69" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="H69" s="19" t="s">
+      <c r="H69" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="19"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="19"/>
-      <c r="L69" s="19"/>
-      <c r="M69" s="19"/>
-    </row>
-    <row r="70" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="19" t="s">
+      <c r="I69" s="1"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19" t="s">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="F70" s="22" t="s">
+      <c r="F70" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G70" s="23" t="s">
+      <c r="G70" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="23"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-      <c r="M70" s="19"/>
-    </row>
-    <row r="71" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="19" t="s">
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19" t="s">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="F71" s="22" t="s">
+      <c r="F71" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-    </row>
-    <row r="72" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="19" t="s">
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19" t="s">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="F72" s="22"/>
-      <c r="G72" s="23" t="s">
+      <c r="F72" s="8"/>
+      <c r="G72" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="23"/>
-      <c r="K72" s="19"/>
-      <c r="L72" s="19"/>
-      <c r="M72" s="19"/>
-    </row>
-    <row r="73" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="19" t="s">
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19" t="s">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D73" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="F73" s="22" t="s">
+      <c r="D73" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="G73" s="20" t="s">
+      <c r="G73" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="H73" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="I73" s="22"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="19"/>
-      <c r="M73" s="19"/>
-    </row>
-    <row r="74" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="19" t="s">
+      <c r="H73" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="I73" s="8"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19" t="s">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D74" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E74" s="19" t="s">
+      <c r="D74" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F74" s="22" t="s">
+      <c r="F74" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="G74" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H74" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-      <c r="M74" s="19"/>
-    </row>
-    <row r="75" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="19" t="s">
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19" t="s">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D75" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E75" s="19" t="s">
+      <c r="D75" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F75" s="22" t="s">
+      <c r="F75" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="20" t="s">
+      <c r="G75" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="H75" s="19"/>
-      <c r="I75" s="24"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="19"/>
-      <c r="L75" s="19"/>
-      <c r="M75" s="19"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
@@ -5568,8 +5582,8 @@
       <c r="D76" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>597</v>
+      <c r="E76" s="8" t="s">
+        <v>596</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>199</v>
@@ -5580,10 +5594,10 @@
       <c r="H76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="J76" s="5"/>
+      <c r="I76" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="J76" s="4"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -5612,7 +5626,7 @@
         <v>204</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="5"/>
+      <c r="J77" s="4"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -5631,7 +5645,7 @@
       <c r="E78" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="F78" s="8" t="s">
         <v>206</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -5657,13 +5671,13 @@
       <c r="D79" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="8" t="s">
         <v>208</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="4" t="s">
         <v>210</v>
       </c>
       <c r="H79" s="1" t="s">
@@ -5698,8 +5712,8 @@
       <c r="H80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>605</v>
+      <c r="I80" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -5723,14 +5737,14 @@
       <c r="F81" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="G81" s="4" t="s">
         <v>219</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>220</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="5"/>
+      <c r="J81" s="4"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -5752,7 +5766,7 @@
       <c r="F82" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="4" t="s">
         <v>222</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -5781,7 +5795,7 @@
       <c r="F83" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="4" t="s">
         <v>225</v>
       </c>
       <c r="H83" s="1" t="s">
@@ -5810,14 +5824,14 @@
       <c r="F84" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="9" t="s">
         <v>228</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I84" s="5" t="s">
-        <v>606</v>
+      <c r="I84" s="4" t="s">
+        <v>605</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -5826,7 +5840,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -5841,21 +5855,21 @@
       <c r="F85" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="9" t="s">
         <v>232</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>233</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="5"/>
+      <c r="J85" s="4"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
@@ -5870,7 +5884,7 @@
       <c r="F86" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="9" t="s">
         <v>236</v>
       </c>
       <c r="H86" s="1" t="s">
@@ -5884,7 +5898,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
@@ -5899,7 +5913,7 @@
       <c r="F87" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="G87" s="9" t="s">
         <v>239</v>
       </c>
       <c r="H87" s="1" t="s">
@@ -5913,7 +5927,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
@@ -5928,7 +5942,7 @@
       <c r="F88" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="G88" s="9" t="s">
         <v>243</v>
       </c>
       <c r="H88" s="1" t="s">
@@ -5942,7 +5956,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
@@ -5957,7 +5971,7 @@
       <c r="F89" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="G89" s="9" t="s">
         <v>246</v>
       </c>
       <c r="H89" s="1" t="s">
@@ -5971,7 +5985,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -5986,7 +6000,7 @@
       <c r="F90" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="G90" s="9" t="s">
         <v>248</v>
       </c>
       <c r="H90" s="1" t="s">
@@ -6000,7 +6014,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>452</v>
+        <v>610</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
@@ -6015,7 +6029,7 @@
       <c r="F91" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="G91" s="9" t="s">
         <v>251</v>
       </c>
       <c r="H91" s="1" t="s">
@@ -6044,13 +6058,13 @@
       <c r="F92" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="4" t="s">
         <v>254</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="I92" s="5" t="s">
+      <c r="I92" s="4" t="s">
         <v>423</v>
       </c>
       <c r="J92" s="1"/>
@@ -6075,7 +6089,7 @@
       <c r="F93" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G93" s="4" t="s">
         <v>258</v>
       </c>
       <c r="H93" s="1" t="s">
@@ -6104,7 +6118,7 @@
       <c r="F94" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="4" t="s">
         <v>262</v>
       </c>
       <c r="H94" s="1" t="s">
@@ -6189,7 +6203,7 @@
       <c r="F97" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="G97" s="4" t="s">
         <v>270</v>
       </c>
       <c r="H97" s="1" t="s">
@@ -6218,7 +6232,7 @@
       <c r="F98" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="4" t="s">
         <v>275</v>
       </c>
       <c r="H98" s="1" t="s">
@@ -6247,13 +6261,13 @@
       <c r="F99" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="4" t="s">
         <v>278</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I99" s="5" t="s">
+      <c r="I99" s="4" t="s">
         <v>426</v>
       </c>
       <c r="J99" s="1"/>
@@ -6278,7 +6292,7 @@
       <c r="F100" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="4" t="s">
         <v>281</v>
       </c>
       <c r="H100" s="1" t="s">
@@ -6307,7 +6321,7 @@
       <c r="F101" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="4" t="s">
         <v>284</v>
       </c>
       <c r="H101" s="1" t="s">
@@ -6336,7 +6350,7 @@
       <c r="F102" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="4" t="s">
         <v>278</v>
       </c>
       <c r="H102" s="1" t="s">
@@ -6365,7 +6379,7 @@
       <c r="F103" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="4" t="s">
         <v>291</v>
       </c>
       <c r="H103" s="1" t="s">
@@ -6394,7 +6408,7 @@
       <c r="F104" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="4" t="s">
         <v>291</v>
       </c>
       <c r="H104" s="1" t="s">
@@ -6423,7 +6437,7 @@
       <c r="F105" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="4" t="s">
         <v>295</v>
       </c>
       <c r="H105" s="1" t="s">
@@ -6452,7 +6466,7 @@
       <c r="F106" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="4" t="s">
         <v>298</v>
       </c>
       <c r="H106" s="1" t="s">
@@ -6481,7 +6495,7 @@
       <c r="F107" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="4" t="s">
         <v>304</v>
       </c>
       <c r="H107" s="1" t="s">
@@ -6510,7 +6524,7 @@
       <c r="F108" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="4" t="s">
         <v>304</v>
       </c>
       <c r="H108" s="1" t="s">
@@ -6539,7 +6553,7 @@
       <c r="F109" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="4" t="s">
         <v>309</v>
       </c>
       <c r="H109" s="1" t="s">
@@ -6568,7 +6582,7 @@
       <c r="F110" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="4" t="s">
         <v>313</v>
       </c>
       <c r="H110" s="1" t="s">
@@ -6597,7 +6611,7 @@
       <c r="F111" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="4" t="s">
         <v>316</v>
       </c>
       <c r="H111" s="1" t="s">
@@ -6684,7 +6698,7 @@
       <c r="F114" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>326</v>
       </c>
       <c r="H114" s="1" t="s">
@@ -6713,7 +6727,7 @@
       <c r="F115" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G115" s="5" t="s">
+      <c r="G115" s="4" t="s">
         <v>330</v>
       </c>
       <c r="H115" s="1" t="s">
@@ -6742,7 +6756,7 @@
       <c r="F116" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="G116" s="4" t="s">
         <v>304</v>
       </c>
       <c r="H116" s="1" t="s">
@@ -6771,7 +6785,7 @@
       <c r="F117" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="G117" s="4" t="s">
         <v>333</v>
       </c>
       <c r="H117" s="1" t="s">
@@ -6800,7 +6814,7 @@
       <c r="F118" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>333</v>
       </c>
       <c r="H118" s="1" t="s">
@@ -6829,7 +6843,7 @@
       <c r="F119" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="G119" s="4" t="s">
         <v>333</v>
       </c>
       <c r="H119" s="1" t="s">
@@ -6843,119 +6857,119 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="G120" s="10" t="s">
+      <c r="H120" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="I120" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="I120" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="J120" s="11"/>
+      <c r="J120" s="10"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G121" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="G121" s="12" t="s">
+      <c r="H121" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="I121" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="J121" s="11"/>
+      <c r="I121" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="J121" s="10"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G122" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="G122" s="10" t="s">
+      <c r="H122" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="I122" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="J122" s="11"/>
+      <c r="I122" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="J122" s="10"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="G123" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="G123" s="10" t="s">
+      <c r="H123" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="I123" s="10" t="s">
         <v>469</v>
-      </c>
-      <c r="I123" s="11" t="s">
-        <v>470</v>
       </c>
       <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="1" t="s">
@@ -6965,25 +6979,25 @@
         <v>44</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="G124" s="6" t="s">
+      <c r="H124" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="H124" s="13" t="s">
+      <c r="I124" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="J124" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
@@ -6993,25 +7007,25 @@
         <v>44</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="G125" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="I125" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="I125" s="5" t="s">
-        <v>481</v>
       </c>
       <c r="J125" s="1"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
@@ -7020,70 +7034,70 @@
       <c r="D126" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E126" s="9" t="s">
+      <c r="E126" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="G126" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="H126" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="J126" s="1"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G127" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="F127" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G127" s="9" t="s">
+      <c r="H127" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="J127" s="1"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
@@ -7101,81 +7115,81 @@
         <v>385</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="G129" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="H129" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="I129" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>502</v>
       </c>
       <c r="J129" s="1"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E130" s="9" t="s">
+      <c r="F130" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="G130" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="H130" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="I130" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>508</v>
       </c>
       <c r="J130" s="1"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E131" s="9" t="s">
+      <c r="F131" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>508</v>
+      <c r="I131" s="5" t="s">
+        <v>507</v>
       </c>
       <c r="J131" s="1"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
@@ -7184,50 +7198,50 @@
       <c r="D132" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E132" s="9" t="s">
+      <c r="E132" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="G132" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="H132" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E133" s="9" t="s">
+      <c r="E133" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G133" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G133" s="9" t="s">
+      <c r="H133" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
@@ -7236,79 +7250,79 @@
       <c r="D134" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E134" s="9" t="s">
+      <c r="E134" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G134" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G134" s="9" t="s">
+      <c r="H134" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E135" s="9" t="s">
+      <c r="F135" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G135" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G135" s="9" t="s">
+      <c r="H135" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G136" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G136" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>590</v>
+      <c r="H136" s="8" t="s">
+        <v>589</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>591</v>
+        <v>528</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>590</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>286</v>
@@ -7316,29 +7330,29 @@
       <c r="D137" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E137" s="9" t="s">
+      <c r="E137" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="G137" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="H137" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="H137" s="9" t="s">
+      <c r="I137" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>534</v>
       </c>
       <c r="J137" s="1"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B138" s="9" t="s">
-        <v>592</v>
+        <v>528</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>591</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>192</v>
@@ -7346,29 +7360,29 @@
       <c r="D138" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E138" s="9" t="s">
-        <v>584</v>
+      <c r="E138" s="8" t="s">
+        <v>583</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G138" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="H138" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="H138" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>534</v>
+      <c r="I138" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J138" s="1"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>592</v>
+        <v>528</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>591</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>192</v>
@@ -7377,88 +7391,88 @@
         <v>44</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="G139" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="H139" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="H139" s="9" t="s">
+      <c r="I139" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="I139" s="5" t="s">
-        <v>540</v>
       </c>
       <c r="J139" s="1"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B140" s="9" t="s">
-        <v>593</v>
+        <v>528</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>592</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E140" s="9" t="s">
+      <c r="E140" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G140" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G140" s="6" t="s">
+      <c r="H140" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="H140" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>534</v>
+      <c r="I140" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J140" s="1"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B141" s="9" t="s">
-        <v>593</v>
+        <v>528</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>592</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E141" s="9" t="s">
+      <c r="E141" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="G141" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="H141" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="H141" s="9" t="s">
+      <c r="I141" s="5" t="s">
         <v>546</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>547</v>
       </c>
       <c r="J141" s="1"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>594</v>
+        <v>528</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>593</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>13</v>
@@ -7466,29 +7480,29 @@
       <c r="D142" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E142" s="9" t="s">
+      <c r="E142" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G142" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G142" s="6" t="s">
+      <c r="H142" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="H142" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>534</v>
+      <c r="I142" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J142" s="1"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B143" s="9" t="s">
-        <v>594</v>
+        <v>528</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>593</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>13</v>
@@ -7496,29 +7510,29 @@
       <c r="D143" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E143" s="9" t="s">
+      <c r="E143" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="G143" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="H143" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="H143" s="9" t="s">
+      <c r="I143" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>555</v>
       </c>
       <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B144" s="9" t="s">
-        <v>594</v>
+        <v>528</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>593</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>13</v>
@@ -7526,29 +7540,29 @@
       <c r="D144" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="9" t="s">
+      <c r="E144" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="G144" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="H144" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="G144" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="H144" s="9" t="s">
+      <c r="I144" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>559</v>
       </c>
       <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B145" s="9" t="s">
-        <v>595</v>
+        <v>528</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>594</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>15</v>
@@ -7557,28 +7571,28 @@
         <v>45</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G145" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="H145" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="H145" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>534</v>
+      <c r="I145" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J145" s="1"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B146" s="9" t="s">
-        <v>595</v>
+        <v>528</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>594</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>157</v>
@@ -7587,28 +7601,28 @@
         <v>45</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>534</v>
+        <v>530</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J146" s="1"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>595</v>
+        <v>528</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>594</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>15</v>
@@ -7617,28 +7631,28 @@
         <v>44</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="F147" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="F147" s="14" t="s">
+      <c r="G147" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="H147" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="H147" s="9" t="s">
+      <c r="I147" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>567</v>
       </c>
       <c r="J147" s="1"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>595</v>
+        <v>528</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>594</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>157</v>
@@ -7647,113 +7661,114 @@
         <v>44</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="G148" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="H148" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="H148" s="9" t="s">
+      <c r="I148" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="I148" s="6" t="s">
-        <v>572</v>
       </c>
       <c r="J148" s="1"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>596</v>
+        <v>528</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>595</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G149" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G149" s="6" t="s">
+      <c r="H149" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="H149" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>534</v>
+      <c r="I149" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B150" s="9" t="s">
-        <v>596</v>
+        <v>528</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>595</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="H150" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="G150" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="H150" s="9" t="s">
+      <c r="I150" s="5" t="s">
         <v>577</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>578</v>
       </c>
       <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B151" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C151" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="D151" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E151" s="4" t="s">
+      <c r="F151" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="G151" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="H151" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="I151" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="H151" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="I151" s="4" t="s">
-        <v>583</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="mailto:Emmanuel.richard@u-bordeaux.fr" xr:uid="{41A885EF-EE44-1D4B-8ADE-2984EF4CC86D}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{6558C59A-CBC3-C44B-BF9F-F7B6D9255B4D}"/>
